--- a/VERGARA/Agosto/vergara Agosto.xlsx
+++ b/VERGARA/Agosto/vergara Agosto.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFDFAB0-C707-410A-848B-FB7A3CBE362A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E06FAA7-2937-4909-9D08-761D09A317D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="278">
   <si>
     <t>MAIL: consorciovergara1670@gmail.com</t>
   </si>
@@ -854,6 +854,17 @@
   </si>
   <si>
     <t>EL MES PASADO PAGO BIEN EL 08/07  $145.692,44 Y LA PUSIMOS NO PAGA</t>
+  </si>
+  <si>
+    <t>PAGO LO QUE QUISO:</t>
+  </si>
+  <si>
+    <t>Departamento 4 D: $131653,48
+Cochera N° 30:        $34542,15
+Total abonado:        $166195,63.</t>
+  </si>
+  <si>
+    <t>SE QUEJA POR MAIL DE DEUDA INEXISTENTE Y ADJUNTA COMPROBANTES</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1070,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1135,6 +1146,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1504,7 +1527,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1771,6 +1794,20 @@
     <xf numFmtId="165" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1854,15 +1891,16 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2281,12 +2319,12 @@
       <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="197" t="s">
+      <c r="B5" s="205" t="s">
         <v>255</v>
       </c>
-      <c r="C5" s="195"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="196"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="204"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
@@ -2300,49 +2338,49 @@
       <c r="E6" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="198" t="s">
+      <c r="B8" s="206" t="s">
         <v>263</v>
       </c>
-      <c r="C8" s="187"/>
+      <c r="C8" s="195"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="187"/>
-      <c r="C9" s="187"/>
+      <c r="B9" s="195"/>
+      <c r="C9" s="195"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="187"/>
-      <c r="C10" s="187"/>
+      <c r="B10" s="195"/>
+      <c r="C10" s="195"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="199" t="s">
+      <c r="A13" s="207" t="s">
         <v>254</v>
       </c>
-      <c r="B13" s="200"/>
-      <c r="C13" s="200"/>
-      <c r="D13" s="200"/>
-      <c r="E13" s="200"/>
+      <c r="B13" s="208"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="200"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="200"/>
-      <c r="D14" s="200"/>
-      <c r="E14" s="200"/>
+      <c r="A14" s="208"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="200"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="200"/>
-      <c r="D15" s="200"/>
-      <c r="E15" s="200"/>
+      <c r="A15" s="208"/>
+      <c r="B15" s="208"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
     </row>
     <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="200"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="200"/>
-      <c r="D16" s="200"/>
-      <c r="E16" s="200"/>
+      <c r="A16" s="208"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2438,10 +2476,10 @@
       <c r="E27" s="88"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="188" t="s">
+      <c r="A28" s="196" t="s">
         <v>256</v>
       </c>
-      <c r="B28" s="189"/>
+      <c r="B28" s="197"/>
       <c r="C28" s="5"/>
       <c r="D28" s="184">
         <v>35000</v>
@@ -2451,10 +2489,10 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="188" t="s">
+      <c r="A29" s="196" t="s">
         <v>258</v>
       </c>
-      <c r="B29" s="189"/>
+      <c r="B29" s="197"/>
       <c r="C29" s="5"/>
       <c r="D29" s="184">
         <f>470000</f>
@@ -2498,10 +2536,10 @@
       <c r="G32" s="147"/>
     </row>
     <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="188" t="s">
+      <c r="A33" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="189"/>
+      <c r="B33" s="197"/>
       <c r="C33" s="53"/>
       <c r="D33" s="173">
         <v>719.9</v>
@@ -2638,10 +2676,10 @@
       <c r="E43" s="98"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="188" t="s">
+      <c r="A44" s="196" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="189"/>
+      <c r="B44" s="197"/>
       <c r="C44" s="5"/>
       <c r="D44" s="173">
         <v>88711.15</v>
@@ -2672,10 +2710,10 @@
       <c r="E46" s="94"/>
     </row>
     <row r="47" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="188" t="s">
+      <c r="A47" s="196" t="s">
         <v>268</v>
       </c>
-      <c r="B47" s="189"/>
+      <c r="B47" s="197"/>
       <c r="C47" s="54"/>
       <c r="D47" s="173">
         <v>76500</v>
@@ -2685,10 +2723,10 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="188" t="s">
+      <c r="A48" s="196" t="s">
         <v>262</v>
       </c>
-      <c r="B48" s="189"/>
+      <c r="B48" s="197"/>
       <c r="C48" s="54"/>
       <c r="D48" s="173">
         <v>16500</v>
@@ -2701,10 +2739,10 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="190" t="s">
+      <c r="A49" s="198" t="s">
         <v>260</v>
       </c>
-      <c r="B49" s="191"/>
+      <c r="B49" s="199"/>
       <c r="C49" s="5"/>
       <c r="D49" s="173">
         <v>60000</v>
@@ -2714,10 +2752,10 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="188" t="s">
+      <c r="A50" s="196" t="s">
         <v>248</v>
       </c>
-      <c r="B50" s="189"/>
+      <c r="B50" s="197"/>
       <c r="C50" s="5"/>
       <c r="D50" s="96">
         <f>60650+58080</f>
@@ -2726,8 +2764,8 @@
       <c r="E50" s="177" t="s">
         <v>259</v>
       </c>
-      <c r="I50" s="188"/>
-      <c r="J50" s="189"/>
+      <c r="I50" s="196"/>
+      <c r="J50" s="197"/>
     </row>
     <row r="51" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
@@ -2838,8 +2876,8 @@
       <c r="E62" s="110"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="190"/>
-      <c r="B63" s="192"/>
+      <c r="A63" s="198"/>
+      <c r="B63" s="200"/>
       <c r="C63" s="5"/>
       <c r="D63" s="96"/>
       <c r="E63" s="93"/>
@@ -2864,12 +2902,12 @@
     <row r="66" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="194" t="s">
+      <c r="A68" s="202" t="s">
         <v>41</v>
       </c>
-      <c r="B68" s="195"/>
-      <c r="C68" s="195"/>
-      <c r="D68" s="196"/>
+      <c r="B68" s="203"/>
+      <c r="C68" s="203"/>
+      <c r="D68" s="204"/>
       <c r="E68" s="140"/>
     </row>
     <row r="69" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3035,16 +3073,16 @@
       <c r="F88" s="122"/>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="193" t="s">
+      <c r="A89" s="201" t="s">
         <v>56</v>
       </c>
-      <c r="B89" s="187"/>
-      <c r="C89" s="187"/>
+      <c r="B89" s="195"/>
+      <c r="C89" s="195"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="187"/>
-      <c r="B90" s="187"/>
-      <c r="C90" s="187"/>
+      <c r="A90" s="195"/>
+      <c r="B90" s="195"/>
+      <c r="C90" s="195"/>
     </row>
     <row r="91" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="53"/>
@@ -3079,32 +3117,32 @@
       <c r="M95" s="7"/>
     </row>
     <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="186"/>
-      <c r="B96" s="187"/>
-      <c r="C96" s="187"/>
-      <c r="D96" s="187"/>
-      <c r="E96" s="187"/>
+      <c r="A96" s="194"/>
+      <c r="B96" s="195"/>
+      <c r="C96" s="195"/>
+      <c r="D96" s="195"/>
+      <c r="E96" s="195"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="187"/>
-      <c r="B97" s="187"/>
-      <c r="C97" s="187"/>
-      <c r="D97" s="187"/>
-      <c r="E97" s="187"/>
+      <c r="A97" s="195"/>
+      <c r="B97" s="195"/>
+      <c r="C97" s="195"/>
+      <c r="D97" s="195"/>
+      <c r="E97" s="195"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="187"/>
-      <c r="B98" s="187"/>
-      <c r="C98" s="187"/>
-      <c r="D98" s="187"/>
-      <c r="E98" s="187"/>
+      <c r="A98" s="195"/>
+      <c r="B98" s="195"/>
+      <c r="C98" s="195"/>
+      <c r="D98" s="195"/>
+      <c r="E98" s="195"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="187"/>
-      <c r="B99" s="187"/>
-      <c r="C99" s="187"/>
-      <c r="D99" s="187"/>
-      <c r="E99" s="187"/>
+      <c r="A99" s="195"/>
+      <c r="B99" s="195"/>
+      <c r="C99" s="195"/>
+      <c r="D99" s="195"/>
+      <c r="E99" s="195"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3162,10 +3200,10 @@
       <c r="E1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="214">
+      <c r="F1" s="222">
         <v>2147076</v>
       </c>
-      <c r="G1" s="212"/>
+      <c r="G1" s="220"/>
       <c r="H1" s="175"/>
       <c r="I1" s="175"/>
       <c r="J1" s="175"/>
@@ -3173,16 +3211,16 @@
         <v>58</v>
       </c>
       <c r="L1" s="175"/>
-      <c r="M1" s="211">
+      <c r="M1" s="219">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="212"/>
+      <c r="N1" s="220"/>
       <c r="O1" s="135"/>
-      <c r="P1" s="210">
+      <c r="P1" s="218">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="187"/>
+      <c r="Q1" s="195"/>
       <c r="R1" s="19"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3193,99 +3231,99 @@
       <c r="E2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="202">
+      <c r="F2" s="210">
         <v>770367.15</v>
       </c>
-      <c r="G2" s="203"/>
+      <c r="G2" s="211"/>
       <c r="H2" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="203"/>
+      <c r="I2" s="221"/>
+      <c r="J2" s="211"/>
       <c r="K2" s="175" t="s">
         <v>61</v>
       </c>
       <c r="L2" s="175"/>
-      <c r="M2" s="213"/>
-      <c r="N2" s="203"/>
+      <c r="M2" s="221"/>
+      <c r="N2" s="211"/>
       <c r="O2" s="137"/>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="219"/>
+      <c r="P2" s="226"/>
+      <c r="Q2" s="227"/>
     </row>
     <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="215" t="s">
+      <c r="A3" s="223" t="s">
         <v>62</v>
       </c>
       <c r="B3" s="116"/>
-      <c r="C3" s="204" t="s">
+      <c r="C3" s="212" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="204" t="s">
+      <c r="D3" s="212" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="209" t="s">
+      <c r="E3" s="217" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="204" t="s">
+      <c r="F3" s="212" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="206" t="s">
+      <c r="G3" s="214" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="204" t="s">
+      <c r="H3" s="212" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="217" t="s">
+      <c r="I3" s="225" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="206" t="s">
+      <c r="J3" s="214" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="208" t="str">
+      <c r="K3" s="216" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="206" t="s">
+      <c r="L3" s="214" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="206" t="s">
+      <c r="M3" s="214" t="s">
         <v>71</v>
       </c>
-      <c r="N3" s="206" t="s">
+      <c r="N3" s="214" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="206" t="s">
+      <c r="O3" s="214" t="s">
         <v>73</v>
       </c>
       <c r="P3" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="Q3" s="220" t="s">
+      <c r="Q3" s="228" t="s">
         <v>75</v>
       </c>
       <c r="T3" s="44"/>
     </row>
     <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="216"/>
+      <c r="A4" s="224"/>
       <c r="B4" s="117"/>
-      <c r="C4" s="205"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="207"/>
-      <c r="H4" s="205"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="207"/>
-      <c r="K4" s="205"/>
-      <c r="L4" s="207"/>
-      <c r="M4" s="207"/>
-      <c r="N4" s="207"/>
-      <c r="O4" s="207"/>
+      <c r="C4" s="213"/>
+      <c r="D4" s="213"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="215"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="215"/>
+      <c r="M4" s="215"/>
+      <c r="N4" s="215"/>
+      <c r="O4" s="215"/>
       <c r="P4" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 18/08</v>
       </c>
-      <c r="Q4" s="205"/>
+      <c r="Q4" s="213"/>
     </row>
     <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="61"/>
@@ -4016,16 +4054,16 @@
       <c r="C16" s="61">
         <v>44</v>
       </c>
-      <c r="D16" s="221" t="s">
+      <c r="D16" s="186" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="222" t="s">
+      <c r="E16" s="187" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="223">
+      <c r="F16" s="188">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G16" s="224">
+      <c r="G16" s="189">
         <v>145692.44</v>
       </c>
       <c r="H16" s="118"/>
@@ -4283,13 +4321,13 @@
       <c r="C20" s="61">
         <v>48</v>
       </c>
-      <c r="D20" s="178" t="s">
+      <c r="D20" s="191" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="178" t="s">
+      <c r="E20" s="191" t="s">
         <v>112</v>
       </c>
-      <c r="F20" s="179">
+      <c r="F20" s="192">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G20" s="69">
@@ -5606,13 +5644,13 @@
       <c r="B40" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="C40" s="61">
+      <c r="C40" s="230">
         <v>68</v>
       </c>
-      <c r="D40" s="60" t="s">
+      <c r="D40" s="230" t="s">
         <v>161</v>
       </c>
-      <c r="E40" s="74" t="str">
+      <c r="E40" s="231" t="str">
         <f>D76</f>
         <v>Jesica Romina Tobio</v>
       </c>
@@ -7870,16 +7908,16 @@
     </row>
     <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="61"/>
-      <c r="B76" s="77" t="s">
+      <c r="B76" s="232" t="s">
         <v>228</v>
       </c>
-      <c r="C76" s="61">
+      <c r="C76" s="230">
         <v>2</v>
       </c>
-      <c r="D76" s="78" t="s">
+      <c r="D76" s="233" t="s">
         <v>229</v>
       </c>
-      <c r="E76" s="78"/>
+      <c r="E76" s="233"/>
       <c r="F76" s="79">
         <v>6.4000000000000003E-3</v>
       </c>
@@ -8900,132 +8938,132 @@
       <c r="E93" s="50"/>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D94" s="201" t="s">
+      <c r="D94" s="209" t="s">
         <v>273</v>
       </c>
-      <c r="E94" s="201"/>
-      <c r="F94" s="201"/>
-      <c r="G94" s="201"/>
-      <c r="H94" s="201"/>
-      <c r="I94" s="201"/>
-      <c r="J94" s="201"/>
-      <c r="K94" s="201"/>
-      <c r="L94" s="201"/>
-      <c r="M94" s="201"/>
-      <c r="N94" s="201"/>
-      <c r="O94" s="201"/>
-      <c r="P94" s="201"/>
+      <c r="E94" s="209"/>
+      <c r="F94" s="209"/>
+      <c r="G94" s="209"/>
+      <c r="H94" s="209"/>
+      <c r="I94" s="209"/>
+      <c r="J94" s="209"/>
+      <c r="K94" s="209"/>
+      <c r="L94" s="209"/>
+      <c r="M94" s="209"/>
+      <c r="N94" s="209"/>
+      <c r="O94" s="209"/>
+      <c r="P94" s="209"/>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D95" s="201"/>
-      <c r="E95" s="201"/>
-      <c r="F95" s="201"/>
-      <c r="G95" s="201"/>
-      <c r="H95" s="201"/>
-      <c r="I95" s="201"/>
-      <c r="J95" s="201"/>
-      <c r="K95" s="201"/>
-      <c r="L95" s="201"/>
-      <c r="M95" s="201"/>
-      <c r="N95" s="201"/>
-      <c r="O95" s="201"/>
-      <c r="P95" s="201"/>
+      <c r="D95" s="209"/>
+      <c r="E95" s="209"/>
+      <c r="F95" s="209"/>
+      <c r="G95" s="209"/>
+      <c r="H95" s="209"/>
+      <c r="I95" s="209"/>
+      <c r="J95" s="209"/>
+      <c r="K95" s="209"/>
+      <c r="L95" s="209"/>
+      <c r="M95" s="209"/>
+      <c r="N95" s="209"/>
+      <c r="O95" s="209"/>
+      <c r="P95" s="209"/>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H96" s="119"/>
     </row>
     <row r="97" spans="4:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="186" t="str">
+      <c r="D97" s="194" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</v>
       </c>
-      <c r="E97" s="187"/>
-      <c r="F97" s="187"/>
-      <c r="G97" s="187"/>
-      <c r="H97" s="187"/>
-      <c r="I97" s="187"/>
-      <c r="J97" s="187"/>
-      <c r="K97" s="187"/>
-      <c r="L97" s="187"/>
-      <c r="M97" s="187"/>
-      <c r="N97" s="187"/>
-      <c r="O97" s="187"/>
-      <c r="P97" s="187"/>
+      <c r="E97" s="195"/>
+      <c r="F97" s="195"/>
+      <c r="G97" s="195"/>
+      <c r="H97" s="195"/>
+      <c r="I97" s="195"/>
+      <c r="J97" s="195"/>
+      <c r="K97" s="195"/>
+      <c r="L97" s="195"/>
+      <c r="M97" s="195"/>
+      <c r="N97" s="195"/>
+      <c r="O97" s="195"/>
+      <c r="P97" s="195"/>
     </row>
     <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="187"/>
-      <c r="E98" s="187"/>
-      <c r="F98" s="187"/>
-      <c r="G98" s="187"/>
-      <c r="H98" s="187"/>
-      <c r="I98" s="187"/>
-      <c r="J98" s="187"/>
-      <c r="K98" s="187"/>
-      <c r="L98" s="187"/>
-      <c r="M98" s="187"/>
-      <c r="N98" s="187"/>
-      <c r="O98" s="187"/>
-      <c r="P98" s="187"/>
+      <c r="D98" s="195"/>
+      <c r="E98" s="195"/>
+      <c r="F98" s="195"/>
+      <c r="G98" s="195"/>
+      <c r="H98" s="195"/>
+      <c r="I98" s="195"/>
+      <c r="J98" s="195"/>
+      <c r="K98" s="195"/>
+      <c r="L98" s="195"/>
+      <c r="M98" s="195"/>
+      <c r="N98" s="195"/>
+      <c r="O98" s="195"/>
+      <c r="P98" s="195"/>
     </row>
     <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="187"/>
-      <c r="E99" s="187"/>
-      <c r="F99" s="187"/>
-      <c r="G99" s="187"/>
-      <c r="H99" s="187"/>
-      <c r="I99" s="187"/>
-      <c r="J99" s="187"/>
-      <c r="K99" s="187"/>
-      <c r="L99" s="187"/>
-      <c r="M99" s="187"/>
-      <c r="N99" s="187"/>
-      <c r="O99" s="187"/>
-      <c r="P99" s="187"/>
+      <c r="D99" s="195"/>
+      <c r="E99" s="195"/>
+      <c r="F99" s="195"/>
+      <c r="G99" s="195"/>
+      <c r="H99" s="195"/>
+      <c r="I99" s="195"/>
+      <c r="J99" s="195"/>
+      <c r="K99" s="195"/>
+      <c r="L99" s="195"/>
+      <c r="M99" s="195"/>
+      <c r="N99" s="195"/>
+      <c r="O99" s="195"/>
+      <c r="P99" s="195"/>
     </row>
     <row r="100" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D100" s="187"/>
-      <c r="E100" s="187"/>
-      <c r="F100" s="187"/>
-      <c r="G100" s="187"/>
-      <c r="H100" s="187"/>
-      <c r="I100" s="187"/>
-      <c r="J100" s="187"/>
-      <c r="K100" s="187"/>
-      <c r="L100" s="187"/>
-      <c r="M100" s="187"/>
-      <c r="N100" s="187"/>
-      <c r="O100" s="187"/>
-      <c r="P100" s="187"/>
+      <c r="D100" s="195"/>
+      <c r="E100" s="195"/>
+      <c r="F100" s="195"/>
+      <c r="G100" s="195"/>
+      <c r="H100" s="195"/>
+      <c r="I100" s="195"/>
+      <c r="J100" s="195"/>
+      <c r="K100" s="195"/>
+      <c r="L100" s="195"/>
+      <c r="M100" s="195"/>
+      <c r="N100" s="195"/>
+      <c r="O100" s="195"/>
+      <c r="P100" s="195"/>
     </row>
     <row r="101" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D101" s="187"/>
-      <c r="E101" s="187"/>
-      <c r="F101" s="187"/>
-      <c r="G101" s="187"/>
-      <c r="H101" s="187"/>
-      <c r="I101" s="187"/>
-      <c r="J101" s="187"/>
-      <c r="K101" s="187"/>
-      <c r="L101" s="187"/>
-      <c r="M101" s="187"/>
-      <c r="N101" s="187"/>
-      <c r="O101" s="187"/>
-      <c r="P101" s="187"/>
+      <c r="D101" s="195"/>
+      <c r="E101" s="195"/>
+      <c r="F101" s="195"/>
+      <c r="G101" s="195"/>
+      <c r="H101" s="195"/>
+      <c r="I101" s="195"/>
+      <c r="J101" s="195"/>
+      <c r="K101" s="195"/>
+      <c r="L101" s="195"/>
+      <c r="M101" s="195"/>
+      <c r="N101" s="195"/>
+      <c r="O101" s="195"/>
+      <c r="P101" s="195"/>
     </row>
     <row r="102" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="187"/>
-      <c r="E102" s="187"/>
-      <c r="F102" s="187"/>
-      <c r="G102" s="187"/>
-      <c r="H102" s="187"/>
-      <c r="I102" s="187"/>
-      <c r="J102" s="187"/>
-      <c r="K102" s="187"/>
-      <c r="L102" s="187"/>
-      <c r="M102" s="187"/>
-      <c r="N102" s="187"/>
-      <c r="O102" s="187"/>
-      <c r="P102" s="187"/>
+      <c r="D102" s="195"/>
+      <c r="E102" s="195"/>
+      <c r="F102" s="195"/>
+      <c r="G102" s="195"/>
+      <c r="H102" s="195"/>
+      <c r="I102" s="195"/>
+      <c r="J102" s="195"/>
+      <c r="K102" s="195"/>
+      <c r="L102" s="195"/>
+      <c r="M102" s="195"/>
+      <c r="N102" s="195"/>
+      <c r="O102" s="195"/>
+      <c r="P102" s="195"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -9061,49 +9099,65 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8AEA40-856C-4C69-BDF8-B1FFAA30BA95}">
-  <dimension ref="D3:G21"/>
+  <dimension ref="D3:I21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D3" s="119"/>
     </row>
-    <row r="4" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D4" s="119"/>
     </row>
-    <row r="5" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D5" s="119"/>
     </row>
-    <row r="6" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D6" s="119"/>
     </row>
-    <row r="7" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D7" s="119"/>
     </row>
-    <row r="8" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D8" s="225" t="s">
+    <row r="8" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D8" s="190" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="9" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D9" s="119"/>
     </row>
-    <row r="10" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D10" s="119"/>
     </row>
-    <row r="11" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D11" s="119"/>
-    </row>
-    <row r="12" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="193" t="s">
+        <v>275</v>
+      </c>
+      <c r="E11" s="193"/>
+      <c r="F11" s="193"/>
+      <c r="G11" s="229" t="s">
+        <v>276</v>
+      </c>
+      <c r="H11" s="229"/>
+      <c r="I11" s="229"/>
+    </row>
+    <row r="12" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D12" s="119"/>
     </row>
-    <row r="13" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D13" s="119"/>
     </row>
-    <row r="14" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D14" s="119"/>
     </row>
-    <row r="15" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D15" s="119"/>
+    <row r="15" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D15" s="234" t="s">
+        <v>277</v>
+      </c>
+      <c r="E15" s="234"/>
+      <c r="F15" s="234"/>
+      <c r="G15" s="234"/>
+      <c r="H15" s="234"/>
+      <c r="I15" s="234"/>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="119"/>
@@ -9115,6 +9169,9 @@
       <c r="G21" s="119"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G11:I11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/VERGARA/Agosto/vergara Agosto.xlsx
+++ b/VERGARA/Agosto/vergara Agosto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E06FAA7-2937-4909-9D08-761D09A317D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6200223E-875A-4425-92DC-23A35D930DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$Q$103</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="283">
   <si>
     <t>MAIL: consorciovergara1670@gmail.com</t>
   </si>
@@ -795,18 +795,6 @@
     <t>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</t>
   </si>
   <si>
-    <t>PERÍODO: JULIO - ADMINISTRADORA: CAROLINA CANCIANI MP:1148</t>
-  </si>
-  <si>
-    <t>Marcela De Biase-  Sra. Contadora - Mes de JULIO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de JULIO</t>
-  </si>
-  <si>
-    <t>Honorarios administracion - Mes de JUNIO Y JULIO</t>
-  </si>
-  <si>
     <t>Transf 17/07</t>
   </si>
   <si>
@@ -819,9 +807,6 @@
     <t>Casa ruan - compra de materiales</t>
   </si>
   <si>
-    <t>VTO 18/08</t>
-  </si>
-  <si>
     <t>Debito 03/07</t>
   </si>
   <si>
@@ -831,13 +816,7 @@
     <t>Transf 28/07</t>
   </si>
   <si>
-    <t>Transf 14/07</t>
-  </si>
-  <si>
     <t>Servisur - Mano de obra y materiales cambio de lamparas y plafones</t>
-  </si>
-  <si>
-    <t>NOS QUEDO PENDIENTE PARA SEPTIEMBR3 UN GASTO DE 125MIL QUE NO SUPIMOS IDENTIFICA</t>
   </si>
   <si>
     <t>No se abono</t>
@@ -865,6 +844,42 @@
   </si>
   <si>
     <t>SE QUEJA POR MAIL DE DEUDA INEXISTENTE Y ADJUNTA COMPROBANTES</t>
+  </si>
+  <si>
+    <t>VTO 15/09</t>
+  </si>
+  <si>
+    <t>PERÍODO: AGOSTO - ADMINISTRADORA: CAROLINA CANCIANI MP:1148</t>
+  </si>
+  <si>
+    <t>Marcela De Biase-  Sra. Contadora - Mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Mes de JULIO Y AGOSTO</t>
+  </si>
+  <si>
+    <t>NOS QUEDO PENDIENTE PARA AG0ST0+ UN GASTO DE 125MIL QUE NO SUPIMOS IDENTIFICA</t>
+  </si>
+  <si>
+    <t>Transf 22/08</t>
+  </si>
+  <si>
+    <t>Roxana goldemberg - carta decomento galpon</t>
+  </si>
+  <si>
+    <t>Salvatierra matias - Desobstruccion y limpieza de todas las rejillas de desagote de pluvial y de ducha en terraza frente y contrafrente</t>
+  </si>
+  <si>
+    <t>Transf 19/08</t>
+  </si>
+  <si>
+    <t>Transf 12/08</t>
+  </si>
+  <si>
+    <t>Santillan Anotnio Javer - Verificacion</t>
   </si>
 </sst>
 </file>
@@ -872,15 +887,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -1524,10 +1539,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1547,8 +1562,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1557,31 +1572,31 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1592,8 +1607,8 @@
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1608,18 +1623,18 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1637,35 +1652,35 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1673,11 +1688,11 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1688,14 +1703,14 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1711,58 +1726,57 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1771,13 +1785,12 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1791,9 +1804,8 @@
     <xf numFmtId="2" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1801,21 +1813,46 @@
     <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1829,78 +1866,68 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2261,21 +2288,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M99"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="65" t="s">
         <v>0</v>
@@ -2284,7 +2311,7 @@
       <c r="D1" s="65"/>
       <c r="E1" s="66"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="128" t="s">
         <v>1</v>
@@ -2293,7 +2320,7 @@
       <c r="D2" s="128"/>
       <c r="E2" s="67"/>
     </row>
-    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
       <c r="B3" s="129" t="s">
         <v>2</v>
@@ -2304,7 +2331,7 @@
       </c>
       <c r="E3" s="67"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -2315,18 +2342,18 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="205" t="s">
-        <v>255</v>
-      </c>
-      <c r="C5" s="203"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="204"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="198" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="199"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="200"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -2337,57 +2364,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="206" t="s">
-        <v>263</v>
-      </c>
-      <c r="C8" s="195"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="195"/>
-      <c r="C9" s="195"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="195"/>
-      <c r="C10" s="195"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="207" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="201" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="202"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="202"/>
+      <c r="C9" s="202"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="202"/>
+      <c r="C10" s="202"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="203" t="s">
         <v>254</v>
       </c>
-      <c r="B13" s="208"/>
-      <c r="C13" s="208"/>
-      <c r="D13" s="208"/>
-      <c r="E13" s="208"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="208"/>
-      <c r="B14" s="208"/>
-      <c r="C14" s="208"/>
-      <c r="D14" s="208"/>
-      <c r="E14" s="208"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="208"/>
-      <c r="B15" s="208"/>
-      <c r="C15" s="208"/>
-      <c r="D15" s="208"/>
-      <c r="E15" s="208"/>
-    </row>
-    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="208"/>
-      <c r="B16" s="208"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="208"/>
-      <c r="E16" s="208"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="204"/>
+      <c r="C13" s="204"/>
+      <c r="D13" s="204"/>
+      <c r="E13" s="204"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="204"/>
+      <c r="B14" s="204"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="204"/>
+      <c r="B15" s="204"/>
+      <c r="C15" s="204"/>
+      <c r="D15" s="204"/>
+      <c r="E15" s="204"/>
+    </row>
+    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="204"/>
+      <c r="B16" s="204"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="204"/>
+      <c r="E16" s="204"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2396,7 +2423,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
         <v>10</v>
       </c>
@@ -2405,42 +2432,42 @@
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="184">
+      <c r="D22" s="182">
         <v>612874.4</v>
       </c>
       <c r="E22" s="85"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="184">
+      <c r="D23" s="182">
         <v>-143013.39000000001</v>
       </c>
       <c r="E23" s="85"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="184">
+      <c r="D24" s="182">
         <v>0.99</v>
       </c>
       <c r="E24" s="85"/>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="55" t="s">
         <v>14</v>
       </c>
@@ -2453,7 +2480,7 @@
       <c r="E25" s="86"/>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
         <v>15</v>
       </c>
@@ -2466,7 +2493,7 @@
       </c>
       <c r="F26" s="19"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="32" t="s">
         <v>16</v>
       </c>
@@ -2475,26 +2502,26 @@
       <c r="D27" s="33"/>
       <c r="E27" s="88"/>
     </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="196" t="s">
-        <v>256</v>
-      </c>
-      <c r="B28" s="197"/>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="205" t="s">
+        <v>273</v>
+      </c>
+      <c r="B28" s="206"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="184">
+      <c r="D28" s="238">
         <v>35000</v>
       </c>
       <c r="E28" s="89" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="196" t="s">
-        <v>258</v>
-      </c>
-      <c r="B29" s="197"/>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="205" t="s">
+        <v>275</v>
+      </c>
+      <c r="B29" s="206"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="184">
+      <c r="D29" s="182">
         <f>470000</f>
         <v>470000</v>
       </c>
@@ -2502,7 +2529,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
         <v>17</v>
       </c>
@@ -2514,7 +2541,7 @@
         <v>505000</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="30" t="s">
         <v>18</v>
       </c>
@@ -2523,30 +2550,30 @@
       <c r="D31" s="34"/>
       <c r="E31" s="64"/>
     </row>
-    <row r="32" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="148" t="s">
+    <row r="32" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="147" t="s">
         <v>19</v>
       </c>
       <c r="B32" s="144"/>
       <c r="C32" s="53"/>
-      <c r="D32" s="174">
+      <c r="D32" s="173">
         <v>70868</v>
       </c>
       <c r="E32" s="112"/>
-      <c r="G32" s="147"/>
-    </row>
-    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="196" t="s">
+      <c r="G32" s="146"/>
+    </row>
+    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="205" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="197"/>
+      <c r="B33" s="206"/>
       <c r="C33" s="53"/>
-      <c r="D33" s="173">
+      <c r="D33" s="172">
         <v>719.9</v>
       </c>
       <c r="E33" s="112"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="25" t="s">
         <v>21</v>
       </c>
@@ -2558,7 +2585,7 @@
         <v>71587.899999999994</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="32" t="s">
         <v>22</v>
       </c>
@@ -2567,70 +2594,70 @@
       <c r="D35" s="37"/>
       <c r="E35" s="92"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="52"/>
-      <c r="D36" s="185">
-        <v>466260.75</v>
+      <c r="D36" s="136">
+        <v>305360.62</v>
       </c>
       <c r="E36" s="114" t="s">
         <v>251</v>
       </c>
       <c r="G36" s="119"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="5"/>
-      <c r="D37" s="173">
-        <v>45243</v>
+      <c r="D37" s="232">
+        <v>27579.35</v>
       </c>
       <c r="E37" s="100" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="str">
         <f>A37</f>
-        <v>Sindicatos mes de JULIO</v>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C38" s="5"/>
-      <c r="D38" s="173">
-        <v>83582.350000000006</v>
+      <c r="D38" s="232">
+        <v>52150.84</v>
       </c>
       <c r="E38" s="100" t="str">
         <f>E37</f>
         <v>Debito 16/07</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="str">
         <f>A38</f>
-        <v>Sindicatos mes de JULIO</v>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C39" s="5"/>
-      <c r="D39" s="173">
-        <v>5027</v>
+      <c r="D39" s="232">
+        <v>3064.37</v>
       </c>
       <c r="E39" s="101" t="str">
         <f>E37</f>
         <v>Debito 16/07</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="25" t="s">
         <v>27</v>
       </c>
@@ -2639,10 +2666,10 @@
       <c r="D40" s="38"/>
       <c r="E40" s="91">
         <f>SUM(D36:D39)</f>
-        <v>600113.1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>388155.17999999993</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="32" t="s">
         <v>28</v>
       </c>
@@ -2651,44 +2678,44 @@
       <c r="D41" s="37"/>
       <c r="E41" s="92"/>
     </row>
-    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B42" s="52"/>
       <c r="C42" s="52"/>
-      <c r="D42" s="173">
+      <c r="D42" s="172">
         <v>1397945.13</v>
       </c>
       <c r="E42" s="98" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="173" t="s">
-        <v>270</v>
+      <c r="D43" s="172" t="s">
+        <v>263</v>
       </c>
       <c r="E43" s="98"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="196" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="205" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="197"/>
+      <c r="B44" s="206"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="173">
+      <c r="D44" s="172">
         <v>88711.15</v>
       </c>
       <c r="E44" s="98" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="25" t="s">
         <v>32</v>
       </c>
@@ -2700,7 +2727,7 @@
         <v>1486656.2799999998</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="32" t="s">
         <v>33</v>
       </c>
@@ -2709,459 +2736,514 @@
       <c r="D46" s="36"/>
       <c r="E46" s="94"/>
     </row>
-    <row r="47" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="196" t="s">
-        <v>268</v>
-      </c>
-      <c r="B47" s="197"/>
+    <row r="47" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="205" t="s">
+        <v>262</v>
+      </c>
+      <c r="B47" s="206"/>
       <c r="C47" s="54"/>
-      <c r="D47" s="173">
+      <c r="D47" s="172">
         <v>76500</v>
       </c>
       <c r="E47" s="145" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="196" t="s">
-        <v>262</v>
-      </c>
-      <c r="B48" s="197"/>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="205" t="s">
+        <v>258</v>
+      </c>
+      <c r="B48" s="206"/>
       <c r="C48" s="54"/>
-      <c r="D48" s="173">
+      <c r="D48" s="172">
         <v>16500</v>
       </c>
-      <c r="E48" s="146" t="s">
-        <v>261</v>
+      <c r="E48" s="233" t="s">
+        <v>257</v>
       </c>
       <c r="H48" s="142" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="198" t="s">
-        <v>260</v>
-      </c>
-      <c r="B49" s="199"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="173">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="191"/>
+      <c r="B49" s="192"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="232">
+        <v>19000</v>
+      </c>
+      <c r="E49" s="233" t="s">
+        <v>277</v>
+      </c>
+      <c r="H49" s="119"/>
+    </row>
+    <row r="50" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="191" t="s">
+        <v>278</v>
+      </c>
+      <c r="B50" s="192"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="232">
+        <v>74376</v>
+      </c>
+      <c r="E50" s="233" t="s">
+        <v>277</v>
+      </c>
+      <c r="H50" s="119"/>
+    </row>
+    <row r="51" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="234" t="s">
+        <v>279</v>
+      </c>
+      <c r="B51" s="235"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="232">
+        <v>144600</v>
+      </c>
+      <c r="E51" s="233" t="s">
+        <v>280</v>
+      </c>
+      <c r="H51" s="119"/>
+    </row>
+    <row r="52" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="95" t="s">
+        <v>282</v>
+      </c>
+      <c r="B52" s="144"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="232">
+        <v>120000</v>
+      </c>
+      <c r="E52" s="233" t="s">
+        <v>281</v>
+      </c>
+      <c r="H52" s="119"/>
+    </row>
+    <row r="53" spans="1:10" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="208" t="s">
+        <v>256</v>
+      </c>
+      <c r="B53" s="209"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="172">
         <v>60000</v>
       </c>
-      <c r="E49" s="146" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="196" t="s">
+      <c r="E53" s="233" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="205" t="s">
         <v>248</v>
       </c>
-      <c r="B50" s="197"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="96">
+      <c r="B54" s="206"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="96">
         <f>60650+58080</f>
         <v>118730</v>
       </c>
-      <c r="E50" s="177" t="s">
-        <v>259</v>
-      </c>
-      <c r="I50" s="196"/>
-      <c r="J50" s="197"/>
-    </row>
-    <row r="51" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="25" t="s">
+      <c r="E54" s="145" t="s">
+        <v>255</v>
+      </c>
+      <c r="I54" s="205"/>
+      <c r="J54" s="206"/>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B51" s="32"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="143">
-        <f>SUM(D47:D50)</f>
-        <v>271730</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="32" t="s">
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="143">
+        <f>SUM(D47:D54)</f>
+        <v>629706</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="B52" s="63"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="94"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="B56" s="63"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="94"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="173">
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="172">
         <v>107565.66</v>
       </c>
-      <c r="E53" s="102"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+      <c r="E57" s="102"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="173">
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="172">
         <v>49082</v>
       </c>
-      <c r="E54" s="99"/>
-    </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="51" t="s">
+      <c r="E58" s="99"/>
+    </row>
+    <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B55" s="51"/>
-      <c r="C55" s="51"/>
-      <c r="D55" s="103"/>
-      <c r="E55" s="91">
-        <f>SUM(D53:D54)</f>
+      <c r="B59" s="51"/>
+      <c r="C59" s="51"/>
+      <c r="D59" s="103"/>
+      <c r="E59" s="91">
+        <f>SUM(D57:D58)</f>
         <v>156647.66</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="85"/>
-      <c r="E56" s="104"/>
-    </row>
-    <row r="57" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="28" t="s">
+    <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="85"/>
+      <c r="E60" s="104"/>
+    </row>
+    <row r="61" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
-      <c r="D57" s="105"/>
-      <c r="E57" s="134"/>
-    </row>
-    <row r="58" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="1"/>
-      <c r="D58" s="106"/>
-      <c r="E58" s="107"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="139"/>
-    </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="105"/>
+      <c r="E61" s="134"/>
+    </row>
+    <row r="62" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="1"/>
+      <c r="D62" s="106"/>
+      <c r="E62" s="107"/>
+      <c r="F62" s="44"/>
+      <c r="G62" s="139"/>
+    </row>
+    <row r="63" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="108"/>
-      <c r="E59" s="133">
-        <f>(SUM(E26:E57))</f>
-        <v>3561596.94</v>
-      </c>
-      <c r="F59" s="132"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-    </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D61" s="106"/>
-      <c r="E61" s="106"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
+      <c r="B63" s="9"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="108"/>
+      <c r="E63" s="133">
+        <f>(SUM(E26:E61))</f>
+        <v>3707615.02</v>
+      </c>
+      <c r="F63" s="132"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D64" s="106"/>
+      <c r="E64" s="106"/>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D65" s="106"/>
+      <c r="E65" s="106"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B62" s="11"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="109"/>
-      <c r="E62" s="110"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="198"/>
-      <c r="B63" s="200"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="96"/>
-      <c r="E63" s="93"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="95"/>
-      <c r="B64" s="97"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="96"/>
-      <c r="E64" s="93"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="49"/>
-      <c r="B65" s="48"/>
-      <c r="C65" s="48"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56">
-        <f>SUM(D63:D64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="67" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="202" t="s">
+      <c r="B66" s="11"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="109"/>
+      <c r="E66" s="110"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="208"/>
+      <c r="B67" s="210"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="96"/>
+      <c r="E67" s="93"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="95"/>
+      <c r="B68" s="97"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="96"/>
+      <c r="E68" s="93"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="49"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="56">
+        <f>SUM(D67:D68)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="212" t="s">
         <v>41</v>
       </c>
-      <c r="B68" s="203"/>
-      <c r="C68" s="203"/>
-      <c r="D68" s="204"/>
-      <c r="E68" s="140"/>
-    </row>
-    <row r="69" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="70" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
+      <c r="B72" s="199"/>
+      <c r="C72" s="199"/>
+      <c r="D72" s="200"/>
+      <c r="E72" s="140"/>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B70" s="9"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="141">
-        <f>E65+E68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="72" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="82" t="s">
+      <c r="B74" s="9"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="141">
+        <f>E69+E72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="B72" s="83">
-        <f>E59</f>
-        <v>3561596.94</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="82" t="s">
+      <c r="B76" s="83">
+        <f>E63</f>
+        <v>3707615.02</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="B73" s="83">
-        <f>E59-E57</f>
-        <v>3561596.94</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="82" t="s">
+      <c r="B77" s="83">
+        <f>E63-E61</f>
+        <v>3707615.02</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="B74" s="83">
-        <f>E70-E68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="82" t="s">
+      <c r="B78" s="83">
+        <f>E74-E72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B75" s="83">
-        <f>E70</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="45" t="s">
+      <c r="B79" s="83">
+        <f>E74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="B77" s="120"/>
-      <c r="C77" s="20"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="29" t="s">
+      <c r="B81" s="120"/>
+      <c r="C81" s="20"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B78" s="57">
+      <c r="B82" s="57">
         <v>831778.51</v>
       </c>
-      <c r="C78" s="22"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="21" t="s">
+      <c r="C82" s="22"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B79" s="41">
+      <c r="B83" s="41">
         <f>PRORRATEO!H92</f>
         <v>6886831.2500000009</v>
       </c>
-      <c r="C79" s="20"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="21" t="s">
+      <c r="C83" s="20"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B80" s="99">
-        <f>B94</f>
-        <v>0</v>
-      </c>
-      <c r="C80" s="20"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="115" t="s">
+      <c r="B84" s="99">
+        <f>B98</f>
+        <v>0</v>
+      </c>
+      <c r="C84" s="20"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="B81" s="47">
+      <c r="B85" s="47">
         <f>-21080</f>
         <v>-21080</v>
       </c>
-      <c r="C81" s="20"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="40" t="s">
+      <c r="C85" s="20"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="B82" s="47">
-        <f>-B73</f>
-        <v>-3561596.94</v>
-      </c>
-      <c r="C82" s="20"/>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="40" t="s">
+      <c r="B86" s="47">
+        <f>-B77</f>
+        <v>-3707615.02</v>
+      </c>
+      <c r="C86" s="20"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B83" s="47">
+      <c r="B87" s="47">
         <f>-PRORRATEO!F1</f>
-        <v>-2147076</v>
-      </c>
-      <c r="C83" s="20"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="40" t="s">
+        <v>-2261553.86</v>
+      </c>
+      <c r="C87" s="20"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B84" s="47">
+      <c r="B88" s="47">
         <f>-PRORRATEO!F2</f>
-        <v>-770367.15</v>
-      </c>
-      <c r="C84" s="20"/>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="24" t="s">
+        <v>-768768.48</v>
+      </c>
+      <c r="C88" s="20"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B85" s="47">
-        <f>-(B74)</f>
-        <v>0</v>
-      </c>
-      <c r="C85" s="20"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="123" t="s">
+      <c r="B89" s="47">
+        <f>-(B78)</f>
+        <v>0</v>
+      </c>
+      <c r="C89" s="20"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="B86" s="124">
-        <f>SUM(B78:B85)</f>
-        <v>1218489.6700000009</v>
-      </c>
-      <c r="C86" s="23"/>
-      <c r="D86" s="44"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B87" s="42"/>
-      <c r="C87" s="23"/>
-      <c r="D87" s="44"/>
-      <c r="E87" s="121"/>
-      <c r="F87" s="122"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B88" s="42"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="44"/>
-      <c r="E88" s="121"/>
-      <c r="F88" s="122"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="201" t="s">
+      <c r="B90" s="124">
+        <f>SUM(B82:B89)</f>
+        <v>959592.40000000084</v>
+      </c>
+      <c r="C90" s="23"/>
+      <c r="D90" s="44"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B91" s="42"/>
+      <c r="C91" s="23"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="121"/>
+      <c r="F91" s="122"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B92" s="42"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="121"/>
+      <c r="F92" s="122"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="211" t="s">
         <v>56</v>
       </c>
-      <c r="B89" s="195"/>
-      <c r="C89" s="195"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="195"/>
-      <c r="B90" s="195"/>
-      <c r="C90" s="195"/>
-    </row>
-    <row r="91" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="53"/>
-      <c r="B91" s="136"/>
-      <c r="C91" s="35">
+      <c r="B93" s="202"/>
+      <c r="C93" s="202"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="202"/>
+      <c r="B94" s="202"/>
+      <c r="C94" s="202"/>
+    </row>
+    <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="53"/>
+      <c r="B95" s="136"/>
+      <c r="C95" s="35">
         <v>11948.17</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="53"/>
-      <c r="B92" s="35"/>
-      <c r="C92" s="35"/>
-    </row>
-    <row r="93" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="126"/>
-      <c r="B93" s="35"/>
-      <c r="C93" s="35">
+    <row r="96" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="53"/>
+      <c r="B96" s="35"/>
+      <c r="C96" s="35"/>
+    </row>
+    <row r="97" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="126"/>
+      <c r="B97" s="35"/>
+      <c r="C97" s="35">
         <v>61209</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" s="45" t="s">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="B94" s="111">
-        <f>SUM(B91:B93)</f>
-        <v>0</v>
-      </c>
-      <c r="C94" s="46"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M95" s="7"/>
-    </row>
-    <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="194"/>
-      <c r="B96" s="195"/>
-      <c r="C96" s="195"/>
-      <c r="D96" s="195"/>
-      <c r="E96" s="195"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="195"/>
-      <c r="B97" s="195"/>
-      <c r="C97" s="195"/>
-      <c r="D97" s="195"/>
-      <c r="E97" s="195"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="195"/>
-      <c r="B98" s="195"/>
-      <c r="C98" s="195"/>
-      <c r="D98" s="195"/>
-      <c r="E98" s="195"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="195"/>
-      <c r="B99" s="195"/>
-      <c r="C99" s="195"/>
-      <c r="D99" s="195"/>
-      <c r="E99" s="195"/>
+      <c r="B98" s="111">
+        <f>SUM(B95:B97)</f>
+        <v>0</v>
+      </c>
+      <c r="C98" s="46"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M99" s="7"/>
+    </row>
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="207"/>
+      <c r="B100" s="202"/>
+      <c r="C100" s="202"/>
+      <c r="D100" s="202"/>
+      <c r="E100" s="202"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101" s="202"/>
+      <c r="B101" s="202"/>
+      <c r="C101" s="202"/>
+      <c r="D101" s="202"/>
+      <c r="E101" s="202"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="202"/>
+      <c r="B102" s="202"/>
+      <c r="C102" s="202"/>
+      <c r="D102" s="202"/>
+      <c r="E102" s="202"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103" s="202"/>
+      <c r="B103" s="202"/>
+      <c r="C103" s="202"/>
+      <c r="D103" s="202"/>
+      <c r="E103" s="202"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="A100:E103"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A93:C94"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A96:E99"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A89:C90"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A50:B50"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3172,27 +3254,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T102"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="11.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" customWidth="1"/>
-    <col min="18" max="18" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="11" width="9.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="11.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" customWidth="1"/>
+    <col min="17" max="17" width="14.33203125" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3200,30 +3282,30 @@
       <c r="E1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="222">
-        <v>2147076</v>
-      </c>
-      <c r="G1" s="220"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="176" t="s">
+      <c r="F1" s="236">
+        <v>2261553.86</v>
+      </c>
+      <c r="G1" s="237"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="175" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="175"/>
-      <c r="M1" s="219">
+      <c r="L1" s="174"/>
+      <c r="M1" s="214">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="220"/>
+      <c r="N1" s="215"/>
       <c r="O1" s="135"/>
-      <c r="P1" s="218">
+      <c r="P1" s="213">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="195"/>
+      <c r="Q1" s="202"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3231,101 +3313,101 @@
       <c r="E2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="210">
-        <v>770367.15</v>
-      </c>
-      <c r="G2" s="211"/>
-      <c r="H2" s="175" t="s">
+      <c r="F2" s="239">
+        <v>768768.48</v>
+      </c>
+      <c r="G2" s="240"/>
+      <c r="H2" s="174" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="221"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="175" t="s">
+      <c r="I2" s="216"/>
+      <c r="J2" s="217"/>
+      <c r="K2" s="174" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="175"/>
-      <c r="M2" s="221"/>
-      <c r="N2" s="211"/>
+      <c r="L2" s="174"/>
+      <c r="M2" s="216"/>
+      <c r="N2" s="217"/>
       <c r="O2" s="137"/>
-      <c r="P2" s="226"/>
-      <c r="Q2" s="227"/>
-    </row>
-    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="223" t="s">
+      <c r="P2" s="223"/>
+      <c r="Q2" s="224"/>
+    </row>
+    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="218" t="s">
         <v>62</v>
       </c>
       <c r="B3" s="116"/>
-      <c r="C3" s="212" t="s">
+      <c r="C3" s="225" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="212" t="s">
+      <c r="D3" s="225" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="217" t="s">
+      <c r="E3" s="230" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="212" t="s">
+      <c r="F3" s="225" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="214" t="s">
+      <c r="G3" s="220" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="212" t="s">
+      <c r="H3" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="225" t="s">
+      <c r="I3" s="222" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="214" t="s">
+      <c r="J3" s="220" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="216" t="str">
+      <c r="K3" s="229" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="214" t="s">
+      <c r="L3" s="220" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="214" t="s">
+      <c r="M3" s="220" t="s">
         <v>71</v>
       </c>
-      <c r="N3" s="214" t="s">
+      <c r="N3" s="220" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="214" t="s">
+      <c r="O3" s="220" t="s">
         <v>73</v>
       </c>
       <c r="P3" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="Q3" s="228" t="s">
+      <c r="Q3" s="227" t="s">
         <v>75</v>
       </c>
       <c r="T3" s="44"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="224"/>
+    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="219"/>
       <c r="B4" s="117"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="215"/>
-      <c r="F4" s="213"/>
-      <c r="G4" s="215"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="215"/>
-      <c r="J4" s="215"/>
-      <c r="K4" s="213"/>
-      <c r="L4" s="215"/>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
+      <c r="C4" s="226"/>
+      <c r="D4" s="226"/>
+      <c r="E4" s="221"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="221"/>
+      <c r="H4" s="226"/>
+      <c r="I4" s="221"/>
+      <c r="J4" s="221"/>
+      <c r="K4" s="226"/>
+      <c r="L4" s="221"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
       <c r="P4" s="58" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 18/08</v>
-      </c>
-      <c r="Q4" s="213"/>
-    </row>
-    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 15/09</v>
+      </c>
+      <c r="Q4" s="226"/>
+    </row>
+    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="61"/>
       <c r="B5" s="61" t="s">
         <v>76</v>
@@ -3365,11 +3447,11 @@
       </c>
       <c r="M5" s="125">
         <f t="shared" ref="M5:M36" si="4">F$1*F5</f>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N5" s="125">
         <f t="shared" ref="N5:N36" si="5">F$2*F5</f>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O5" s="125">
         <f t="shared" ref="O5:O36" si="6">I$2*F5</f>
@@ -3377,18 +3459,18 @@
       </c>
       <c r="P5" s="72">
         <f t="shared" ref="P5:P36" si="7">ROUND(SUM(I5:O5),0) + R5</f>
-        <v>131652.32999999999</v>
+        <v>133933.32999999999</v>
       </c>
       <c r="Q5" s="73">
         <f t="shared" ref="Q5:Q36" si="8">ROUND(P5*3%,0) + P5</f>
-        <v>135602.32999999999</v>
+        <v>137951.32999999999</v>
       </c>
       <c r="R5" s="44">
         <f t="shared" ref="R5:R36" si="9">ROUND(0.001+C5/100,2)</f>
         <v>0.33</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="61"/>
       <c r="B6" s="61" t="s">
         <v>78</v>
@@ -3428,11 +3510,11 @@
       </c>
       <c r="M6" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N6" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O6" s="125">
         <f t="shared" si="6"/>
@@ -3440,11 +3522,11 @@
       </c>
       <c r="P6" s="72">
         <f t="shared" si="7"/>
-        <v>90592.34</v>
+        <v>92161.34</v>
       </c>
       <c r="Q6" s="73">
         <f t="shared" si="8"/>
-        <v>93310.34</v>
+        <v>94926.34</v>
       </c>
       <c r="R6" s="44">
         <f t="shared" si="9"/>
@@ -3452,7 +3534,7 @@
       </c>
       <c r="S6" s="44"/>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="61">
         <v>1</v>
       </c>
@@ -3462,11 +3544,11 @@
       <c r="C7" s="61">
         <v>35</v>
       </c>
-      <c r="D7" s="178" t="s">
+      <c r="D7" s="176" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="181"/>
-      <c r="F7" s="179">
+      <c r="E7" s="179"/>
+      <c r="F7" s="177">
         <v>1.4200000000000001E-2</v>
       </c>
       <c r="G7" s="69">
@@ -3494,11 +3576,11 @@
       </c>
       <c r="M7" s="125">
         <f t="shared" si="4"/>
-        <v>30488.479200000002</v>
+        <v>32114.064812000001</v>
       </c>
       <c r="N7" s="125">
         <f t="shared" si="5"/>
-        <v>10939.213530000001</v>
+        <v>10916.512416</v>
       </c>
       <c r="O7" s="125">
         <f t="shared" si="6"/>
@@ -3506,18 +3588,18 @@
       </c>
       <c r="P7" s="72">
         <f t="shared" si="7"/>
-        <v>92548.35</v>
+        <v>94151.35</v>
       </c>
       <c r="Q7" s="73">
         <f t="shared" si="8"/>
-        <v>95324.35</v>
+        <v>96976.35</v>
       </c>
       <c r="R7" s="44">
         <f t="shared" si="9"/>
         <v>0.35</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="61">
         <v>2</v>
       </c>
@@ -3527,11 +3609,11 @@
       <c r="C8" s="61">
         <v>36</v>
       </c>
-      <c r="D8" s="178" t="s">
+      <c r="D8" s="176" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="181"/>
-      <c r="F8" s="179">
+      <c r="E8" s="179"/>
+      <c r="F8" s="177">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G8" s="69">
@@ -3559,11 +3641,11 @@
       </c>
       <c r="M8" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N8" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O8" s="125">
         <f t="shared" si="6"/>
@@ -3571,11 +3653,11 @@
       </c>
       <c r="P8" s="72">
         <f t="shared" si="7"/>
-        <v>127522.36</v>
+        <v>129802.36</v>
       </c>
       <c r="Q8" s="73">
         <f t="shared" si="8"/>
-        <v>131348.35999999999</v>
+        <v>133696.35999999999</v>
       </c>
       <c r="R8" s="44">
         <f t="shared" si="9"/>
@@ -3583,7 +3665,7 @@
       </c>
       <c r="T8" s="44"/>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="61">
         <v>3</v>
       </c>
@@ -3627,11 +3709,11 @@
       </c>
       <c r="M9" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N9" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O9" s="125">
         <f t="shared" si="6"/>
@@ -3639,11 +3721,11 @@
       </c>
       <c r="P9" s="72">
         <f t="shared" si="7"/>
-        <v>104026.37</v>
+        <v>106306.37</v>
       </c>
       <c r="Q9" s="73">
         <f t="shared" si="8"/>
-        <v>107147.37</v>
+        <v>109495.37</v>
       </c>
       <c r="R9" s="44">
         <f t="shared" si="9"/>
@@ -3651,7 +3733,7 @@
       </c>
       <c r="T9" s="44"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="61">
         <v>4</v>
       </c>
@@ -3695,11 +3777,11 @@
       </c>
       <c r="M10" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N10" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O10" s="125">
         <f t="shared" si="6"/>
@@ -3707,18 +3789,18 @@
       </c>
       <c r="P10" s="72">
         <f t="shared" si="7"/>
-        <v>90592.38</v>
+        <v>92161.38</v>
       </c>
       <c r="Q10" s="73">
         <f t="shared" si="8"/>
-        <v>93310.38</v>
+        <v>94926.38</v>
       </c>
       <c r="R10" s="44">
         <f t="shared" si="9"/>
         <v>0.38</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="61">
         <v>5</v>
       </c>
@@ -3759,11 +3841,11 @@
       </c>
       <c r="M11" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N11" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O11" s="125">
         <f t="shared" si="6"/>
@@ -3771,18 +3853,18 @@
       </c>
       <c r="P11" s="72">
         <f t="shared" si="7"/>
-        <v>90592.39</v>
+        <v>92161.39</v>
       </c>
       <c r="Q11" s="73">
         <f t="shared" si="8"/>
-        <v>93310.39</v>
+        <v>94926.39</v>
       </c>
       <c r="R11" s="44">
         <f t="shared" si="9"/>
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="61">
         <v>6</v>
       </c>
@@ -3821,11 +3903,11 @@
       </c>
       <c r="M12" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N12" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O12" s="125">
         <f t="shared" si="6"/>
@@ -3833,18 +3915,18 @@
       </c>
       <c r="P12" s="72">
         <f t="shared" si="7"/>
-        <v>281717.40000000002</v>
+        <v>283997.40000000002</v>
       </c>
       <c r="Q12" s="73">
         <f t="shared" si="8"/>
-        <v>290169.40000000002</v>
+        <v>292517.40000000002</v>
       </c>
       <c r="R12" s="44">
         <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="61">
         <v>7</v>
       </c>
@@ -3854,13 +3936,13 @@
       <c r="C13" s="61">
         <v>41</v>
       </c>
-      <c r="D13" s="178" t="s">
+      <c r="D13" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="181" t="s">
+      <c r="E13" s="179" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="179">
+      <c r="F13" s="177">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G13" s="69">
@@ -3887,11 +3969,11 @@
       </c>
       <c r="M13" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N13" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O13" s="125">
         <f t="shared" si="6"/>
@@ -3899,18 +3981,18 @@
       </c>
       <c r="P13" s="72">
         <f t="shared" si="7"/>
-        <v>204408.41</v>
+        <v>206688.41</v>
       </c>
       <c r="Q13" s="73">
         <f t="shared" si="8"/>
-        <v>210540.41</v>
+        <v>212889.41</v>
       </c>
       <c r="R13" s="44">
         <f t="shared" si="9"/>
         <v>0.41</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="61">
         <v>8</v>
       </c>
@@ -3954,11 +4036,11 @@
       </c>
       <c r="M14" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N14" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O14" s="125">
         <f t="shared" si="6"/>
@@ -3966,18 +4048,18 @@
       </c>
       <c r="P14" s="72">
         <f t="shared" si="7"/>
-        <v>90592.42</v>
+        <v>92161.42</v>
       </c>
       <c r="Q14" s="73">
         <f t="shared" si="8"/>
-        <v>93310.42</v>
+        <v>94926.42</v>
       </c>
       <c r="R14" s="44">
         <f t="shared" si="9"/>
         <v>0.42</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="61">
         <v>1</v>
       </c>
@@ -4021,11 +4103,11 @@
       </c>
       <c r="M15" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N15" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O15" s="125">
         <f t="shared" si="6"/>
@@ -4033,18 +4115,18 @@
       </c>
       <c r="P15" s="72">
         <f t="shared" si="7"/>
-        <v>90592.43</v>
+        <v>92161.43</v>
       </c>
       <c r="Q15" s="73">
         <f t="shared" si="8"/>
-        <v>93310.43</v>
+        <v>94926.43</v>
       </c>
       <c r="R15" s="44">
         <f t="shared" si="9"/>
         <v>0.43</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="61">
         <v>1</v>
       </c>
@@ -4054,16 +4136,16 @@
       <c r="C16" s="61">
         <v>44</v>
       </c>
-      <c r="D16" s="186" t="s">
+      <c r="D16" s="183" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="187" t="s">
+      <c r="E16" s="184" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="188">
+      <c r="F16" s="185">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G16" s="189">
+      <c r="G16" s="186">
         <v>145692.44</v>
       </c>
       <c r="H16" s="118"/>
@@ -4085,11 +4167,11 @@
       </c>
       <c r="M16" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N16" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O16" s="125">
         <f t="shared" si="6"/>
@@ -4097,18 +4179,18 @@
       </c>
       <c r="P16" s="72">
         <f t="shared" si="7"/>
-        <v>281716.44</v>
+        <v>283996.44</v>
       </c>
       <c r="Q16" s="73">
         <f t="shared" si="8"/>
-        <v>290167.44</v>
+        <v>292516.44</v>
       </c>
       <c r="R16" s="44">
         <f t="shared" si="9"/>
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="61">
         <v>2</v>
       </c>
@@ -4152,11 +4234,11 @@
       </c>
       <c r="M17" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N17" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O17" s="125">
         <f t="shared" si="6"/>
@@ -4164,18 +4246,18 @@
       </c>
       <c r="P17" s="72">
         <f t="shared" si="7"/>
-        <v>131652.45000000001</v>
+        <v>133933.45000000001</v>
       </c>
       <c r="Q17" s="73">
         <f t="shared" si="8"/>
-        <v>135602.45000000001</v>
+        <v>137951.45000000001</v>
       </c>
       <c r="R17" s="44">
         <f t="shared" si="9"/>
         <v>0.45</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="61">
         <v>2</v>
       </c>
@@ -4219,11 +4301,11 @@
       </c>
       <c r="M18" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N18" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O18" s="125">
         <f t="shared" si="6"/>
@@ -4231,11 +4313,11 @@
       </c>
       <c r="P18" s="72">
         <f t="shared" si="7"/>
-        <v>90592.46</v>
+        <v>92161.46</v>
       </c>
       <c r="Q18" s="73">
         <f t="shared" si="8"/>
-        <v>93310.46</v>
+        <v>94926.46</v>
       </c>
       <c r="R18" s="44">
         <f t="shared" si="9"/>
@@ -4243,7 +4325,7 @@
       </c>
       <c r="S18" s="119"/>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="61">
         <v>3</v>
       </c>
@@ -4257,7 +4339,7 @@
         <v>98</v>
       </c>
       <c r="E19" s="74" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F19" s="68">
         <v>1.3899999999999999E-2</v>
@@ -4287,11 +4369,11 @@
       </c>
       <c r="M19" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N19" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O19" s="125">
         <f t="shared" si="6"/>
@@ -4299,11 +4381,11 @@
       </c>
       <c r="P19" s="72">
         <f t="shared" si="7"/>
-        <v>90593.47</v>
+        <v>92162.47</v>
       </c>
       <c r="Q19" s="73">
         <f t="shared" si="8"/>
-        <v>93311.47</v>
+        <v>94927.47</v>
       </c>
       <c r="R19" s="44">
         <f t="shared" si="9"/>
@@ -4311,7 +4393,7 @@
       </c>
       <c r="S19" s="119"/>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="61">
         <v>3</v>
       </c>
@@ -4321,13 +4403,13 @@
       <c r="C20" s="61">
         <v>48</v>
       </c>
-      <c r="D20" s="191" t="s">
+      <c r="D20" s="188" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="191" t="s">
+      <c r="E20" s="188" t="s">
         <v>112</v>
       </c>
-      <c r="F20" s="192">
+      <c r="F20" s="189">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G20" s="69">
@@ -4355,11 +4437,11 @@
       </c>
       <c r="M20" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N20" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O20" s="125">
         <f t="shared" si="6"/>
@@ -4367,11 +4449,11 @@
       </c>
       <c r="P20" s="72">
         <f t="shared" si="7"/>
-        <v>131653.48000000001</v>
+        <v>133933.48000000001</v>
       </c>
       <c r="Q20" s="73">
         <f t="shared" si="8"/>
-        <v>135603.48000000001</v>
+        <v>137951.48000000001</v>
       </c>
       <c r="R20" s="44">
         <f t="shared" si="9"/>
@@ -4380,7 +4462,7 @@
       <c r="S20" s="119"/>
       <c r="T20" s="43"/>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="61">
         <v>4</v>
       </c>
@@ -4424,11 +4506,11 @@
       </c>
       <c r="M21" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N21" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O21" s="125">
         <f t="shared" si="6"/>
@@ -4436,18 +4518,18 @@
       </c>
       <c r="P21" s="72">
         <f t="shared" si="7"/>
-        <v>131652.49</v>
+        <v>133933.49</v>
       </c>
       <c r="Q21" s="73">
         <f t="shared" si="8"/>
-        <v>135602.49</v>
+        <v>137951.49</v>
       </c>
       <c r="R21" s="44">
         <f t="shared" si="9"/>
         <v>0.49</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="61">
         <v>4</v>
       </c>
@@ -4460,7 +4542,7 @@
       <c r="D22" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="170"/>
+      <c r="E22" s="169"/>
       <c r="F22" s="68">
         <v>1.3899999999999999E-2</v>
       </c>
@@ -4488,11 +4570,11 @@
       </c>
       <c r="M22" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N22" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O22" s="125">
         <f t="shared" si="6"/>
@@ -4500,18 +4582,18 @@
       </c>
       <c r="P22" s="72">
         <f t="shared" si="7"/>
-        <v>578894.5</v>
+        <v>580463.5</v>
       </c>
       <c r="Q22" s="73">
         <f t="shared" si="8"/>
-        <v>596261.5</v>
+        <v>597877.5</v>
       </c>
       <c r="R22" s="44">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="61">
         <v>5</v>
       </c>
@@ -4554,11 +4636,11 @@
       </c>
       <c r="M23" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N23" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O23" s="125">
         <f t="shared" si="6"/>
@@ -4566,18 +4648,18 @@
       </c>
       <c r="P23" s="72">
         <f t="shared" si="7"/>
-        <v>36153.51</v>
+        <v>37722.51</v>
       </c>
       <c r="Q23" s="73">
         <f t="shared" si="8"/>
-        <v>37238.51</v>
+        <v>38854.51</v>
       </c>
       <c r="R23" s="44">
         <f t="shared" si="9"/>
         <v>0.51</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="61">
         <v>5</v>
       </c>
@@ -4621,11 +4703,11 @@
       </c>
       <c r="M24" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N24" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O24" s="125">
         <f t="shared" si="6"/>
@@ -4633,18 +4715,18 @@
       </c>
       <c r="P24" s="72">
         <f t="shared" si="7"/>
-        <v>131652.51999999999</v>
+        <v>133933.51999999999</v>
       </c>
       <c r="Q24" s="73">
         <f t="shared" si="8"/>
-        <v>135602.51999999999</v>
+        <v>137951.51999999999</v>
       </c>
       <c r="R24" s="44">
         <f t="shared" si="9"/>
         <v>0.52</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="61">
         <v>6</v>
       </c>
@@ -4686,11 +4768,11 @@
       </c>
       <c r="M25" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N25" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O25" s="125">
         <f t="shared" si="6"/>
@@ -4698,18 +4780,18 @@
       </c>
       <c r="P25" s="72">
         <f t="shared" si="7"/>
-        <v>131652.53</v>
+        <v>133933.53</v>
       </c>
       <c r="Q25" s="73">
         <f t="shared" si="8"/>
-        <v>135602.53</v>
+        <v>137951.53</v>
       </c>
       <c r="R25" s="44">
         <f t="shared" si="9"/>
         <v>0.53</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="61">
         <v>6</v>
       </c>
@@ -4753,11 +4835,11 @@
       </c>
       <c r="M26" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N26" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O26" s="125">
         <f t="shared" si="6"/>
@@ -4765,18 +4847,18 @@
       </c>
       <c r="P26" s="72">
         <f t="shared" si="7"/>
-        <v>90592.54</v>
+        <v>92161.54</v>
       </c>
       <c r="Q26" s="73">
         <f t="shared" si="8"/>
-        <v>93310.54</v>
+        <v>94926.54</v>
       </c>
       <c r="R26" s="44">
         <f t="shared" si="9"/>
         <v>0.54</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="61">
         <v>7</v>
       </c>
@@ -4786,13 +4868,13 @@
       <c r="C27" s="61">
         <v>55</v>
       </c>
-      <c r="D27" s="178" t="s">
+      <c r="D27" s="176" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="181" t="s">
+      <c r="E27" s="179" t="s">
         <v>127</v>
       </c>
-      <c r="F27" s="179">
+      <c r="F27" s="177">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G27" s="69">
@@ -4820,11 +4902,11 @@
       </c>
       <c r="M27" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N27" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O27" s="125">
         <f t="shared" si="6"/>
@@ -4832,18 +4914,18 @@
       </c>
       <c r="P27" s="72">
         <f t="shared" si="7"/>
-        <v>102503.55</v>
+        <v>104072.55</v>
       </c>
       <c r="Q27" s="73">
         <f t="shared" si="8"/>
-        <v>105578.55</v>
+        <v>107194.55</v>
       </c>
       <c r="R27" s="44">
         <f t="shared" si="9"/>
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="61">
         <v>7</v>
       </c>
@@ -4888,11 +4970,11 @@
       </c>
       <c r="M28" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N28" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O28" s="125">
         <f t="shared" si="6"/>
@@ -4900,18 +4982,18 @@
       </c>
       <c r="P28" s="72">
         <f t="shared" si="7"/>
-        <v>131652.56</v>
+        <v>133932.56</v>
       </c>
       <c r="Q28" s="73">
         <f t="shared" si="8"/>
-        <v>135602.56</v>
+        <v>137950.56</v>
       </c>
       <c r="R28" s="44">
         <f t="shared" si="9"/>
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="61">
         <v>8</v>
       </c>
@@ -4953,11 +5035,11 @@
       </c>
       <c r="M29" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N29" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O29" s="125">
         <f t="shared" si="6"/>
@@ -4965,18 +5047,18 @@
       </c>
       <c r="P29" s="72">
         <f t="shared" si="7"/>
-        <v>131652.57</v>
+        <v>133933.57</v>
       </c>
       <c r="Q29" s="73">
         <f t="shared" si="8"/>
-        <v>135602.57</v>
+        <v>137951.57</v>
       </c>
       <c r="R29" s="44">
         <f t="shared" si="9"/>
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="61">
         <v>8</v>
       </c>
@@ -5020,11 +5102,11 @@
       </c>
       <c r="M30" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N30" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O30" s="125">
         <f t="shared" si="6"/>
@@ -5032,18 +5114,18 @@
       </c>
       <c r="P30" s="72">
         <f t="shared" si="7"/>
-        <v>90592.58</v>
+        <v>92161.58</v>
       </c>
       <c r="Q30" s="73">
         <f t="shared" si="8"/>
-        <v>93310.58</v>
+        <v>94926.58</v>
       </c>
       <c r="R30" s="44">
         <f t="shared" si="9"/>
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="61">
         <v>9</v>
       </c>
@@ -5085,11 +5167,11 @@
       </c>
       <c r="M31" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N31" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O31" s="125">
         <f t="shared" si="6"/>
@@ -5097,18 +5179,18 @@
       </c>
       <c r="P31" s="72">
         <f t="shared" si="7"/>
-        <v>90592.59</v>
+        <v>92161.59</v>
       </c>
       <c r="Q31" s="73">
         <f t="shared" si="8"/>
-        <v>93310.59</v>
+        <v>94926.59</v>
       </c>
       <c r="R31" s="44">
         <f t="shared" si="9"/>
         <v>0.59</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="61">
         <v>9</v>
       </c>
@@ -5150,11 +5232,11 @@
       </c>
       <c r="M32" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N32" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O32" s="125">
         <f t="shared" si="6"/>
@@ -5162,18 +5244,18 @@
       </c>
       <c r="P32" s="72">
         <f t="shared" si="7"/>
-        <v>131652.6</v>
+        <v>133933.6</v>
       </c>
       <c r="Q32" s="73">
         <f t="shared" si="8"/>
-        <v>135602.6</v>
+        <v>137951.6</v>
       </c>
       <c r="R32" s="44">
         <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="61">
         <v>10</v>
       </c>
@@ -5183,14 +5265,14 @@
       <c r="C33" s="61">
         <v>61</v>
       </c>
-      <c r="D33" s="178" t="s">
+      <c r="D33" s="176" t="s">
         <v>141</v>
       </c>
-      <c r="E33" s="178"/>
-      <c r="F33" s="179">
+      <c r="E33" s="176"/>
+      <c r="F33" s="177">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G33" s="183">
+      <c r="G33" s="181">
         <v>145692.60999999999</v>
       </c>
       <c r="H33" s="118">
@@ -5215,11 +5297,11 @@
       </c>
       <c r="M33" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N33" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O33" s="125">
         <f t="shared" si="6"/>
@@ -5227,18 +5309,18 @@
       </c>
       <c r="P33" s="72">
         <f t="shared" si="7"/>
-        <v>131653.60999999999</v>
+        <v>133933.60999999999</v>
       </c>
       <c r="Q33" s="73">
         <f t="shared" si="8"/>
-        <v>135603.60999999999</v>
+        <v>137951.60999999999</v>
       </c>
       <c r="R33" s="44">
         <f t="shared" si="9"/>
         <v>0.61</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="61">
         <v>10</v>
       </c>
@@ -5282,11 +5364,11 @@
       </c>
       <c r="M34" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N34" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O34" s="125">
         <f t="shared" si="6"/>
@@ -5294,18 +5376,18 @@
       </c>
       <c r="P34" s="72">
         <f t="shared" si="7"/>
-        <v>90592.62</v>
+        <v>92161.62</v>
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="8"/>
-        <v>93310.62</v>
+        <v>94926.62</v>
       </c>
       <c r="R34" s="44">
         <f t="shared" si="9"/>
         <v>0.62</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="61">
         <v>11</v>
       </c>
@@ -5349,11 +5431,11 @@
       </c>
       <c r="M35" s="125">
         <f t="shared" si="4"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N35" s="125">
         <f t="shared" si="5"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O35" s="125">
         <f t="shared" si="6"/>
@@ -5361,18 +5443,18 @@
       </c>
       <c r="P35" s="72">
         <f t="shared" si="7"/>
-        <v>90592.63</v>
+        <v>92161.63</v>
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="8"/>
-        <v>93310.63</v>
+        <v>94926.63</v>
       </c>
       <c r="R35" s="44">
         <f t="shared" si="9"/>
         <v>0.63</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="61">
         <v>11</v>
       </c>
@@ -5416,11 +5498,11 @@
       </c>
       <c r="M36" s="125">
         <f t="shared" si="4"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N36" s="125">
         <f t="shared" si="5"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O36" s="125">
         <f t="shared" si="6"/>
@@ -5428,18 +5510,18 @@
       </c>
       <c r="P36" s="72">
         <f t="shared" si="7"/>
-        <v>131652.64000000001</v>
+        <v>133933.64000000001</v>
       </c>
       <c r="Q36" s="73">
         <f t="shared" si="8"/>
-        <v>135602.64000000001</v>
+        <v>137951.64000000001</v>
       </c>
       <c r="R36" s="44">
         <f t="shared" si="9"/>
         <v>0.64</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="61">
         <v>12</v>
       </c>
@@ -5483,11 +5565,11 @@
       </c>
       <c r="M37" s="125">
         <f t="shared" ref="M37:M56" si="14">F$1*F37</f>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N37" s="125">
         <f t="shared" ref="N37:N56" si="15">F$2*F37</f>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O37" s="125">
         <f t="shared" ref="O37:O68" si="16">I$2*F37</f>
@@ -5495,18 +5577,18 @@
       </c>
       <c r="P37" s="72">
         <f t="shared" ref="P37:P68" si="17">ROUND(SUM(I37:O37),0) + R37</f>
-        <v>131652.65</v>
+        <v>133933.65</v>
       </c>
       <c r="Q37" s="73">
         <f t="shared" ref="Q37:Q56" si="18">ROUND(P37*3%,0) + P37</f>
-        <v>135602.65</v>
+        <v>137951.65</v>
       </c>
       <c r="R37" s="44">
         <f t="shared" ref="R37:R68" si="19">ROUND(0.001+C37/100,2)</f>
         <v>0.65</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="61">
         <v>12</v>
       </c>
@@ -5547,11 +5629,11 @@
       </c>
       <c r="M38" s="125">
         <f t="shared" si="14"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N38" s="125">
         <f t="shared" si="15"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O38" s="125">
         <f t="shared" si="16"/>
@@ -5559,18 +5641,18 @@
       </c>
       <c r="P38" s="72">
         <f t="shared" si="17"/>
-        <v>308526.65999999997</v>
+        <v>310095.65999999997</v>
       </c>
       <c r="Q38" s="73">
         <f t="shared" si="18"/>
-        <v>317782.65999999997</v>
+        <v>319398.65999999997</v>
       </c>
       <c r="R38" s="44">
         <f t="shared" si="19"/>
         <v>0.66</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="61">
         <v>1</v>
       </c>
@@ -5614,11 +5696,11 @@
       </c>
       <c r="M39" s="125">
         <f t="shared" si="14"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N39" s="125">
         <f t="shared" si="15"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O39" s="125">
         <f t="shared" si="16"/>
@@ -5626,31 +5708,31 @@
       </c>
       <c r="P39" s="72">
         <f t="shared" si="17"/>
-        <v>90592.67</v>
+        <v>92161.67</v>
       </c>
       <c r="Q39" s="73">
         <f t="shared" si="18"/>
-        <v>93310.67</v>
+        <v>94926.67</v>
       </c>
       <c r="R39" s="44">
         <f t="shared" si="19"/>
         <v>0.67</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="61">
         <v>1</v>
       </c>
       <c r="B40" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="C40" s="230">
+      <c r="C40" s="193">
         <v>68</v>
       </c>
-      <c r="D40" s="230" t="s">
+      <c r="D40" s="193" t="s">
         <v>161</v>
       </c>
-      <c r="E40" s="231" t="str">
+      <c r="E40" s="194" t="str">
         <f>D76</f>
         <v>Jesica Romina Tobio</v>
       </c>
@@ -5679,11 +5761,11 @@
       </c>
       <c r="M40" s="125">
         <f t="shared" si="14"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N40" s="125">
         <f t="shared" si="15"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O40" s="125">
         <f t="shared" si="16"/>
@@ -5691,18 +5773,18 @@
       </c>
       <c r="P40" s="72">
         <f t="shared" si="17"/>
-        <v>281716.68</v>
+        <v>283996.68</v>
       </c>
       <c r="Q40" s="73">
         <f t="shared" si="18"/>
-        <v>290168.68</v>
+        <v>292516.68</v>
       </c>
       <c r="R40" s="44">
         <f t="shared" si="19"/>
         <v>0.68</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="60">
         <v>1</v>
       </c>
@@ -5745,11 +5827,11 @@
       </c>
       <c r="M41" s="125">
         <f t="shared" si="14"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N41" s="125">
         <f t="shared" si="15"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O41" s="125">
         <f t="shared" si="16"/>
@@ -5757,18 +5839,18 @@
       </c>
       <c r="P41" s="72">
         <f t="shared" si="17"/>
-        <v>131652.69</v>
+        <v>133933.69</v>
       </c>
       <c r="Q41" s="73">
         <f t="shared" si="18"/>
-        <v>135602.69</v>
+        <v>137951.69</v>
       </c>
       <c r="R41" s="44">
         <f t="shared" si="19"/>
         <v>0.69</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="61">
         <v>2</v>
       </c>
@@ -5812,11 +5894,11 @@
       </c>
       <c r="M42" s="125">
         <f t="shared" si="14"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N42" s="125">
         <f t="shared" si="15"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O42" s="125">
         <f t="shared" si="16"/>
@@ -5824,18 +5906,18 @@
       </c>
       <c r="P42" s="72">
         <f t="shared" si="17"/>
-        <v>131445.70000000001</v>
+        <v>133014.70000000001</v>
       </c>
       <c r="Q42" s="73">
         <f t="shared" si="18"/>
-        <v>135388.70000000001</v>
+        <v>137004.70000000001</v>
       </c>
       <c r="R42" s="44">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="61">
         <v>2</v>
       </c>
@@ -5879,11 +5961,11 @@
       </c>
       <c r="M43" s="125">
         <f t="shared" si="14"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N43" s="125">
         <f t="shared" si="15"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O43" s="125">
         <f t="shared" si="16"/>
@@ -5891,18 +5973,18 @@
       </c>
       <c r="P43" s="72">
         <f t="shared" si="17"/>
-        <v>90592.71</v>
+        <v>92161.71</v>
       </c>
       <c r="Q43" s="73">
         <f t="shared" si="18"/>
-        <v>93310.71</v>
+        <v>94926.71</v>
       </c>
       <c r="R43" s="44">
         <f t="shared" si="19"/>
         <v>0.71</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="61">
         <v>2</v>
       </c>
@@ -5912,13 +5994,13 @@
       <c r="C44" s="61">
         <v>72</v>
       </c>
-      <c r="D44" s="178" t="s">
+      <c r="D44" s="176" t="s">
         <v>168</v>
       </c>
-      <c r="E44" s="178" t="s">
+      <c r="E44" s="176" t="s">
         <v>249</v>
       </c>
-      <c r="F44" s="182">
+      <c r="F44" s="180">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G44" s="69">
@@ -5945,11 +6027,11 @@
       </c>
       <c r="M44" s="125">
         <f t="shared" si="14"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N44" s="125">
         <f t="shared" si="15"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O44" s="125">
         <f t="shared" si="16"/>
@@ -5957,18 +6039,18 @@
       </c>
       <c r="P44" s="72">
         <f t="shared" si="17"/>
-        <v>451878.72</v>
+        <v>454158.72</v>
       </c>
       <c r="Q44" s="73">
         <f t="shared" si="18"/>
-        <v>465434.72</v>
+        <v>467783.72</v>
       </c>
       <c r="R44" s="44">
         <f t="shared" si="19"/>
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="61">
         <v>3</v>
       </c>
@@ -6009,11 +6091,11 @@
       </c>
       <c r="M45" s="125">
         <f t="shared" si="14"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N45" s="125">
         <f t="shared" si="15"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O45" s="125">
         <f t="shared" si="16"/>
@@ -6021,18 +6103,18 @@
       </c>
       <c r="P45" s="72">
         <f t="shared" si="17"/>
-        <v>616960.73</v>
+        <v>619240.73</v>
       </c>
       <c r="Q45" s="73">
         <f t="shared" si="18"/>
-        <v>635469.73</v>
+        <v>637817.73</v>
       </c>
       <c r="R45" s="44">
         <f t="shared" si="19"/>
         <v>0.73</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="61">
         <v>3</v>
       </c>
@@ -6075,11 +6157,11 @@
       </c>
       <c r="M46" s="125">
         <f t="shared" si="14"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N46" s="125">
         <f t="shared" si="15"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O46" s="125">
         <f t="shared" si="16"/>
@@ -6087,18 +6169,18 @@
       </c>
       <c r="P46" s="72">
         <f t="shared" si="17"/>
-        <v>90592.74</v>
+        <v>92161.74</v>
       </c>
       <c r="Q46" s="73">
         <f t="shared" si="18"/>
-        <v>93310.74</v>
+        <v>94926.74</v>
       </c>
       <c r="R46" s="44">
         <f t="shared" si="19"/>
         <v>0.74</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="61">
         <v>3</v>
       </c>
@@ -6139,11 +6221,11 @@
       </c>
       <c r="M47" s="125">
         <f t="shared" si="14"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N47" s="125">
         <f t="shared" si="15"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O47" s="125">
         <f t="shared" si="16"/>
@@ -6151,11 +6233,11 @@
       </c>
       <c r="P47" s="72">
         <f t="shared" si="17"/>
-        <v>193854.75</v>
+        <v>195423.75</v>
       </c>
       <c r="Q47" s="73">
         <f t="shared" si="18"/>
-        <v>199670.75</v>
+        <v>201286.75</v>
       </c>
       <c r="R47" s="44">
         <f t="shared" si="19"/>
@@ -6163,7 +6245,7 @@
       </c>
       <c r="T47" s="142"/>
     </row>
-    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="61">
         <v>4</v>
       </c>
@@ -6207,11 +6289,11 @@
       </c>
       <c r="M48" s="125">
         <f t="shared" si="14"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N48" s="125">
         <f t="shared" si="15"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O48" s="125">
         <f t="shared" si="16"/>
@@ -6219,18 +6301,18 @@
       </c>
       <c r="P48" s="72">
         <f t="shared" si="17"/>
-        <v>131652.76</v>
+        <v>133933.76000000001</v>
       </c>
       <c r="Q48" s="73">
         <f t="shared" si="18"/>
-        <v>135602.76</v>
+        <v>137951.76</v>
       </c>
       <c r="R48" s="44">
         <f t="shared" si="19"/>
         <v>0.76</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="61">
         <v>4</v>
       </c>
@@ -6240,13 +6322,13 @@
       <c r="C49" s="61">
         <v>77</v>
       </c>
-      <c r="D49" s="178" t="s">
+      <c r="D49" s="176" t="s">
         <v>168</v>
       </c>
-      <c r="E49" s="178" t="s">
+      <c r="E49" s="176" t="s">
         <v>184</v>
       </c>
-      <c r="F49" s="182">
+      <c r="F49" s="180">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G49" s="69">
@@ -6274,11 +6356,11 @@
       </c>
       <c r="M49" s="125">
         <f t="shared" si="14"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N49" s="125">
         <f t="shared" si="15"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O49" s="125">
         <f t="shared" si="16"/>
@@ -6286,18 +6368,18 @@
       </c>
       <c r="P49" s="72">
         <f t="shared" si="17"/>
-        <v>131652.76999999999</v>
+        <v>133933.76999999999</v>
       </c>
       <c r="Q49" s="73">
         <f t="shared" si="18"/>
-        <v>135602.76999999999</v>
+        <v>137951.76999999999</v>
       </c>
       <c r="R49" s="44">
         <f t="shared" si="19"/>
         <v>0.77</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="61">
         <v>4</v>
       </c>
@@ -6340,11 +6422,11 @@
       </c>
       <c r="M50" s="125">
         <f t="shared" si="14"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N50" s="125">
         <f t="shared" si="15"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O50" s="125">
         <f t="shared" si="16"/>
@@ -6352,18 +6434,18 @@
       </c>
       <c r="P50" s="72">
         <f t="shared" si="17"/>
-        <v>193854.78</v>
+        <v>195423.78</v>
       </c>
       <c r="Q50" s="73">
         <f t="shared" si="18"/>
-        <v>199670.78</v>
+        <v>201286.78</v>
       </c>
       <c r="R50" s="44">
         <f t="shared" si="19"/>
         <v>0.78</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="61">
         <v>5</v>
       </c>
@@ -6404,11 +6486,11 @@
       </c>
       <c r="M51" s="125">
         <f t="shared" si="14"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N51" s="125">
         <f t="shared" si="15"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O51" s="125">
         <f t="shared" si="16"/>
@@ -6416,18 +6498,18 @@
       </c>
       <c r="P51" s="72">
         <f t="shared" si="17"/>
-        <v>87584.79</v>
+        <v>89153.79</v>
       </c>
       <c r="Q51" s="73">
         <f t="shared" si="18"/>
-        <v>90212.79</v>
+        <v>91828.79</v>
       </c>
       <c r="R51" s="44">
         <f t="shared" si="19"/>
         <v>0.79</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="61">
         <v>5</v>
       </c>
@@ -6470,11 +6552,11 @@
       </c>
       <c r="M52" s="125">
         <f t="shared" si="14"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N52" s="125">
         <f t="shared" si="15"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O52" s="125">
         <f t="shared" si="16"/>
@@ -6482,18 +6564,18 @@
       </c>
       <c r="P52" s="72">
         <f t="shared" si="17"/>
-        <v>123313.8</v>
+        <v>125594.8</v>
       </c>
       <c r="Q52" s="73">
         <f t="shared" si="18"/>
-        <v>127012.8</v>
+        <v>129362.8</v>
       </c>
       <c r="R52" s="44">
         <f t="shared" si="19"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="61">
         <v>5</v>
       </c>
@@ -6537,11 +6619,11 @@
       </c>
       <c r="M53" s="125">
         <f t="shared" si="14"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N53" s="125">
         <f t="shared" si="15"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O53" s="125">
         <f t="shared" si="16"/>
@@ -6549,11 +6631,11 @@
       </c>
       <c r="P53" s="72">
         <f t="shared" si="17"/>
-        <v>131652.81</v>
+        <v>133933.81</v>
       </c>
       <c r="Q53" s="73">
         <f t="shared" si="18"/>
-        <v>135602.81</v>
+        <v>137951.81</v>
       </c>
       <c r="R53" s="44">
         <f t="shared" si="19"/>
@@ -6563,7 +6645,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="61">
         <v>6</v>
       </c>
@@ -6605,11 +6687,11 @@
       </c>
       <c r="M54" s="125">
         <f t="shared" si="14"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N54" s="125">
         <f t="shared" si="15"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O54" s="125">
         <f t="shared" si="16"/>
@@ -6617,18 +6699,18 @@
       </c>
       <c r="P54" s="72">
         <f t="shared" si="17"/>
-        <v>90592.82</v>
+        <v>92161.82</v>
       </c>
       <c r="Q54" s="73">
         <f t="shared" si="18"/>
-        <v>93310.82</v>
+        <v>94926.82</v>
       </c>
       <c r="R54" s="44">
         <f t="shared" si="19"/>
         <v>0.82</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="61">
         <v>6</v>
       </c>
@@ -6669,11 +6751,11 @@
       </c>
       <c r="M55" s="125">
         <f t="shared" si="14"/>
-        <v>29844.356399999997</v>
+        <v>31435.598653999998</v>
       </c>
       <c r="N55" s="125">
         <f t="shared" si="15"/>
-        <v>10708.103385</v>
+        <v>10685.881872</v>
       </c>
       <c r="O55" s="125">
         <f t="shared" si="16"/>
@@ -6681,18 +6763,18 @@
       </c>
       <c r="P55" s="72">
         <f t="shared" si="17"/>
-        <v>424543.83</v>
+        <v>426112.83</v>
       </c>
       <c r="Q55" s="73">
         <f t="shared" si="18"/>
-        <v>437279.83</v>
+        <v>438895.83</v>
       </c>
       <c r="R55" s="44">
         <f t="shared" si="19"/>
         <v>0.83</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="61">
         <v>6</v>
       </c>
@@ -6734,11 +6816,11 @@
       </c>
       <c r="M56" s="125">
         <f t="shared" si="14"/>
-        <v>43370.9352</v>
+        <v>45683.387971999997</v>
       </c>
       <c r="N56" s="125">
         <f t="shared" si="15"/>
-        <v>15561.416429999999</v>
+        <v>15529.123296</v>
       </c>
       <c r="O56" s="125">
         <f t="shared" si="16"/>
@@ -6746,18 +6828,18 @@
       </c>
       <c r="P56" s="72">
         <f t="shared" si="17"/>
-        <v>131652.84</v>
+        <v>133933.84</v>
       </c>
       <c r="Q56" s="73">
         <f t="shared" si="18"/>
-        <v>135602.84</v>
+        <v>137951.84</v>
       </c>
       <c r="R56" s="44">
         <f t="shared" si="19"/>
         <v>0.84</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="61">
         <v>7</v>
       </c>
@@ -6793,7 +6875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="61">
         <v>7</v>
       </c>
@@ -6829,7 +6911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="61">
         <v>7</v>
       </c>
@@ -6873,11 +6955,11 @@
       </c>
       <c r="M59" s="125">
         <f t="shared" ref="M59:M90" si="23">F$1*F59</f>
-        <v>6870.6432000000004</v>
+        <v>7236.9723519999998</v>
       </c>
       <c r="N59" s="125">
         <f t="shared" ref="N59:N90" si="24">F$2*F59</f>
-        <v>2465.17488</v>
+        <v>2460.0591359999999</v>
       </c>
       <c r="O59" s="125">
         <f t="shared" si="16"/>
@@ -6885,18 +6967,18 @@
       </c>
       <c r="P59" s="72">
         <f t="shared" si="17"/>
-        <v>20856.169999999998</v>
+        <v>21217.17</v>
       </c>
       <c r="Q59" s="73">
         <f t="shared" ref="Q59:Q90" si="25">ROUND(P59*3%,0) + P59</f>
-        <v>21482.17</v>
+        <v>21854.17</v>
       </c>
       <c r="R59" s="44">
         <f t="shared" si="19"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="61">
         <v>8</v>
       </c>
@@ -6935,11 +7017,11 @@
       </c>
       <c r="M60" s="125">
         <f t="shared" si="23"/>
-        <v>7085.3508000000002</v>
+        <v>7463.1277379999992</v>
       </c>
       <c r="N60" s="125">
         <f t="shared" si="24"/>
-        <v>2542.2115950000002</v>
+        <v>2536.9359839999997</v>
       </c>
       <c r="O60" s="125">
         <f t="shared" si="16"/>
@@ -6947,18 +7029,18 @@
       </c>
       <c r="P60" s="72">
         <f t="shared" si="17"/>
-        <v>229373.18</v>
+        <v>229746.18</v>
       </c>
       <c r="Q60" s="73">
         <f t="shared" si="25"/>
-        <v>236254.18</v>
+        <v>236638.18</v>
       </c>
       <c r="R60" s="44">
         <f t="shared" si="19"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="61">
         <v>8</v>
       </c>
@@ -6997,11 +7079,11 @@
       </c>
       <c r="M61" s="125">
         <f t="shared" si="23"/>
-        <v>858.83040000000005</v>
+        <v>904.62154399999997</v>
       </c>
       <c r="N61" s="125">
         <f t="shared" si="24"/>
-        <v>308.14686</v>
+        <v>307.50739199999998</v>
       </c>
       <c r="O61" s="125">
         <f t="shared" si="16"/>
@@ -7009,18 +7091,18 @@
       </c>
       <c r="P61" s="72">
         <f t="shared" si="17"/>
-        <v>9901.19</v>
+        <v>9946.19</v>
       </c>
       <c r="Q61" s="73">
         <f t="shared" si="25"/>
-        <v>10198.19</v>
+        <v>10244.19</v>
       </c>
       <c r="R61" s="44">
         <f t="shared" si="19"/>
         <v>0.19</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="61">
         <v>8</v>
       </c>
@@ -7059,11 +7141,11 @@
       </c>
       <c r="M62" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N62" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O62" s="125">
         <f t="shared" si="16"/>
@@ -7071,18 +7153,18 @@
       </c>
       <c r="P62" s="72">
         <f t="shared" si="17"/>
-        <v>2789.2</v>
+        <v>2812.2</v>
       </c>
       <c r="Q62" s="73">
         <f t="shared" si="25"/>
-        <v>2873.2</v>
+        <v>2896.2</v>
       </c>
       <c r="R62" s="44">
         <f t="shared" si="19"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="61">
         <v>9</v>
       </c>
@@ -7123,11 +7205,11 @@
       </c>
       <c r="M63" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N63" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O63" s="125">
         <f t="shared" si="16"/>
@@ -7135,18 +7217,18 @@
       </c>
       <c r="P63" s="72">
         <f t="shared" si="17"/>
-        <v>-43770.79</v>
+        <v>-43748.79</v>
       </c>
       <c r="Q63" s="73">
         <f t="shared" si="25"/>
-        <v>-45083.79</v>
+        <v>-45060.79</v>
       </c>
       <c r="R63" s="44">
         <f t="shared" si="19"/>
         <v>0.21</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="61">
         <v>9</v>
       </c>
@@ -7156,11 +7238,11 @@
       <c r="C64" s="61">
         <v>22</v>
       </c>
-      <c r="D64" s="178" t="s">
+      <c r="D64" s="176" t="s">
         <v>83</v>
       </c>
-      <c r="E64" s="181"/>
-      <c r="F64" s="182">
+      <c r="E64" s="179"/>
+      <c r="F64" s="180">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G64" s="69">
@@ -7188,11 +7270,11 @@
       </c>
       <c r="M64" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N64" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O64" s="125">
         <f t="shared" si="16"/>
@@ -7200,18 +7282,18 @@
       </c>
       <c r="P64" s="72">
         <f t="shared" si="17"/>
-        <v>1303.22</v>
+        <v>1326.22</v>
       </c>
       <c r="Q64" s="73">
         <f t="shared" si="25"/>
-        <v>1342.22</v>
+        <v>1366.22</v>
       </c>
       <c r="R64" s="44">
         <f t="shared" si="19"/>
         <v>0.22</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="61">
         <v>9</v>
       </c>
@@ -7255,11 +7337,11 @@
       </c>
       <c r="M65" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N65" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O65" s="125">
         <f t="shared" si="16"/>
@@ -7267,18 +7349,18 @@
       </c>
       <c r="P65" s="72">
         <f t="shared" si="17"/>
-        <v>2294.23</v>
+        <v>2317.23</v>
       </c>
       <c r="Q65" s="73">
         <f t="shared" si="25"/>
-        <v>2363.23</v>
+        <v>2387.23</v>
       </c>
       <c r="R65" s="44">
         <f t="shared" si="19"/>
         <v>0.23</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="61">
         <v>10</v>
       </c>
@@ -7319,11 +7401,11 @@
       </c>
       <c r="M66" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N66" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O66" s="125">
         <f t="shared" si="16"/>
@@ -7331,18 +7413,18 @@
       </c>
       <c r="P66" s="72">
         <f t="shared" si="17"/>
-        <v>1260.24</v>
+        <v>1283.24</v>
       </c>
       <c r="Q66" s="73">
         <f t="shared" si="25"/>
-        <v>1298.24</v>
+        <v>1321.24</v>
       </c>
       <c r="R66" s="44">
         <f t="shared" si="19"/>
         <v>0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="61">
         <v>10</v>
       </c>
@@ -7386,11 +7468,11 @@
       </c>
       <c r="M67" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N67" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O67" s="125">
         <f t="shared" si="16"/>
@@ -7398,18 +7480,18 @@
       </c>
       <c r="P67" s="72">
         <f t="shared" si="17"/>
-        <v>1303.25</v>
+        <v>1326.25</v>
       </c>
       <c r="Q67" s="73">
         <f t="shared" si="25"/>
-        <v>1342.25</v>
+        <v>1366.25</v>
       </c>
       <c r="R67" s="44">
         <f t="shared" si="19"/>
         <v>0.25</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="61">
         <v>10</v>
       </c>
@@ -7423,7 +7505,7 @@
         <v>134</v>
       </c>
       <c r="E68" s="60" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F68" s="75">
         <v>2.0000000000000001E-4</v>
@@ -7453,11 +7535,11 @@
       </c>
       <c r="M68" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N68" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O68" s="125">
         <f t="shared" si="16"/>
@@ -7465,18 +7547,18 @@
       </c>
       <c r="P68" s="72">
         <f t="shared" si="17"/>
-        <v>1303.26</v>
+        <v>1326.26</v>
       </c>
       <c r="Q68" s="73">
         <f t="shared" si="25"/>
-        <v>1342.26</v>
+        <v>1366.26</v>
       </c>
       <c r="R68" s="44">
         <f t="shared" si="19"/>
         <v>0.26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="61">
         <v>11</v>
       </c>
@@ -7515,11 +7597,11 @@
       </c>
       <c r="M69" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N69" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O69" s="125">
         <f t="shared" ref="O69:O90" si="27">I$2*F69</f>
@@ -7527,18 +7609,18 @@
       </c>
       <c r="P69" s="72">
         <f t="shared" ref="P69:P90" si="28">ROUND(SUM(I69:O69),0) + R69</f>
-        <v>15436.27</v>
+        <v>15459.27</v>
       </c>
       <c r="Q69" s="73">
         <f t="shared" si="25"/>
-        <v>15899.27</v>
+        <v>15923.27</v>
       </c>
       <c r="R69" s="44">
         <f t="shared" ref="R69:R90" si="29">ROUND(0.001+C69/100,2)</f>
         <v>0.27</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="61">
         <v>11</v>
       </c>
@@ -7577,11 +7659,11 @@
       </c>
       <c r="M70" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N70" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O70" s="125">
         <f t="shared" si="27"/>
@@ -7589,18 +7671,18 @@
       </c>
       <c r="P70" s="72">
         <f t="shared" si="28"/>
-        <v>15436.28</v>
+        <v>15459.28</v>
       </c>
       <c r="Q70" s="73">
         <f t="shared" si="25"/>
-        <v>15899.28</v>
+        <v>15923.28</v>
       </c>
       <c r="R70" s="44">
         <f t="shared" si="29"/>
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="61">
         <v>11</v>
       </c>
@@ -7641,11 +7723,11 @@
       </c>
       <c r="M71" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N71" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O71" s="125">
         <f t="shared" si="27"/>
@@ -7653,18 +7735,18 @@
       </c>
       <c r="P71" s="72">
         <f t="shared" si="28"/>
-        <v>4352.29</v>
+        <v>4374.29</v>
       </c>
       <c r="Q71" s="73">
         <f t="shared" si="25"/>
-        <v>4483.29</v>
+        <v>4505.29</v>
       </c>
       <c r="R71" s="44">
         <f t="shared" si="29"/>
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="61"/>
       <c r="B72" s="77" t="s">
         <v>223</v>
@@ -7703,11 +7785,11 @@
       </c>
       <c r="M72" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N72" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O72" s="125">
         <f t="shared" si="27"/>
@@ -7715,18 +7797,18 @@
       </c>
       <c r="P72" s="72">
         <f t="shared" si="28"/>
-        <v>2789.3</v>
+        <v>2812.3</v>
       </c>
       <c r="Q72" s="73">
         <f t="shared" si="25"/>
-        <v>2873.3</v>
+        <v>2896.3</v>
       </c>
       <c r="R72" s="44">
         <f t="shared" si="29"/>
         <v>0.3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="61"/>
       <c r="B73" s="77" t="s">
         <v>224</v>
@@ -7763,11 +7845,11 @@
       </c>
       <c r="M73" s="125">
         <f t="shared" si="23"/>
-        <v>429.41520000000003</v>
+        <v>452.31077199999999</v>
       </c>
       <c r="N73" s="125">
         <f t="shared" si="24"/>
-        <v>154.07343</v>
+        <v>153.75369599999999</v>
       </c>
       <c r="O73" s="125">
         <f t="shared" si="27"/>
@@ -7775,18 +7857,18 @@
       </c>
       <c r="P73" s="72">
         <f t="shared" si="28"/>
-        <v>8801.31</v>
+        <v>8824.31</v>
       </c>
       <c r="Q73" s="73">
         <f t="shared" si="25"/>
-        <v>9065.31</v>
+        <v>9089.31</v>
       </c>
       <c r="R73" s="44">
         <f t="shared" si="29"/>
         <v>0.31</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="61"/>
       <c r="B74" s="77" t="s">
         <v>225</v>
@@ -7823,11 +7905,11 @@
       </c>
       <c r="M74" s="125">
         <f t="shared" si="23"/>
-        <v>33923.800800000005</v>
+        <v>35732.550988000003</v>
       </c>
       <c r="N74" s="125">
         <f t="shared" si="24"/>
-        <v>12171.800970000002</v>
+        <v>12146.541984000001</v>
       </c>
       <c r="O74" s="125">
         <f t="shared" si="27"/>
@@ -7835,18 +7917,18 @@
       </c>
       <c r="P74" s="72">
         <f t="shared" si="28"/>
-        <v>2800902.32</v>
+        <v>2802686.32</v>
       </c>
       <c r="Q74" s="73">
         <f t="shared" si="25"/>
-        <v>2884929.32</v>
+        <v>2886767.32</v>
       </c>
       <c r="R74" s="44">
         <f t="shared" si="29"/>
         <v>0.32</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="61"/>
       <c r="B75" s="77" t="s">
         <v>227</v>
@@ -7883,11 +7965,11 @@
       </c>
       <c r="M75" s="125">
         <f t="shared" si="23"/>
-        <v>13097.163600000002</v>
+        <v>13795.478546</v>
       </c>
       <c r="N75" s="125">
         <f t="shared" si="24"/>
-        <v>4699.2396150000004</v>
+        <v>4689.4877280000001</v>
       </c>
       <c r="O75" s="125">
         <f t="shared" si="27"/>
@@ -7895,29 +7977,29 @@
       </c>
       <c r="P75" s="72">
         <f t="shared" si="28"/>
-        <v>390081.01</v>
+        <v>390770.01</v>
       </c>
       <c r="Q75" s="73">
         <f t="shared" si="25"/>
-        <v>401783.01</v>
+        <v>402493.01</v>
       </c>
       <c r="R75" s="44">
         <f t="shared" si="29"/>
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="61"/>
-      <c r="B76" s="232" t="s">
+      <c r="B76" s="195" t="s">
         <v>228</v>
       </c>
-      <c r="C76" s="230">
+      <c r="C76" s="193">
         <v>2</v>
       </c>
-      <c r="D76" s="233" t="s">
+      <c r="D76" s="196" t="s">
         <v>229</v>
       </c>
-      <c r="E76" s="233"/>
+      <c r="E76" s="196"/>
       <c r="F76" s="79">
         <v>6.4000000000000003E-3</v>
       </c>
@@ -7943,11 +8025,11 @@
       </c>
       <c r="M76" s="125">
         <f t="shared" si="23"/>
-        <v>13741.286400000001</v>
+        <v>14473.944704</v>
       </c>
       <c r="N76" s="125">
         <f t="shared" si="24"/>
-        <v>4930.3497600000001</v>
+        <v>4920.1182719999997</v>
       </c>
       <c r="O76" s="125">
         <f t="shared" si="27"/>
@@ -7955,18 +8037,18 @@
       </c>
       <c r="P76" s="72">
         <f t="shared" si="28"/>
-        <v>89256.02</v>
+        <v>89979.02</v>
       </c>
       <c r="Q76" s="73">
         <f t="shared" si="25"/>
-        <v>91934.02</v>
+        <v>92678.02</v>
       </c>
       <c r="R76" s="44">
         <f t="shared" si="29"/>
         <v>0.02</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="61"/>
       <c r="B77" s="77" t="s">
         <v>230</v>
@@ -8005,11 +8087,11 @@
       </c>
       <c r="M77" s="125">
         <f t="shared" si="23"/>
-        <v>12238.333200000001</v>
+        <v>12890.857001999999</v>
       </c>
       <c r="N77" s="125">
         <f t="shared" si="24"/>
-        <v>4391.0927550000006</v>
+        <v>4381.9803359999996</v>
       </c>
       <c r="O77" s="125">
         <f t="shared" si="27"/>
@@ -8017,18 +8099,18 @@
       </c>
       <c r="P77" s="72">
         <f t="shared" si="28"/>
-        <v>37149.03</v>
+        <v>37793.03</v>
       </c>
       <c r="Q77" s="73">
         <f t="shared" si="25"/>
-        <v>38263.03</v>
+        <v>38927.03</v>
       </c>
       <c r="R77" s="44">
         <f t="shared" si="29"/>
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="61"/>
       <c r="B78" s="77" t="s">
         <v>232</v>
@@ -8065,11 +8147,11 @@
       </c>
       <c r="M78" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N78" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O78" s="125">
         <f t="shared" si="27"/>
@@ -8077,18 +8159,18 @@
       </c>
       <c r="P78" s="72">
         <f t="shared" si="28"/>
-        <v>73915.039999999994</v>
+        <v>74514.039999999994</v>
       </c>
       <c r="Q78" s="73">
         <f t="shared" si="25"/>
-        <v>76132.039999999994</v>
+        <v>76749.039999999994</v>
       </c>
       <c r="R78" s="44">
         <f t="shared" si="29"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="61"/>
       <c r="B79" s="77" t="s">
         <v>233</v>
@@ -8130,11 +8212,11 @@
       </c>
       <c r="M79" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N79" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O79" s="125">
         <f t="shared" si="27"/>
@@ -8142,18 +8224,18 @@
       </c>
       <c r="P79" s="72">
         <f t="shared" si="28"/>
-        <v>34542.050000000003</v>
+        <v>35141.050000000003</v>
       </c>
       <c r="Q79" s="73">
         <f t="shared" si="25"/>
-        <v>35578.050000000003</v>
+        <v>36195.050000000003</v>
       </c>
       <c r="R79" s="44">
         <f t="shared" si="29"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="61"/>
       <c r="B80" s="77" t="s">
         <v>234</v>
@@ -8195,11 +8277,11 @@
       </c>
       <c r="M80" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N80" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O80" s="125">
         <f t="shared" si="27"/>
@@ -8207,21 +8289,21 @@
       </c>
       <c r="P80" s="72">
         <f t="shared" si="28"/>
-        <v>27035.06</v>
+        <v>27634.06</v>
       </c>
       <c r="Q80" s="73">
         <f t="shared" si="25"/>
-        <v>27846.06</v>
+        <v>28463.06</v>
       </c>
       <c r="R80" s="44">
         <f t="shared" si="29"/>
         <v>0.06</v>
       </c>
-      <c r="S80" s="169" t="s">
+      <c r="S80" s="168" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="61">
         <v>12</v>
       </c>
@@ -8265,11 +8347,11 @@
       </c>
       <c r="M81" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N81" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O81" s="125">
         <f t="shared" si="27"/>
@@ -8277,18 +8359,18 @@
       </c>
       <c r="P81" s="72">
         <f t="shared" si="28"/>
-        <v>34542.07</v>
+        <v>35141.07</v>
       </c>
       <c r="Q81" s="73">
         <f t="shared" si="25"/>
-        <v>35578.07</v>
+        <v>36195.07</v>
       </c>
       <c r="R81" s="44">
         <f t="shared" si="29"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="61">
         <v>12</v>
       </c>
@@ -8301,7 +8383,7 @@
       <c r="D82" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="E82" s="171"/>
+      <c r="E82" s="170"/>
       <c r="F82" s="79">
         <v>5.3E-3</v>
       </c>
@@ -8327,11 +8409,11 @@
       </c>
       <c r="M82" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N82" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O82" s="125">
         <f t="shared" si="27"/>
@@ -8339,18 +8421,18 @@
       </c>
       <c r="P82" s="72">
         <f t="shared" si="28"/>
-        <v>233198.07999999999</v>
+        <v>233796.08</v>
       </c>
       <c r="Q82" s="73">
         <f t="shared" si="25"/>
-        <v>240194.08</v>
+        <v>240810.08</v>
       </c>
       <c r="R82" s="44">
         <f t="shared" si="29"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="61">
         <v>12</v>
       </c>
@@ -8392,11 +8474,11 @@
       </c>
       <c r="M83" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N83" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O83" s="125">
         <f t="shared" si="27"/>
@@ -8404,18 +8486,18 @@
       </c>
       <c r="P83" s="72">
         <f t="shared" si="28"/>
-        <v>161875.09</v>
+        <v>162474.09</v>
       </c>
       <c r="Q83" s="73">
         <f t="shared" si="25"/>
-        <v>166731.09</v>
+        <v>167348.09</v>
       </c>
       <c r="R83" s="44">
         <f t="shared" si="29"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="61"/>
       <c r="B84" s="76" t="s">
         <v>240</v>
@@ -8452,11 +8534,11 @@
       </c>
       <c r="M84" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N84" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O84" s="125">
         <f t="shared" si="27"/>
@@ -8464,18 +8546,18 @@
       </c>
       <c r="P84" s="72">
         <f t="shared" si="28"/>
-        <v>335361.09999999998</v>
+        <v>335960.1</v>
       </c>
       <c r="Q84" s="73">
         <f t="shared" si="25"/>
-        <v>345422.1</v>
+        <v>346039.1</v>
       </c>
       <c r="R84" s="44">
         <f t="shared" si="29"/>
         <v>0.1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="61"/>
       <c r="B85" s="76" t="s">
         <v>241</v>
@@ -8483,13 +8565,13 @@
       <c r="C85" s="76">
         <v>11</v>
       </c>
-      <c r="D85" s="178" t="s">
+      <c r="D85" s="176" t="s">
         <v>168</v>
       </c>
-      <c r="E85" s="178" t="s">
-        <v>271</v>
-      </c>
-      <c r="F85" s="179">
+      <c r="E85" s="176" t="s">
+        <v>264</v>
+      </c>
+      <c r="F85" s="177">
         <v>5.3E-3</v>
       </c>
       <c r="G85" s="69">
@@ -8516,11 +8598,11 @@
       </c>
       <c r="M85" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N85" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O85" s="125">
         <f t="shared" si="27"/>
@@ -8528,18 +8610,18 @@
       </c>
       <c r="P85" s="72">
         <f t="shared" si="28"/>
-        <v>126011.11</v>
+        <v>126609.11</v>
       </c>
       <c r="Q85" s="73">
         <f t="shared" si="25"/>
-        <v>129791.11</v>
+        <v>130407.11</v>
       </c>
       <c r="R85" s="44">
         <f t="shared" si="29"/>
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="61"/>
       <c r="B86" s="76" t="s">
         <v>242</v>
@@ -8547,7 +8629,7 @@
       <c r="C86" s="76">
         <v>12</v>
       </c>
-      <c r="D86" s="172" t="s">
+      <c r="D86" s="171" t="s">
         <v>119</v>
       </c>
       <c r="E86" s="60" t="s">
@@ -8581,11 +8663,11 @@
       </c>
       <c r="M86" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N86" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O86" s="125">
         <f t="shared" si="27"/>
@@ -8593,18 +8675,18 @@
       </c>
       <c r="P86" s="72">
         <f t="shared" si="28"/>
-        <v>34542.120000000003</v>
+        <v>35141.120000000003</v>
       </c>
       <c r="Q86" s="73">
         <f t="shared" si="25"/>
-        <v>35578.120000000003</v>
+        <v>36195.120000000003</v>
       </c>
       <c r="R86" s="44">
         <f t="shared" si="29"/>
         <v>0.12</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="61"/>
       <c r="B87" s="61" t="s">
         <v>243</v>
@@ -8612,11 +8694,11 @@
       <c r="C87" s="61">
         <v>13</v>
       </c>
-      <c r="D87" s="180" t="s">
+      <c r="D87" s="178" t="s">
         <v>141</v>
       </c>
-      <c r="E87" s="181"/>
-      <c r="F87" s="179">
+      <c r="E87" s="179"/>
+      <c r="F87" s="177">
         <v>5.3E-3</v>
       </c>
       <c r="G87" s="69">
@@ -8644,11 +8726,11 @@
       </c>
       <c r="M87" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N87" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O87" s="125">
         <f t="shared" si="27"/>
@@ -8656,18 +8738,18 @@
       </c>
       <c r="P87" s="72">
         <f t="shared" si="28"/>
-        <v>34542.129999999997</v>
+        <v>35141.129999999997</v>
       </c>
       <c r="Q87" s="73">
         <f t="shared" si="25"/>
-        <v>35578.129999999997</v>
+        <v>36195.129999999997</v>
       </c>
       <c r="R87" s="44">
         <f t="shared" si="29"/>
         <v>0.13</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="61"/>
       <c r="B88" s="61" t="s">
         <v>244</v>
@@ -8675,7 +8757,7 @@
       <c r="C88" s="61">
         <v>14</v>
       </c>
-      <c r="D88" s="172" t="s">
+      <c r="D88" s="171" t="s">
         <v>129</v>
       </c>
       <c r="E88" s="74" t="s">
@@ -8709,11 +8791,11 @@
       </c>
       <c r="M88" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N88" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O88" s="125">
         <f t="shared" si="27"/>
@@ -8721,18 +8803,18 @@
       </c>
       <c r="P88" s="72">
         <f t="shared" si="28"/>
-        <v>27298.14</v>
+        <v>27897.14</v>
       </c>
       <c r="Q88" s="73">
         <f t="shared" si="25"/>
-        <v>28117.14</v>
+        <v>28734.14</v>
       </c>
       <c r="R88" s="44">
         <f t="shared" si="29"/>
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="61"/>
       <c r="B89" s="61" t="s">
         <v>246</v>
@@ -8740,7 +8822,7 @@
       <c r="C89" s="61">
         <v>15</v>
       </c>
-      <c r="D89" s="172" t="s">
+      <c r="D89" s="171" t="s">
         <v>111</v>
       </c>
       <c r="E89" s="74" t="str">
@@ -8775,11 +8857,11 @@
       </c>
       <c r="M89" s="125">
         <f t="shared" si="23"/>
-        <v>11379.5028</v>
+        <v>11986.235457999999</v>
       </c>
       <c r="N89" s="125">
         <f t="shared" si="24"/>
-        <v>4082.9458950000003</v>
+        <v>4074.4729440000001</v>
       </c>
       <c r="O89" s="125">
         <f t="shared" si="27"/>
@@ -8787,18 +8869,18 @@
       </c>
       <c r="P89" s="72">
         <f t="shared" si="28"/>
-        <v>34542.15</v>
+        <v>35141.15</v>
       </c>
       <c r="Q89" s="73">
         <f t="shared" si="25"/>
-        <v>35578.15</v>
+        <v>36195.15</v>
       </c>
       <c r="R89" s="44">
         <f t="shared" si="29"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="60"/>
       <c r="B90" s="60" t="s">
         <v>247</v>
@@ -8813,11 +8895,11 @@
       <c r="F90" s="68">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="G90" s="149">
+      <c r="G90" s="148">
         <v>44717.16</v>
       </c>
       <c r="H90" s="118"/>
-      <c r="I90" s="150">
+      <c r="I90" s="149">
         <f t="shared" si="20"/>
         <v>44717.16</v>
       </c>
@@ -8835,11 +8917,11 @@
       </c>
       <c r="M90" s="125">
         <f t="shared" si="23"/>
-        <v>13311.8712</v>
+        <v>14021.633931999999</v>
       </c>
       <c r="N90" s="125">
         <f t="shared" si="24"/>
-        <v>4776.2763299999997</v>
+        <v>4766.3645759999999</v>
       </c>
       <c r="O90" s="125">
         <f t="shared" si="27"/>
@@ -8847,226 +8929,234 @@
       </c>
       <c r="P90" s="72">
         <f t="shared" si="28"/>
-        <v>86467.16</v>
+        <v>87167.16</v>
       </c>
       <c r="Q90" s="73">
         <f t="shared" si="25"/>
-        <v>89061.16</v>
+        <v>89782.16</v>
       </c>
       <c r="R90" s="44">
         <f t="shared" si="29"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="61"/>
       <c r="B91" s="138"/>
       <c r="C91" s="138"/>
       <c r="D91" s="138"/>
       <c r="E91" s="138"/>
-      <c r="F91" s="151"/>
-      <c r="G91" s="152"/>
-      <c r="H91" s="153"/>
-      <c r="I91" s="154"/>
-      <c r="J91" s="155"/>
-      <c r="K91" s="156"/>
-      <c r="L91" s="157"/>
-      <c r="M91" s="157"/>
-      <c r="N91" s="157"/>
-      <c r="O91" s="157"/>
-      <c r="P91" s="158"/>
-      <c r="Q91" s="158"/>
+      <c r="F91" s="150"/>
+      <c r="G91" s="151"/>
+      <c r="H91" s="152"/>
+      <c r="I91" s="153"/>
+      <c r="J91" s="154"/>
+      <c r="K91" s="155"/>
+      <c r="L91" s="156"/>
+      <c r="M91" s="156"/>
+      <c r="N91" s="156"/>
+      <c r="O91" s="156"/>
+      <c r="P91" s="157"/>
+      <c r="Q91" s="157"/>
       <c r="R91" s="44"/>
     </row>
-    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="80"/>
-      <c r="B92" s="159"/>
-      <c r="C92" s="160"/>
-      <c r="D92" s="161"/>
-      <c r="E92" s="161"/>
-      <c r="F92" s="162">
+      <c r="B92" s="158"/>
+      <c r="C92" s="159"/>
+      <c r="D92" s="160"/>
+      <c r="E92" s="160"/>
+      <c r="F92" s="161">
         <f t="shared" ref="F92:L92" si="30">SUM(F5:F91)</f>
         <v>0.99999999999999956</v>
       </c>
-      <c r="G92" s="163">
+      <c r="G92" s="162">
         <f t="shared" si="30"/>
         <v>13317175.699999997</v>
       </c>
-      <c r="H92" s="164">
+      <c r="H92" s="163">
         <f t="shared" si="30"/>
         <v>6886831.2500000009</v>
       </c>
-      <c r="I92" s="165">
+      <c r="I92" s="164">
         <f t="shared" si="30"/>
         <v>6430344.4500000002</v>
       </c>
-      <c r="J92" s="166">
+      <c r="J92" s="165">
         <f t="shared" si="30"/>
         <v>197632.69379999998</v>
       </c>
-      <c r="K92" s="166">
+      <c r="K92" s="165">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L92" s="167">
+      <c r="L92" s="166">
         <f t="shared" si="30"/>
         <v>3600000</v>
       </c>
-      <c r="M92" s="167">
+      <c r="M92" s="166">
         <f>SUM(M5:M90)</f>
-        <v>2147075.9999999967</v>
-      </c>
-      <c r="N92" s="167">
+        <v>2261553.8600000041</v>
+      </c>
+      <c r="N92" s="166">
         <f>SUM(N5:N90)</f>
-        <v>770367.15</v>
-      </c>
-      <c r="O92" s="167">
+        <v>768768.48000000021</v>
+      </c>
+      <c r="O92" s="166">
         <f>SUM(O5:O90)</f>
         <v>0</v>
       </c>
-      <c r="P92" s="168">
+      <c r="P92" s="167">
         <f>SUM(P5:P91)</f>
-        <v>13145437.699999997</v>
-      </c>
-      <c r="Q92" s="168">
+        <v>13258339.699999997</v>
+      </c>
+      <c r="Q92" s="167">
         <f>SUM(Q5:Q91)</f>
-        <v>13539810.699999997</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+        <v>13656092.699999997</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D93" s="50"/>
       <c r="E93" s="50"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D94" s="209" t="s">
-        <v>273</v>
-      </c>
-      <c r="E94" s="209"/>
-      <c r="F94" s="209"/>
-      <c r="G94" s="209"/>
-      <c r="H94" s="209"/>
-      <c r="I94" s="209"/>
-      <c r="J94" s="209"/>
-      <c r="K94" s="209"/>
-      <c r="L94" s="209"/>
-      <c r="M94" s="209"/>
-      <c r="N94" s="209"/>
-      <c r="O94" s="209"/>
-      <c r="P94" s="209"/>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D95" s="209"/>
-      <c r="E95" s="209"/>
-      <c r="F95" s="209"/>
-      <c r="G95" s="209"/>
-      <c r="H95" s="209"/>
-      <c r="I95" s="209"/>
-      <c r="J95" s="209"/>
-      <c r="K95" s="209"/>
-      <c r="L95" s="209"/>
-      <c r="M95" s="209"/>
-      <c r="N95" s="209"/>
-      <c r="O95" s="209"/>
-      <c r="P95" s="209"/>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D94" s="228" t="s">
+        <v>266</v>
+      </c>
+      <c r="E94" s="228"/>
+      <c r="F94" s="228"/>
+      <c r="G94" s="228"/>
+      <c r="H94" s="228"/>
+      <c r="I94" s="228"/>
+      <c r="J94" s="228"/>
+      <c r="K94" s="228"/>
+      <c r="L94" s="228"/>
+      <c r="M94" s="228"/>
+      <c r="N94" s="228"/>
+      <c r="O94" s="228"/>
+      <c r="P94" s="228"/>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D95" s="228"/>
+      <c r="E95" s="228"/>
+      <c r="F95" s="228"/>
+      <c r="G95" s="228"/>
+      <c r="H95" s="228"/>
+      <c r="I95" s="228"/>
+      <c r="J95" s="228"/>
+      <c r="K95" s="228"/>
+      <c r="L95" s="228"/>
+      <c r="M95" s="228"/>
+      <c r="N95" s="228"/>
+      <c r="O95" s="228"/>
+      <c r="P95" s="228"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="H96" s="119"/>
     </row>
-    <row r="97" spans="4:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="194" t="str">
+    <row r="97" spans="4:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D97" s="207" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</v>
       </c>
-      <c r="E97" s="195"/>
-      <c r="F97" s="195"/>
-      <c r="G97" s="195"/>
-      <c r="H97" s="195"/>
-      <c r="I97" s="195"/>
-      <c r="J97" s="195"/>
-      <c r="K97" s="195"/>
-      <c r="L97" s="195"/>
-      <c r="M97" s="195"/>
-      <c r="N97" s="195"/>
-      <c r="O97" s="195"/>
-      <c r="P97" s="195"/>
-    </row>
-    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="195"/>
-      <c r="E98" s="195"/>
-      <c r="F98" s="195"/>
-      <c r="G98" s="195"/>
-      <c r="H98" s="195"/>
-      <c r="I98" s="195"/>
-      <c r="J98" s="195"/>
-      <c r="K98" s="195"/>
-      <c r="L98" s="195"/>
-      <c r="M98" s="195"/>
-      <c r="N98" s="195"/>
-      <c r="O98" s="195"/>
-      <c r="P98" s="195"/>
-    </row>
-    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="195"/>
-      <c r="E99" s="195"/>
-      <c r="F99" s="195"/>
-      <c r="G99" s="195"/>
-      <c r="H99" s="195"/>
-      <c r="I99" s="195"/>
-      <c r="J99" s="195"/>
-      <c r="K99" s="195"/>
-      <c r="L99" s="195"/>
-      <c r="M99" s="195"/>
-      <c r="N99" s="195"/>
-      <c r="O99" s="195"/>
-      <c r="P99" s="195"/>
-    </row>
-    <row r="100" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D100" s="195"/>
-      <c r="E100" s="195"/>
-      <c r="F100" s="195"/>
-      <c r="G100" s="195"/>
-      <c r="H100" s="195"/>
-      <c r="I100" s="195"/>
-      <c r="J100" s="195"/>
-      <c r="K100" s="195"/>
-      <c r="L100" s="195"/>
-      <c r="M100" s="195"/>
-      <c r="N100" s="195"/>
-      <c r="O100" s="195"/>
-      <c r="P100" s="195"/>
-    </row>
-    <row r="101" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D101" s="195"/>
-      <c r="E101" s="195"/>
-      <c r="F101" s="195"/>
-      <c r="G101" s="195"/>
-      <c r="H101" s="195"/>
-      <c r="I101" s="195"/>
-      <c r="J101" s="195"/>
-      <c r="K101" s="195"/>
-      <c r="L101" s="195"/>
-      <c r="M101" s="195"/>
-      <c r="N101" s="195"/>
-      <c r="O101" s="195"/>
-      <c r="P101" s="195"/>
-    </row>
-    <row r="102" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="195"/>
-      <c r="E102" s="195"/>
-      <c r="F102" s="195"/>
-      <c r="G102" s="195"/>
-      <c r="H102" s="195"/>
-      <c r="I102" s="195"/>
-      <c r="J102" s="195"/>
-      <c r="K102" s="195"/>
-      <c r="L102" s="195"/>
-      <c r="M102" s="195"/>
-      <c r="N102" s="195"/>
-      <c r="O102" s="195"/>
-      <c r="P102" s="195"/>
+      <c r="E97" s="202"/>
+      <c r="F97" s="202"/>
+      <c r="G97" s="202"/>
+      <c r="H97" s="202"/>
+      <c r="I97" s="202"/>
+      <c r="J97" s="202"/>
+      <c r="K97" s="202"/>
+      <c r="L97" s="202"/>
+      <c r="M97" s="202"/>
+      <c r="N97" s="202"/>
+      <c r="O97" s="202"/>
+      <c r="P97" s="202"/>
+    </row>
+    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D98" s="202"/>
+      <c r="E98" s="202"/>
+      <c r="F98" s="202"/>
+      <c r="G98" s="202"/>
+      <c r="H98" s="202"/>
+      <c r="I98" s="202"/>
+      <c r="J98" s="202"/>
+      <c r="K98" s="202"/>
+      <c r="L98" s="202"/>
+      <c r="M98" s="202"/>
+      <c r="N98" s="202"/>
+      <c r="O98" s="202"/>
+      <c r="P98" s="202"/>
+    </row>
+    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D99" s="202"/>
+      <c r="E99" s="202"/>
+      <c r="F99" s="202"/>
+      <c r="G99" s="202"/>
+      <c r="H99" s="202"/>
+      <c r="I99" s="202"/>
+      <c r="J99" s="202"/>
+      <c r="K99" s="202"/>
+      <c r="L99" s="202"/>
+      <c r="M99" s="202"/>
+      <c r="N99" s="202"/>
+      <c r="O99" s="202"/>
+      <c r="P99" s="202"/>
+    </row>
+    <row r="100" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D100" s="202"/>
+      <c r="E100" s="202"/>
+      <c r="F100" s="202"/>
+      <c r="G100" s="202"/>
+      <c r="H100" s="202"/>
+      <c r="I100" s="202"/>
+      <c r="J100" s="202"/>
+      <c r="K100" s="202"/>
+      <c r="L100" s="202"/>
+      <c r="M100" s="202"/>
+      <c r="N100" s="202"/>
+      <c r="O100" s="202"/>
+      <c r="P100" s="202"/>
+    </row>
+    <row r="101" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D101" s="202"/>
+      <c r="E101" s="202"/>
+      <c r="F101" s="202"/>
+      <c r="G101" s="202"/>
+      <c r="H101" s="202"/>
+      <c r="I101" s="202"/>
+      <c r="J101" s="202"/>
+      <c r="K101" s="202"/>
+      <c r="L101" s="202"/>
+      <c r="M101" s="202"/>
+      <c r="N101" s="202"/>
+      <c r="O101" s="202"/>
+      <c r="P101" s="202"/>
+    </row>
+    <row r="102" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D102" s="202"/>
+      <c r="E102" s="202"/>
+      <c r="F102" s="202"/>
+      <c r="G102" s="202"/>
+      <c r="H102" s="202"/>
+      <c r="I102" s="202"/>
+      <c r="J102" s="202"/>
+      <c r="K102" s="202"/>
+      <c r="L102" s="202"/>
+      <c r="M102" s="202"/>
+      <c r="N102" s="202"/>
+      <c r="O102" s="202"/>
+      <c r="P102" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D94:P95"/>
+    <mergeCell ref="D97:P102"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="M2:N2"/>
@@ -9083,14 +9173,6 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D94:P95"/>
-    <mergeCell ref="D97:P102"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -9100,69 +9182,69 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8AEA40-856C-4C69-BDF8-B1FFAA30BA95}">
   <dimension ref="D3:I21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D3" s="119"/>
     </row>
-    <row r="4" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D4" s="119"/>
     </row>
-    <row r="5" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D5" s="119"/>
     </row>
-    <row r="6" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D6" s="119"/>
     </row>
-    <row r="7" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D7" s="119"/>
     </row>
-    <row r="8" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D8" s="190" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="9" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D8" s="187" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D9" s="119"/>
     </row>
-    <row r="10" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D10" s="119"/>
     </row>
-    <row r="11" spans="4:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="193" t="s">
-        <v>275</v>
-      </c>
-      <c r="E11" s="193"/>
-      <c r="F11" s="193"/>
-      <c r="G11" s="229" t="s">
-        <v>276</v>
-      </c>
-      <c r="H11" s="229"/>
-      <c r="I11" s="229"/>
-    </row>
-    <row r="12" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="190" t="s">
+        <v>268</v>
+      </c>
+      <c r="E11" s="190"/>
+      <c r="F11" s="190"/>
+      <c r="G11" s="231" t="s">
+        <v>269</v>
+      </c>
+      <c r="H11" s="231"/>
+      <c r="I11" s="231"/>
+    </row>
+    <row r="12" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D12" s="119"/>
     </row>
-    <row r="13" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D13" s="119"/>
     </row>
-    <row r="14" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D14" s="119"/>
     </row>
-    <row r="15" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D15" s="234" t="s">
-        <v>277</v>
-      </c>
-      <c r="E15" s="234"/>
-      <c r="F15" s="234"/>
-      <c r="G15" s="234"/>
-      <c r="H15" s="234"/>
-      <c r="I15" s="234"/>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D15" s="197" t="s">
+        <v>270</v>
+      </c>
+      <c r="E15" s="197"/>
+      <c r="F15" s="197"/>
+      <c r="G15" s="197"/>
+      <c r="H15" s="197"/>
+      <c r="I15" s="197"/>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D18" s="119"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D21" s="119"/>
       <c r="E21" s="119"/>
       <c r="F21" s="119"/>

--- a/VERGARA/Agosto/vergara Agosto.xlsx
+++ b/VERGARA/Agosto/vergara Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6200223E-875A-4425-92DC-23A35D930DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C074D26-6D2D-47EB-99CE-4A46321DC761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="282">
   <si>
     <t>MAIL: consorciovergara1670@gmail.com</t>
   </si>
@@ -774,18 +774,9 @@
     <t>S.S.31</t>
   </si>
   <si>
-    <t xml:space="preserve">Articulos de limpieza </t>
-  </si>
-  <si>
     <t>Luz Maria Alberio</t>
   </si>
   <si>
-    <t>Transf 09/06</t>
-  </si>
-  <si>
-    <t>PMC 09/06</t>
-  </si>
-  <si>
     <t>ESTE ES ROBIN</t>
   </si>
   <si>
@@ -793,33 +784,6 @@
   </si>
   <si>
     <t>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</t>
-  </si>
-  <si>
-    <t>Transf 17/07</t>
-  </si>
-  <si>
-    <t>Servisur - Reemplazo 1 plafon psio 9 - 1 plafon sala de medidores - 3 lamparas salade gas</t>
-  </si>
-  <si>
-    <t>Transf 21/07</t>
-  </si>
-  <si>
-    <t>Casa ruan - compra de materiales</t>
-  </si>
-  <si>
-    <t>Debito 03/07</t>
-  </si>
-  <si>
-    <t>Debito 16/07</t>
-  </si>
-  <si>
-    <t>Transf 28/07</t>
-  </si>
-  <si>
-    <t>Servisur - Mano de obra y materiales cambio de lamparas y plafones</t>
-  </si>
-  <si>
-    <t>No se abono</t>
   </si>
   <si>
     <t>Matias Zeolla</t>
@@ -835,14 +799,6 @@
     <t>EL MES PASADO PAGO BIEN EL 08/07  $145.692,44 Y LA PUSIMOS NO PAGA</t>
   </si>
   <si>
-    <t>PAGO LO QUE QUISO:</t>
-  </si>
-  <si>
-    <t>Departamento 4 D: $131653,48
-Cochera N° 30:        $34542,15
-Total abonado:        $166195,63.</t>
-  </si>
-  <si>
     <t>SE QUEJA POR MAIL DE DEUDA INEXISTENTE Y ADJUNTA COMPROBANTES</t>
   </si>
   <si>
@@ -858,18 +814,6 @@
     <t>Sindicatos mes de AGOSTO</t>
   </si>
   <si>
-    <t>Honorarios administracion - Mes de JULIO Y AGOSTO</t>
-  </si>
-  <si>
-    <t>NOS QUEDO PENDIENTE PARA AG0ST0+ UN GASTO DE 125MIL QUE NO SUPIMOS IDENTIFICA</t>
-  </si>
-  <si>
-    <t>Transf 22/08</t>
-  </si>
-  <si>
-    <t>Roxana goldemberg - carta decomento galpon</t>
-  </si>
-  <si>
     <t>Salvatierra matias - Desobstruccion y limpieza de todas las rejillas de desagote de pluvial y de ducha en terraza frente y contrafrente</t>
   </si>
   <si>
@@ -879,7 +823,58 @@
     <t>Transf 12/08</t>
   </si>
   <si>
-    <t>Santillan Anotnio Javer - Verificacion</t>
+    <t>Reemplazo por vacaciones Sr. Encargado - mes anterior</t>
+  </si>
+  <si>
+    <t>Espinola Cristian - Reparacion rampa tuerca accionadora</t>
+  </si>
+  <si>
+    <t>Transf 26/08</t>
+  </si>
+  <si>
+    <t>Compra bomba sumergible de napa</t>
+  </si>
+  <si>
+    <t>Transf 25/08</t>
+  </si>
+  <si>
+    <t>Santillan Anotnio Javer - Verificacion entradas de agua por corte AySa</t>
+  </si>
+  <si>
+    <t>Debito 01/09</t>
+  </si>
+  <si>
+    <t>Roxana goldemberg - carta decomento galpon (no recibida)</t>
+  </si>
+  <si>
+    <t>Transf 04/08</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Mes de JULIO -  AUN SE DEBE AGOSTO</t>
+  </si>
+  <si>
+    <t>Debito 06/08</t>
+  </si>
+  <si>
+    <t>PMC 12/08</t>
+  </si>
+  <si>
+    <t>Debito 13/08</t>
+  </si>
+  <si>
+    <t>Metrogas Plan de pagos cuota 9</t>
+  </si>
+  <si>
+    <t>Transf 14/08</t>
+  </si>
+  <si>
+    <t>2 meses</t>
+  </si>
+  <si>
+    <t>Transf 27/08</t>
+  </si>
+  <si>
+    <t>Doartero - Extracción rejillas y impermeabilizante de las mismas en terraza - Cambio de bajada de pluvial en piso 13 rotura de de columna y reconstrucción de la misma</t>
   </si>
 </sst>
 </file>
@@ -887,17 +882,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1084,8 +1079,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1154,25 +1156,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.749992370372631"/>
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1539,10 +1535,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1562,8 +1558,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1572,31 +1568,31 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1607,8 +1603,8 @@
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1623,18 +1619,18 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1652,35 +1648,35 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1688,11 +1684,11 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1703,14 +1699,14 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1726,57 +1722,51 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="12" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1785,52 +1775,46 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="19" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="14" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="14" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="14" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1853,27 +1837,36 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1888,7 +1881,7 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1899,35 +1892,42 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="19" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2289,20 +2289,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
       <c r="B1" s="65" t="s">
         <v>0</v>
@@ -2311,7 +2311,7 @@
       <c r="D1" s="65"/>
       <c r="E1" s="66"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="128" t="s">
         <v>1</v>
@@ -2320,7 +2320,7 @@
       <c r="D2" s="128"/>
       <c r="E2" s="67"/>
     </row>
-    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
       <c r="B3" s="129" t="s">
         <v>2</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E3" s="67"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -2342,18 +2342,18 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="198" t="s">
-        <v>272</v>
-      </c>
-      <c r="C5" s="199"/>
-      <c r="D5" s="199"/>
-      <c r="E5" s="200"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="194" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="196"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -2364,57 +2364,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="201" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="202"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="202"/>
-      <c r="C10" s="202"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="203" t="s">
-        <v>254</v>
-      </c>
-      <c r="B13" s="204"/>
-      <c r="C13" s="204"/>
-      <c r="D13" s="204"/>
-      <c r="E13" s="204"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="204"/>
-      <c r="B14" s="204"/>
-      <c r="C14" s="204"/>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="204"/>
-      <c r="B15" s="204"/>
-      <c r="C15" s="204"/>
-      <c r="D15" s="204"/>
-      <c r="E15" s="204"/>
-    </row>
-    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="204"/>
-      <c r="B16" s="204"/>
-      <c r="C16" s="204"/>
-      <c r="D16" s="204"/>
-      <c r="E16" s="204"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="197" t="s">
+        <v>257</v>
+      </c>
+      <c r="C8" s="198"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="198"/>
+      <c r="C9" s="198"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="198"/>
+      <c r="C10" s="198"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="199" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="200"/>
+      <c r="C13" s="200"/>
+      <c r="D13" s="200"/>
+      <c r="E13" s="200"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="200"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="200"/>
+      <c r="D14" s="200"/>
+      <c r="E14" s="200"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="200"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="200"/>
+      <c r="E15" s="200"/>
+    </row>
+    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="200"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="200"/>
+      <c r="E16" s="200"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2423,7 +2423,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
         <v>10</v>
       </c>
@@ -2432,42 +2432,42 @@
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="182">
-        <v>612874.4</v>
+      <c r="D22" s="232">
+        <v>620754.80000000005</v>
       </c>
       <c r="E22" s="85"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="182">
-        <v>-143013.39000000001</v>
+      <c r="D23" s="232">
+        <v>-144884.35999999999</v>
       </c>
       <c r="E23" s="85"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="182">
-        <v>0.99</v>
+      <c r="D24" s="232">
+        <v>0.56000000000000005</v>
       </c>
       <c r="E24" s="85"/>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="55" t="s">
         <v>14</v>
       </c>
@@ -2475,600 +2475,604 @@
       <c r="C25" s="55"/>
       <c r="D25" s="113">
         <f>SUM(D22:D24)</f>
-        <v>469862</v>
+        <v>475871.00000000006</v>
       </c>
       <c r="E25" s="86"/>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="25" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="52" t="s">
+        <v>264</v>
+      </c>
+      <c r="B26" s="174"/>
+      <c r="C26" s="174"/>
+      <c r="D26" s="233">
+        <v>125000</v>
+      </c>
+      <c r="E26" s="175"/>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="113">
+        <f>D26</f>
+        <v>125000</v>
+      </c>
+      <c r="E27" s="86"/>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="87">
-        <f>D25</f>
-        <v>469862</v>
-      </c>
-      <c r="F26" s="19"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="32" t="s">
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="87">
+        <f>D25+D27</f>
+        <v>600871</v>
+      </c>
+      <c r="F28" s="19"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="88"/>
-    </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="205" t="s">
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="88"/>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="201" t="s">
+        <v>259</v>
+      </c>
+      <c r="B30" s="202"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="232">
+        <v>35000</v>
+      </c>
+      <c r="E30" s="89" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="201" t="s">
         <v>273</v>
       </c>
-      <c r="B28" s="206"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="238">
-        <v>35000</v>
-      </c>
-      <c r="E28" s="89" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="205" t="s">
-        <v>275</v>
-      </c>
-      <c r="B29" s="206"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="182">
+      <c r="B31" s="202"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="232">
         <f>470000</f>
         <v>470000</v>
       </c>
-      <c r="E29" s="89" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="25" t="s">
+      <c r="E31" s="89" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="90">
-        <f>SUM(D28:D29)</f>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="90">
+        <f>SUM(D30:D31)</f>
         <v>505000</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="64"/>
-    </row>
-    <row r="32" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="147" t="s">
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="64"/>
+    </row>
+    <row r="34" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="144"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="173">
+      <c r="B34" s="141"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="234">
         <v>70868</v>
       </c>
-      <c r="E32" s="112"/>
-      <c r="G32" s="146"/>
-    </row>
-    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="205" t="s">
+      <c r="E34" s="112"/>
+      <c r="G34" s="143"/>
+    </row>
+    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="201" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="206"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="172">
+      <c r="B35" s="202"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="235">
         <v>719.9</v>
       </c>
-      <c r="E33" s="112"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="25" t="s">
+      <c r="E35" s="112"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="91">
-        <f>SUM(D32:D33)</f>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="91">
+        <f>SUM(D34:D35)</f>
         <v>71587.899999999994</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="32" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="92"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="92"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="136">
+      <c r="B38" s="5"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="236">
         <v>305360.62</v>
       </c>
-      <c r="E36" s="114" t="s">
-        <v>251</v>
-      </c>
-      <c r="G36" s="119"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+      <c r="E38" s="114" t="s">
+        <v>275</v>
+      </c>
+      <c r="G38" s="119"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5"/>
+      <c r="D39" s="235">
+        <v>27579.35</v>
+      </c>
+      <c r="E39" s="100" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="str">
+        <f>A39</f>
+        <v>Sindicatos mes de AGOSTO</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="235">
+        <v>52150.84</v>
+      </c>
+      <c r="E40" s="100" t="str">
+        <f>E39</f>
+        <v>Debito 13/08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="str">
+        <f>A40</f>
+        <v>Sindicatos mes de AGOSTO</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="235">
+        <v>3064.37</v>
+      </c>
+      <c r="E41" s="101" t="str">
+        <f>E39</f>
+        <v>Debito 13/08</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="91">
+        <f>SUM(D38:D41)</f>
+        <v>388155.17999999993</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="92"/>
+    </row>
+    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" s="52"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="235">
+        <v>1397945.12</v>
+      </c>
+      <c r="E44" s="98" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="235">
+        <v>100000</v>
+      </c>
+      <c r="E45" s="98" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="201" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="202"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="235">
+        <v>90474.73</v>
+      </c>
+      <c r="E46" s="98" t="s">
         <v>274</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="232">
-        <v>27579.35</v>
-      </c>
-      <c r="E37" s="100" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="str">
-        <f>A37</f>
-        <v>Sindicatos mes de AGOSTO</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="232">
-        <v>52150.84</v>
-      </c>
-      <c r="E38" s="100" t="str">
-        <f>E37</f>
-        <v>Debito 16/07</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="str">
-        <f>A38</f>
-        <v>Sindicatos mes de AGOSTO</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="232">
-        <v>3064.37</v>
-      </c>
-      <c r="E39" s="101" t="str">
-        <f>E37</f>
-        <v>Debito 16/07</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="91">
-        <f>SUM(D36:D39)</f>
-        <v>388155.17999999993</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="92"/>
-    </row>
-    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B42" s="52"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="172">
-        <v>1397945.13</v>
-      </c>
-      <c r="E42" s="98" t="s">
+    </row>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="91">
+        <f>SUM(D44:D46)</f>
+        <v>1588419.85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="94"/>
+    </row>
+    <row r="49" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="210" t="s">
+        <v>265</v>
+      </c>
+      <c r="B49" s="211"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="235">
+        <v>145000</v>
+      </c>
+      <c r="E49" s="173" t="s">
+        <v>266</v>
+      </c>
+      <c r="H49" s="119"/>
+    </row>
+    <row r="50" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="176" t="s">
+        <v>267</v>
+      </c>
+      <c r="B50" s="177"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="235">
+        <v>500000</v>
+      </c>
+      <c r="E50" s="173" t="s">
+        <v>268</v>
+      </c>
+      <c r="H50" s="119"/>
+    </row>
+    <row r="51" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="208" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="172" t="s">
+      <c r="B51" s="209"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="235">
+        <v>144600</v>
+      </c>
+      <c r="E51" s="173" t="s">
+        <v>262</v>
+      </c>
+      <c r="H51" s="119"/>
+    </row>
+    <row r="52" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="176" t="s">
+        <v>269</v>
+      </c>
+      <c r="B52" s="177"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="235">
+        <v>120000</v>
+      </c>
+      <c r="E52" s="173" t="s">
         <v>263</v>
       </c>
-      <c r="E43" s="98"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="205" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" s="206"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="172">
-        <v>88711.15</v>
-      </c>
-      <c r="E44" s="98" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="91">
-        <f>SUM(D42:D44)</f>
-        <v>1486656.2799999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="94"/>
-    </row>
-    <row r="47" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="205" t="s">
-        <v>262</v>
-      </c>
-      <c r="B47" s="206"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="172">
-        <v>76500</v>
-      </c>
-      <c r="E47" s="145" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="205" t="s">
-        <v>258</v>
-      </c>
-      <c r="B48" s="206"/>
-      <c r="C48" s="54"/>
-      <c r="D48" s="172">
-        <v>16500</v>
-      </c>
-      <c r="E48" s="233" t="s">
-        <v>257</v>
-      </c>
-      <c r="H48" s="142" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="191"/>
-      <c r="B49" s="192"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="232">
-        <v>19000</v>
-      </c>
-      <c r="E49" s="233" t="s">
-        <v>277</v>
-      </c>
-      <c r="H49" s="119"/>
-    </row>
-    <row r="50" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="191" t="s">
-        <v>278</v>
-      </c>
-      <c r="B50" s="192"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="232">
-        <v>74376</v>
-      </c>
-      <c r="E50" s="233" t="s">
-        <v>277</v>
-      </c>
-      <c r="H50" s="119"/>
-    </row>
-    <row r="51" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="234" t="s">
-        <v>279</v>
-      </c>
-      <c r="B51" s="235"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="232">
-        <v>144600</v>
-      </c>
-      <c r="E51" s="233" t="s">
+      <c r="H52" s="119"/>
+    </row>
+    <row r="53" spans="1:10" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="206" t="s">
+        <v>281</v>
+      </c>
+      <c r="B53" s="207"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="96">
+        <v>450000</v>
+      </c>
+      <c r="E53" s="142" t="s">
         <v>280</v>
       </c>
-      <c r="H51" s="119"/>
-    </row>
-    <row r="52" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="95" t="s">
-        <v>282</v>
-      </c>
-      <c r="B52" s="144"/>
-      <c r="C52" s="54"/>
-      <c r="D52" s="232">
-        <v>120000</v>
-      </c>
-      <c r="E52" s="233" t="s">
-        <v>281</v>
-      </c>
-      <c r="H52" s="119"/>
-    </row>
-    <row r="53" spans="1:10" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="208" t="s">
-        <v>256</v>
-      </c>
-      <c r="B53" s="209"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="172">
-        <v>60000</v>
-      </c>
-      <c r="E53" s="233" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="205" t="s">
-        <v>248</v>
-      </c>
-      <c r="B54" s="206"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="96">
-        <f>60650+58080</f>
-        <v>118730</v>
-      </c>
-      <c r="E54" s="145" t="s">
-        <v>255</v>
-      </c>
-      <c r="I54" s="205"/>
-      <c r="J54" s="206"/>
-    </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="25" t="s">
+      <c r="I53" s="201"/>
+      <c r="J53" s="202"/>
+    </row>
+    <row r="54" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B55" s="32"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="143">
-        <f>SUM(D47:D54)</f>
-        <v>629706</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="32" t="s">
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="178">
+        <f>SUM(D49:D53)</f>
+        <v>1359600</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="63"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="94"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B55" s="63"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="94"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="235">
+        <v>109198.01</v>
+      </c>
+      <c r="E56" s="102"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="172">
-        <v>107565.66</v>
-      </c>
-      <c r="E57" s="102"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="172">
-        <v>49082</v>
-      </c>
-      <c r="E58" s="99"/>
-    </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="51" t="s">
+      <c r="D57" s="235">
+        <v>56000</v>
+      </c>
+      <c r="E57" s="99"/>
+    </row>
+    <row r="58" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B59" s="51"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="103"/>
-      <c r="E59" s="91">
-        <f>SUM(D57:D58)</f>
-        <v>156647.66</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="85"/>
-      <c r="E60" s="104"/>
-    </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="28" t="s">
+      <c r="B58" s="51"/>
+      <c r="C58" s="51"/>
+      <c r="D58" s="103"/>
+      <c r="E58" s="91">
+        <f>SUM(D56:D57)</f>
+        <v>165198.01</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="85"/>
+      <c r="E59" s="104"/>
+    </row>
+    <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="105"/>
-      <c r="E61" s="134"/>
-    </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="1"/>
-      <c r="D62" s="106"/>
-      <c r="E62" s="107"/>
-      <c r="F62" s="44"/>
-      <c r="G62" s="139"/>
-    </row>
-    <row r="63" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="3" t="s">
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="133"/>
+    </row>
+    <row r="61" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+      <c r="D61" s="106"/>
+      <c r="E61" s="107"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="137"/>
+    </row>
+    <row r="62" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B63" s="9"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="108"/>
-      <c r="E63" s="133">
-        <f>(SUM(E26:E61))</f>
-        <v>3707615.02</v>
-      </c>
-      <c r="F63" s="132"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B62" s="9"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="108"/>
+      <c r="E62" s="193">
+        <f>(SUM(E28:E60))</f>
+        <v>4678831.9399999995</v>
+      </c>
+      <c r="F62" s="132"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D63" s="106"/>
+      <c r="E63" s="106"/>
+    </row>
+    <row r="64" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D64" s="106"/>
       <c r="E64" s="106"/>
     </row>
-    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D65" s="106"/>
-      <c r="E65" s="106"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="10" t="s">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B66" s="11"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="109"/>
-      <c r="E66" s="110"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="208"/>
-      <c r="B67" s="210"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="109"/>
+      <c r="E65" s="110"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="201" t="s">
+        <v>277</v>
+      </c>
+      <c r="B66" s="202"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="96">
+        <v>48523.32</v>
+      </c>
+      <c r="E66" s="93" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="95"/>
+      <c r="B67" s="97"/>
       <c r="C67" s="5"/>
       <c r="D67" s="96"/>
       <c r="E67" s="93"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="95"/>
-      <c r="B68" s="97"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="96"/>
-      <c r="E68" s="93"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="49"/>
-      <c r="B69" s="48"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="56"/>
-      <c r="E69" s="56">
-        <f>SUM(D67:D68)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="72" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="212" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="49"/>
+      <c r="B68" s="48"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="56">
+        <f>SUM(D66:D67)</f>
+        <v>48523.32</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="70" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="B72" s="199"/>
-      <c r="C72" s="199"/>
-      <c r="D72" s="200"/>
-      <c r="E72" s="140"/>
-    </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
+      <c r="B71" s="195"/>
+      <c r="C71" s="195"/>
+      <c r="D71" s="196"/>
+      <c r="E71" s="138"/>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="141">
-        <f>E69+E72</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="9"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="139">
+        <f>E68+E71</f>
+        <v>48523.32</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="B75" s="83">
+        <f>E62</f>
+        <v>4678831.9399999995</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="82" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B76" s="83">
-        <f>E63</f>
-        <v>3707615.02</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f>E62-E60</f>
+        <v>4678831.9399999995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="82" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B77" s="83">
-        <f>E63-E61</f>
-        <v>3707615.02</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f>E73-E71</f>
+        <v>48523.32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="82" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B78" s="83">
-        <f>E74-E72</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="82" t="s">
-        <v>46</v>
-      </c>
-      <c r="B79" s="83">
-        <f>E74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="45" t="s">
+        <f>E73</f>
+        <v>48523.32</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="B81" s="120"/>
-      <c r="C81" s="20"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="29" t="s">
+      <c r="B80" s="120"/>
+      <c r="C80" s="20"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B82" s="57">
-        <v>831778.51</v>
-      </c>
-      <c r="C82" s="22"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="21" t="s">
+      <c r="B81" s="57">
+        <v>1218489.6700000009</v>
+      </c>
+      <c r="C81" s="22"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B83" s="41">
+      <c r="B82" s="41">
         <f>PRORRATEO!H92</f>
-        <v>6886831.2500000009</v>
+        <v>6136186.074</v>
+      </c>
+      <c r="C82" s="20"/>
+    </row>
+    <row r="83" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="B83" s="47">
+        <f>-74376-19000</f>
+        <v>-93376</v>
       </c>
       <c r="C83" s="20"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="21" t="s">
         <v>50</v>
       </c>
@@ -3078,27 +3082,27 @@
       </c>
       <c r="C84" s="20"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="115" t="s">
         <v>51</v>
       </c>
       <c r="B85" s="47">
-        <f>-21080</f>
-        <v>-21080</v>
+        <f>-4372-5746</f>
+        <v>-10118</v>
       </c>
       <c r="C85" s="20"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="40" t="s">
         <v>52</v>
       </c>
       <c r="B86" s="47">
-        <f>-B77</f>
-        <v>-3707615.02</v>
+        <f>-B76</f>
+        <v>-4678831.9399999995</v>
       </c>
       <c r="C86" s="20"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="40" t="s">
         <v>53</v>
       </c>
@@ -3108,7 +3112,7 @@
       </c>
       <c r="C87" s="20"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="40" t="s">
         <v>54</v>
       </c>
@@ -3118,73 +3122,73 @@
       </c>
       <c r="C88" s="20"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="24" t="s">
         <v>55</v>
       </c>
       <c r="B89" s="47">
-        <f>-(B78)</f>
-        <v>0</v>
+        <f>-(B77)</f>
+        <v>-48523.32</v>
       </c>
       <c r="C89" s="20"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="123" t="s">
         <v>34</v>
       </c>
       <c r="B90" s="124">
-        <f>SUM(B82:B89)</f>
-        <v>959592.40000000084</v>
+        <f>SUM(B81:B89)</f>
+        <v>-506495.85599999846</v>
       </c>
       <c r="C90" s="23"/>
       <c r="D90" s="44"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B91" s="42"/>
       <c r="C91" s="23"/>
       <c r="D91" s="44"/>
       <c r="E91" s="121"/>
       <c r="F91" s="122"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B92" s="42"/>
       <c r="C92" s="23"/>
       <c r="D92" s="44"/>
       <c r="E92" s="121"/>
       <c r="F92" s="122"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="211" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="204" t="s">
         <v>56</v>
       </c>
-      <c r="B93" s="202"/>
-      <c r="C93" s="202"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="202"/>
-      <c r="B94" s="202"/>
-      <c r="C94" s="202"/>
-    </row>
-    <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B93" s="198"/>
+      <c r="C93" s="198"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="198"/>
+      <c r="B94" s="198"/>
+      <c r="C94" s="198"/>
+    </row>
+    <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="53"/>
-      <c r="B95" s="136"/>
+      <c r="B95" s="135"/>
       <c r="C95" s="35">
         <v>11948.17</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="53"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35"/>
     </row>
-    <row r="97" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="126"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35">
         <v>61209</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="45" t="s">
         <v>34</v>
       </c>
@@ -3194,56 +3198,54 @@
       </c>
       <c r="C98" s="46"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="207"/>
-      <c r="B100" s="202"/>
-      <c r="C100" s="202"/>
-      <c r="D100" s="202"/>
-      <c r="E100" s="202"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="202"/>
-      <c r="B101" s="202"/>
-      <c r="C101" s="202"/>
-      <c r="D101" s="202"/>
-      <c r="E101" s="202"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="202"/>
-      <c r="B102" s="202"/>
-      <c r="C102" s="202"/>
-      <c r="D102" s="202"/>
-      <c r="E102" s="202"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="202"/>
-      <c r="B103" s="202"/>
-      <c r="C103" s="202"/>
-      <c r="D103" s="202"/>
-      <c r="E103" s="202"/>
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="203"/>
+      <c r="B100" s="198"/>
+      <c r="C100" s="198"/>
+      <c r="D100" s="198"/>
+      <c r="E100" s="198"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="198"/>
+      <c r="B101" s="198"/>
+      <c r="C101" s="198"/>
+      <c r="D101" s="198"/>
+      <c r="E101" s="198"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="198"/>
+      <c r="B102" s="198"/>
+      <c r="C102" s="198"/>
+      <c r="D102" s="198"/>
+      <c r="E102" s="198"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="198"/>
+      <c r="B103" s="198"/>
+      <c r="C103" s="198"/>
+      <c r="D103" s="198"/>
+      <c r="E103" s="198"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="15">
     <mergeCell ref="A100:E103"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A93:C94"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A71:D71"/>
     <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A93:C94"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A54:B54"/>
     <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A49:B49"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3254,27 +3256,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T102"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
-    <col min="5" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.44140625" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" customWidth="1"/>
-    <col min="10" max="11" width="9.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="11.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.6640625" customWidth="1"/>
-    <col min="17" max="17" width="14.33203125" customWidth="1"/>
-    <col min="18" max="18" width="10.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="11" width="9.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="11.7109375" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" customWidth="1"/>
+    <col min="18" max="18" width="10.42578125" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3282,30 +3284,29 @@
       <c r="E1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="236">
+      <c r="F1" s="237">
         <v>2261553.86</v>
       </c>
-      <c r="G1" s="237"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="175" t="s">
+      <c r="G1" s="214"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="169" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="174"/>
-      <c r="M1" s="214">
-        <f>P1</f>
+      <c r="L1" s="168"/>
+      <c r="M1" s="213">
+        <v>4678831.9400000004</v>
+      </c>
+      <c r="N1" s="214"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="212">
         <v>3600000</v>
       </c>
-      <c r="N1" s="215"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="213">
-        <v>3600000</v>
-      </c>
-      <c r="Q1" s="202"/>
+      <c r="Q1" s="198"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3313,101 +3314,106 @@
       <c r="E2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="239">
+      <c r="F2" s="238">
         <v>768768.48</v>
       </c>
-      <c r="G2" s="240"/>
-      <c r="H2" s="174" t="s">
+      <c r="G2" s="216"/>
+      <c r="H2" s="168" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="216"/>
-      <c r="J2" s="217"/>
-      <c r="K2" s="174" t="s">
+      <c r="I2" s="215"/>
+      <c r="J2" s="216"/>
+      <c r="K2" s="168" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="174"/>
-      <c r="M2" s="216"/>
-      <c r="N2" s="217"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="224"/>
-    </row>
-    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="218" t="s">
+      <c r="L2" s="168"/>
+      <c r="M2" s="215">
+        <f>O2</f>
+        <v>48523.32</v>
+      </c>
+      <c r="N2" s="216"/>
+      <c r="O2" s="244">
+        <v>48523.32</v>
+      </c>
+      <c r="P2" s="222"/>
+      <c r="Q2" s="223"/>
+    </row>
+    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="217" t="s">
         <v>62</v>
       </c>
       <c r="B3" s="116"/>
-      <c r="C3" s="225" t="s">
+      <c r="C3" s="224" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="225" t="s">
+      <c r="D3" s="224" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="230" t="s">
+      <c r="E3" s="228" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="225" t="s">
+      <c r="F3" s="239" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="220" t="s">
+      <c r="G3" s="240" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="225" t="s">
+      <c r="H3" s="224" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="222" t="s">
+      <c r="I3" s="221" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="220" t="s">
+      <c r="J3" s="219" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="229" t="str">
+      <c r="K3" s="227" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="220" t="s">
+      <c r="L3" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="220" t="s">
+      <c r="M3" s="219" t="s">
         <v>71</v>
       </c>
-      <c r="N3" s="220" t="s">
+      <c r="N3" s="219" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="220" t="s">
+      <c r="O3" s="219" t="s">
         <v>73</v>
       </c>
       <c r="P3" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="Q3" s="227" t="s">
+      <c r="Q3" s="226" t="s">
         <v>75</v>
       </c>
       <c r="T3" s="44"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="219"/>
+    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="218"/>
       <c r="B4" s="117"/>
-      <c r="C4" s="226"/>
-      <c r="D4" s="226"/>
-      <c r="E4" s="221"/>
-      <c r="F4" s="226"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="226"/>
-      <c r="I4" s="221"/>
-      <c r="J4" s="221"/>
-      <c r="K4" s="226"/>
-      <c r="L4" s="221"/>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
+      <c r="C4" s="225"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="220"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="220"/>
+      <c r="J4" s="220"/>
+      <c r="K4" s="225"/>
+      <c r="L4" s="220"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
       <c r="P4" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/09</v>
       </c>
-      <c r="Q4" s="226"/>
-    </row>
-    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q4" s="225"/>
+    </row>
+    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="61"/>
       <c r="B5" s="61" t="s">
         <v>76</v>
@@ -3423,11 +3429,11 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G5" s="69">
-        <v>145692.32999999999</v>
+        <v>131652.32999999999</v>
       </c>
       <c r="H5" s="118">
         <f>G5</f>
-        <v>145692.32999999999</v>
+        <v>131652.32999999999</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" ref="I5:I36" si="0">G5-H5</f>
@@ -3439,11 +3445,11 @@
       </c>
       <c r="K5" s="71">
         <f t="shared" ref="K5:K36" si="2">M$2*F5</f>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" ref="L5:L36" si="3">M$1*F5</f>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M5" s="125">
         <f t="shared" ref="M5:M36" si="4">F$1*F5</f>
@@ -3459,18 +3465,18 @@
       </c>
       <c r="P5" s="72">
         <f t="shared" ref="P5:P36" si="7">ROUND(SUM(I5:O5),0) + R5</f>
-        <v>133933.32999999999</v>
+        <v>156705.32999999999</v>
       </c>
       <c r="Q5" s="73">
         <f t="shared" ref="Q5:Q36" si="8">ROUND(P5*3%,0) + P5</f>
-        <v>137951.32999999999</v>
+        <v>161406.32999999999</v>
       </c>
       <c r="R5" s="44">
         <f t="shared" ref="R5:R36" si="9">ROUND(0.001+C5/100,2)</f>
         <v>0.33</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="61"/>
       <c r="B6" s="61" t="s">
         <v>78</v>
@@ -3486,11 +3492,11 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G6" s="69">
-        <v>100253.34</v>
+        <v>90592.34</v>
       </c>
       <c r="H6" s="118">
         <f>G6</f>
-        <v>100253.34</v>
+        <v>90592.34</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
@@ -3502,11 +3508,11 @@
       </c>
       <c r="K6" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M6" s="125">
         <f t="shared" si="4"/>
@@ -3522,11 +3528,11 @@
       </c>
       <c r="P6" s="72">
         <f t="shared" si="7"/>
-        <v>92161.34</v>
+        <v>107832.34</v>
       </c>
       <c r="Q6" s="73">
         <f t="shared" si="8"/>
-        <v>94926.34</v>
+        <v>111067.34</v>
       </c>
       <c r="R6" s="44">
         <f t="shared" si="9"/>
@@ -3534,7 +3540,7 @@
       </c>
       <c r="S6" s="44"/>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="61">
         <v>1</v>
       </c>
@@ -3544,19 +3550,19 @@
       <c r="C7" s="61">
         <v>35</v>
       </c>
-      <c r="D7" s="176" t="s">
+      <c r="D7" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="179"/>
-      <c r="F7" s="177">
+      <c r="E7" s="74"/>
+      <c r="F7" s="179">
         <v>1.4200000000000001E-2</v>
       </c>
       <c r="G7" s="69">
-        <v>96180.35</v>
+        <v>92548.35</v>
       </c>
       <c r="H7" s="118">
         <f>G7</f>
-        <v>96180.35</v>
+        <v>92548.35</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
@@ -3568,11 +3574,11 @@
       </c>
       <c r="K7" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>689.03114400000004</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="3"/>
-        <v>51120</v>
+        <v>66439.413548000011</v>
       </c>
       <c r="M7" s="125">
         <f t="shared" si="4"/>
@@ -3588,18 +3594,18 @@
       </c>
       <c r="P7" s="72">
         <f t="shared" si="7"/>
-        <v>94151.35</v>
+        <v>110159.35</v>
       </c>
       <c r="Q7" s="73">
         <f t="shared" si="8"/>
-        <v>96976.35</v>
+        <v>113464.35</v>
       </c>
       <c r="R7" s="44">
         <f t="shared" si="9"/>
         <v>0.35</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="61">
         <v>2</v>
       </c>
@@ -3609,23 +3615,23 @@
       <c r="C8" s="61">
         <v>36</v>
       </c>
-      <c r="D8" s="176" t="s">
+      <c r="D8" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="179"/>
-      <c r="F8" s="177">
+      <c r="E8" s="74"/>
+      <c r="F8" s="179">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G8" s="69">
-        <v>136239.35999999999</v>
+        <v>127522.36</v>
       </c>
       <c r="H8" s="118">
-        <f>141812-H64</f>
-        <v>140369.78</v>
+        <f>132693.36-H64</f>
+        <v>131390.13999999998</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>-4130.4200000000128</v>
+        <v>-3867.7799999999843</v>
       </c>
       <c r="J8" s="70">
         <f t="shared" si="1"/>
@@ -3633,11 +3639,11 @@
       </c>
       <c r="K8" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M8" s="125">
         <f t="shared" si="4"/>
@@ -3653,11 +3659,11 @@
       </c>
       <c r="P8" s="72">
         <f t="shared" si="7"/>
-        <v>129802.36</v>
+        <v>152837.35999999999</v>
       </c>
       <c r="Q8" s="73">
         <f t="shared" si="8"/>
-        <v>133696.35999999999</v>
+        <v>157422.35999999999</v>
       </c>
       <c r="R8" s="44">
         <f t="shared" si="9"/>
@@ -3665,7 +3671,7 @@
       </c>
       <c r="T8" s="44"/>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="61">
         <v>3</v>
       </c>
@@ -3681,19 +3687,19 @@
       <c r="E9" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="68">
+      <c r="F9" s="179">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G9" s="69">
-        <v>116853.37</v>
+        <v>107147.37</v>
       </c>
       <c r="H9" s="118">
-        <f>24240.37+120239.37</f>
-        <v>144479.74</v>
+        <f>G9</f>
+        <v>107147.37</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" si="0"/>
-        <v>-27626.369999999995</v>
+        <v>0</v>
       </c>
       <c r="J9" s="70">
         <f t="shared" si="1"/>
@@ -3701,11 +3707,11 @@
       </c>
       <c r="K9" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L9" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M9" s="125">
         <f t="shared" si="4"/>
@@ -3721,11 +3727,11 @@
       </c>
       <c r="P9" s="72">
         <f t="shared" si="7"/>
-        <v>106306.37</v>
+        <v>156705.37</v>
       </c>
       <c r="Q9" s="73">
         <f t="shared" si="8"/>
-        <v>109495.37</v>
+        <v>161406.37</v>
       </c>
       <c r="R9" s="44">
         <f t="shared" si="9"/>
@@ -3733,7 +3739,7 @@
       </c>
       <c r="T9" s="44"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="61">
         <v>4</v>
       </c>
@@ -3749,15 +3755,15 @@
       <c r="E10" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="68">
+      <c r="F10" s="179">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G10" s="69">
-        <v>166932.38</v>
+        <v>90592.38</v>
       </c>
       <c r="H10" s="118">
-        <f>83573.38+16680+66679</f>
-        <v>166932.38</v>
+        <f>G10</f>
+        <v>90592.38</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
@@ -3769,11 +3775,11 @@
       </c>
       <c r="K10" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M10" s="125">
         <f t="shared" si="4"/>
@@ -3789,18 +3795,18 @@
       </c>
       <c r="P10" s="72">
         <f t="shared" si="7"/>
-        <v>92161.38</v>
+        <v>107832.38</v>
       </c>
       <c r="Q10" s="73">
         <f t="shared" si="8"/>
-        <v>94926.38</v>
+        <v>111067.38</v>
       </c>
       <c r="R10" s="44">
         <f t="shared" si="9"/>
         <v>0.38</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="61">
         <v>5</v>
       </c>
@@ -3814,14 +3820,15 @@
         <v>91</v>
       </c>
       <c r="E11" s="60"/>
-      <c r="F11" s="68">
+      <c r="F11" s="179">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G11" s="69">
-        <v>100253.39</v>
+        <v>90592.39</v>
       </c>
       <c r="H11" s="118">
-        <v>100253.39</v>
+        <f>G11</f>
+        <v>90592.39</v>
       </c>
       <c r="I11" s="70">
         <f t="shared" si="0"/>
@@ -3833,11 +3840,11 @@
       </c>
       <c r="K11" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L11" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M11" s="125">
         <f t="shared" si="4"/>
@@ -3853,18 +3860,18 @@
       </c>
       <c r="P11" s="72">
         <f t="shared" si="7"/>
-        <v>92161.39</v>
+        <v>107832.39</v>
       </c>
       <c r="Q11" s="73">
         <f t="shared" si="8"/>
-        <v>94926.39</v>
+        <v>111067.39</v>
       </c>
       <c r="R11" s="44">
         <f t="shared" si="9"/>
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="61">
         <v>6</v>
       </c>
@@ -3878,28 +3885,28 @@
         <v>93</v>
       </c>
       <c r="E12" s="74"/>
-      <c r="F12" s="68">
+      <c r="F12" s="179">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G12" s="69">
-        <v>145693.4</v>
+        <v>281717.40000000002</v>
       </c>
       <c r="H12" s="118"/>
       <c r="I12" s="70">
         <f t="shared" si="0"/>
-        <v>145693.4</v>
+        <v>281717.40000000002</v>
       </c>
       <c r="J12" s="70">
         <f t="shared" si="1"/>
-        <v>4370.8019999999997</v>
+        <v>8451.5220000000008</v>
       </c>
       <c r="K12" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L12" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M12" s="125">
         <f t="shared" si="4"/>
@@ -3915,18 +3922,18 @@
       </c>
       <c r="P12" s="72">
         <f t="shared" si="7"/>
-        <v>283997.40000000002</v>
+        <v>446874.4</v>
       </c>
       <c r="Q12" s="73">
         <f t="shared" si="8"/>
-        <v>292517.40000000002</v>
+        <v>460280.4</v>
       </c>
       <c r="R12" s="44">
         <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="61">
         <v>7</v>
       </c>
@@ -3936,36 +3943,36 @@
       <c r="C13" s="61">
         <v>41</v>
       </c>
-      <c r="D13" s="176" t="s">
+      <c r="D13" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="179" t="s">
+      <c r="E13" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="177">
+      <c r="F13" s="179">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G13" s="69">
-        <v>192089.41</v>
+        <v>204408.41</v>
       </c>
       <c r="H13" s="118">
-        <v>121453</v>
+        <v>131652.41</v>
       </c>
       <c r="I13" s="70">
         <f t="shared" si="0"/>
-        <v>70636.41</v>
+        <v>72756</v>
       </c>
       <c r="J13" s="70">
         <f t="shared" si="1"/>
-        <v>2119.0923000000003</v>
+        <v>2182.6799999999998</v>
       </c>
       <c r="K13" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L13" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M13" s="125">
         <f t="shared" si="4"/>
@@ -3981,18 +3988,18 @@
       </c>
       <c r="P13" s="72">
         <f t="shared" si="7"/>
-        <v>206688.41</v>
+        <v>231644.41</v>
       </c>
       <c r="Q13" s="73">
         <f t="shared" si="8"/>
-        <v>212889.41</v>
+        <v>238593.41</v>
       </c>
       <c r="R13" s="44">
         <f t="shared" si="9"/>
         <v>0.41</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="61">
         <v>8</v>
       </c>
@@ -4012,11 +4019,11 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G14" s="69">
-        <v>100253.42</v>
+        <v>90592.42</v>
       </c>
       <c r="H14" s="118">
         <f>G14</f>
-        <v>100253.42</v>
+        <v>90592.42</v>
       </c>
       <c r="I14" s="70">
         <f t="shared" si="0"/>
@@ -4028,11 +4035,11 @@
       </c>
       <c r="K14" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L14" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M14" s="125">
         <f t="shared" si="4"/>
@@ -4048,18 +4055,18 @@
       </c>
       <c r="P14" s="72">
         <f t="shared" si="7"/>
-        <v>92161.42</v>
+        <v>107832.42</v>
       </c>
       <c r="Q14" s="73">
         <f t="shared" si="8"/>
-        <v>94926.42</v>
+        <v>111067.42</v>
       </c>
       <c r="R14" s="44">
         <f t="shared" si="9"/>
         <v>0.42</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="61">
         <v>1</v>
       </c>
@@ -4079,11 +4086,11 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G15" s="69">
-        <v>100253.43</v>
+        <v>90592.43</v>
       </c>
       <c r="H15" s="118">
         <f>G15</f>
-        <v>100253.43</v>
+        <v>90592.43</v>
       </c>
       <c r="I15" s="70">
         <f t="shared" si="0"/>
@@ -4095,11 +4102,11 @@
       </c>
       <c r="K15" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L15" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M15" s="125">
         <f t="shared" si="4"/>
@@ -4115,18 +4122,18 @@
       </c>
       <c r="P15" s="72">
         <f t="shared" si="7"/>
-        <v>92161.43</v>
+        <v>107832.43</v>
       </c>
       <c r="Q15" s="73">
         <f t="shared" si="8"/>
-        <v>94926.43</v>
+        <v>111067.43</v>
       </c>
       <c r="R15" s="44">
         <f t="shared" si="9"/>
         <v>0.43</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="61">
         <v>1</v>
       </c>
@@ -4136,34 +4143,37 @@
       <c r="C16" s="61">
         <v>44</v>
       </c>
-      <c r="D16" s="183" t="s">
+      <c r="D16" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="184" t="s">
+      <c r="E16" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="185">
+      <c r="F16" s="179">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G16" s="186">
-        <v>145692.44</v>
-      </c>
-      <c r="H16" s="118"/>
+      <c r="G16" s="170">
+        <v>281716.44</v>
+      </c>
+      <c r="H16" s="118">
+        <f>145692.44+131652.44+4372</f>
+        <v>281716.88</v>
+      </c>
       <c r="I16" s="70">
         <f t="shared" si="0"/>
-        <v>145692.44</v>
+        <v>-0.44000000000232831</v>
       </c>
       <c r="J16" s="70">
         <f t="shared" si="1"/>
-        <v>4370.7731999999996</v>
+        <v>0</v>
       </c>
       <c r="K16" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L16" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M16" s="125">
         <f t="shared" si="4"/>
@@ -4179,18 +4189,18 @@
       </c>
       <c r="P16" s="72">
         <f t="shared" si="7"/>
-        <v>283996.44</v>
+        <v>156705.44</v>
       </c>
       <c r="Q16" s="73">
         <f t="shared" si="8"/>
-        <v>292516.44</v>
+        <v>161406.44</v>
       </c>
       <c r="R16" s="44">
         <f t="shared" si="9"/>
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="61">
         <v>2</v>
       </c>
@@ -4210,11 +4220,11 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G17" s="69">
-        <v>145692.45000000001</v>
+        <v>131652.45000000001</v>
       </c>
       <c r="H17" s="118">
         <f>G17</f>
-        <v>145692.45000000001</v>
+        <v>131652.45000000001</v>
       </c>
       <c r="I17" s="70">
         <f t="shared" si="0"/>
@@ -4226,11 +4236,11 @@
       </c>
       <c r="K17" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L17" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M17" s="125">
         <f t="shared" si="4"/>
@@ -4246,18 +4256,18 @@
       </c>
       <c r="P17" s="72">
         <f t="shared" si="7"/>
-        <v>133933.45000000001</v>
+        <v>156705.45000000001</v>
       </c>
       <c r="Q17" s="73">
         <f t="shared" si="8"/>
-        <v>137951.45000000001</v>
+        <v>161406.45000000001</v>
       </c>
       <c r="R17" s="44">
         <f t="shared" si="9"/>
         <v>0.45</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="61">
         <v>2</v>
       </c>
@@ -4277,11 +4287,11 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G18" s="69">
-        <v>100253.46</v>
+        <v>93310.46</v>
       </c>
       <c r="H18" s="118">
         <f>G18</f>
-        <v>100253.46</v>
+        <v>93310.46</v>
       </c>
       <c r="I18" s="70">
         <f t="shared" si="0"/>
@@ -4293,11 +4303,11 @@
       </c>
       <c r="K18" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L18" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M18" s="125">
         <f t="shared" si="4"/>
@@ -4313,11 +4323,11 @@
       </c>
       <c r="P18" s="72">
         <f t="shared" si="7"/>
-        <v>92161.46</v>
+        <v>107832.46</v>
       </c>
       <c r="Q18" s="73">
         <f t="shared" si="8"/>
-        <v>94926.46</v>
+        <v>111067.46</v>
       </c>
       <c r="R18" s="44">
         <f t="shared" si="9"/>
@@ -4325,7 +4335,7 @@
       </c>
       <c r="S18" s="119"/>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="61">
         <v>3</v>
       </c>
@@ -4339,33 +4349,33 @@
         <v>98</v>
       </c>
       <c r="E19" s="74" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="F19" s="68">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G19" s="69">
-        <v>95238.47</v>
+        <v>90593.47</v>
       </c>
       <c r="H19" s="118">
-        <f>95238</f>
-        <v>95238</v>
+        <f>G19</f>
+        <v>90593.47</v>
       </c>
       <c r="I19" s="70">
         <f t="shared" si="0"/>
-        <v>0.47000000000116415</v>
+        <v>0</v>
       </c>
       <c r="J19" s="70">
         <f t="shared" si="1"/>
-        <v>1.4100000000034925E-2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L19" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M19" s="125">
         <f t="shared" si="4"/>
@@ -4381,11 +4391,11 @@
       </c>
       <c r="P19" s="72">
         <f t="shared" si="7"/>
-        <v>92162.47</v>
+        <v>107832.47</v>
       </c>
       <c r="Q19" s="73">
         <f t="shared" si="8"/>
-        <v>94927.47</v>
+        <v>111067.47</v>
       </c>
       <c r="R19" s="44">
         <f t="shared" si="9"/>
@@ -4393,7 +4403,7 @@
       </c>
       <c r="S19" s="119"/>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="61">
         <v>3</v>
       </c>
@@ -4403,37 +4413,37 @@
       <c r="C20" s="61">
         <v>48</v>
       </c>
-      <c r="D20" s="188" t="s">
+      <c r="D20" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="188" t="s">
+      <c r="E20" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="F20" s="189">
+      <c r="F20" s="179">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G20" s="69">
-        <v>145692.48000000001</v>
+      <c r="G20" s="170">
+        <v>131653.48000000001</v>
       </c>
       <c r="H20" s="118">
-        <f>183918-H89</f>
-        <v>145691.85</v>
+        <f>166195.63-H89</f>
+        <v>131653.48000000001</v>
       </c>
       <c r="I20" s="70">
         <f t="shared" si="0"/>
-        <v>0.63000000000465661</v>
+        <v>0</v>
       </c>
       <c r="J20" s="70">
         <f t="shared" si="1"/>
-        <v>1.8900000000139697E-2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L20" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M20" s="125">
         <f t="shared" si="4"/>
@@ -4449,11 +4459,11 @@
       </c>
       <c r="P20" s="72">
         <f t="shared" si="7"/>
-        <v>133933.48000000001</v>
+        <v>156705.48000000001</v>
       </c>
       <c r="Q20" s="73">
         <f t="shared" si="8"/>
-        <v>137951.48000000001</v>
+        <v>161406.48000000001</v>
       </c>
       <c r="R20" s="44">
         <f t="shared" si="9"/>
@@ -4462,7 +4472,7 @@
       <c r="S20" s="119"/>
       <c r="T20" s="43"/>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="61">
         <v>4</v>
       </c>
@@ -4478,15 +4488,15 @@
       <c r="E21" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="F21" s="68">
+      <c r="F21" s="179">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G21" s="69">
-        <v>145692.49</v>
+      <c r="G21" s="170">
+        <v>131652.49</v>
       </c>
       <c r="H21" s="118">
         <f>G21</f>
-        <v>145692.49</v>
+        <v>131652.49</v>
       </c>
       <c r="I21" s="70">
         <f t="shared" si="0"/>
@@ -4498,11 +4508,11 @@
       </c>
       <c r="K21" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L21" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M21" s="125">
         <f t="shared" si="4"/>
@@ -4518,18 +4528,18 @@
       </c>
       <c r="P21" s="72">
         <f t="shared" si="7"/>
-        <v>133933.49</v>
+        <v>156705.49</v>
       </c>
       <c r="Q21" s="73">
         <f t="shared" si="8"/>
-        <v>137951.49</v>
+        <v>161406.49</v>
       </c>
       <c r="R21" s="44">
         <f t="shared" si="9"/>
         <v>0.49</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="61">
         <v>4</v>
       </c>
@@ -4542,31 +4552,31 @@
       <c r="D22" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="169"/>
+      <c r="E22" s="165"/>
       <c r="F22" s="68">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G22" s="69">
-        <v>574079.5</v>
+        <v>578894.5</v>
       </c>
       <c r="H22" s="118">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I22" s="70">
         <f t="shared" si="0"/>
-        <v>474079.5</v>
+        <v>378894.5</v>
       </c>
       <c r="J22" s="70">
         <f t="shared" si="1"/>
-        <v>14222.385</v>
+        <v>11366.834999999999</v>
       </c>
       <c r="K22" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L22" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M22" s="125">
         <f t="shared" si="4"/>
@@ -4582,18 +4592,18 @@
       </c>
       <c r="P22" s="72">
         <f t="shared" si="7"/>
-        <v>580463.5</v>
+        <v>498093.5</v>
       </c>
       <c r="Q22" s="73">
         <f t="shared" si="8"/>
-        <v>597877.5</v>
+        <v>513036.5</v>
       </c>
       <c r="R22" s="44">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="61">
         <v>5</v>
       </c>
@@ -4613,26 +4623,24 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G23" s="69">
-        <v>394277.51</v>
-      </c>
-      <c r="H23" s="118">
-        <v>448716.51</v>
-      </c>
+        <v>36153.51</v>
+      </c>
+      <c r="H23" s="118"/>
       <c r="I23" s="70">
         <f t="shared" si="0"/>
-        <v>-54439</v>
+        <v>36153.51</v>
       </c>
       <c r="J23" s="70">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1084.6052999999999</v>
       </c>
       <c r="K23" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L23" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M23" s="125">
         <f t="shared" si="4"/>
@@ -4648,18 +4656,18 @@
       </c>
       <c r="P23" s="72">
         <f t="shared" si="7"/>
-        <v>37722.51</v>
+        <v>145070.51</v>
       </c>
       <c r="Q23" s="73">
         <f t="shared" si="8"/>
-        <v>38854.51</v>
+        <v>149422.51</v>
       </c>
       <c r="R23" s="44">
         <f t="shared" si="9"/>
         <v>0.51</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="61">
         <v>5</v>
       </c>
@@ -4679,11 +4687,11 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G24" s="69">
-        <v>145692.51999999999</v>
+        <v>131652.51999999999</v>
       </c>
       <c r="H24" s="118">
-        <f>24240.52+121452</f>
-        <v>145692.51999999999</v>
+        <f>G24</f>
+        <v>131652.51999999999</v>
       </c>
       <c r="I24" s="84">
         <f t="shared" si="0"/>
@@ -4695,11 +4703,11 @@
       </c>
       <c r="K24" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L24" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M24" s="125">
         <f t="shared" si="4"/>
@@ -4715,83 +4723,82 @@
       </c>
       <c r="P24" s="72">
         <f t="shared" si="7"/>
-        <v>133933.51999999999</v>
+        <v>156705.51999999999</v>
       </c>
       <c r="Q24" s="73">
         <f t="shared" si="8"/>
-        <v>137951.51999999999</v>
+        <v>161406.51999999999</v>
       </c>
       <c r="R24" s="44">
         <f t="shared" si="9"/>
         <v>0.52</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="61">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="180">
         <v>6</v>
       </c>
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="180" t="s">
         <v>121</v>
       </c>
-      <c r="C25" s="61">
+      <c r="C25" s="180">
         <v>53</v>
       </c>
-      <c r="D25" s="60" t="s">
+      <c r="D25" s="180" t="s">
         <v>122</v>
       </c>
-      <c r="E25" s="74"/>
-      <c r="F25" s="68">
+      <c r="E25" s="189"/>
+      <c r="F25" s="181">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G25" s="69">
-        <v>141065.53</v>
-      </c>
-      <c r="H25" s="118">
-        <f>G25</f>
-        <v>141065.53</v>
-      </c>
-      <c r="I25" s="70">
+      <c r="G25" s="182">
+        <v>137951.53</v>
+      </c>
+      <c r="H25" s="230">
+        <v>135603.48000000001</v>
+      </c>
+      <c r="I25" s="183">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="70">
+        <v>2348.0499999999884</v>
+      </c>
+      <c r="J25" s="183">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="71">
+        <v>70.44149999999965</v>
+      </c>
+      <c r="K25" s="184">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="71">
+        <v>980.171064</v>
+      </c>
+      <c r="L25" s="184">
         <f t="shared" si="3"/>
-        <v>72720</v>
-      </c>
-      <c r="M25" s="125">
+        <v>94512.405188000004</v>
+      </c>
+      <c r="M25" s="185">
         <f t="shared" si="4"/>
         <v>45683.387971999997</v>
       </c>
-      <c r="N25" s="125">
+      <c r="N25" s="185">
         <f t="shared" si="5"/>
         <v>15529.123296</v>
       </c>
-      <c r="O25" s="125">
+      <c r="O25" s="185">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P25" s="72">
+      <c r="P25" s="186">
         <f t="shared" si="7"/>
-        <v>133933.53</v>
-      </c>
-      <c r="Q25" s="73">
+        <v>159124.53</v>
+      </c>
+      <c r="Q25" s="187">
         <f t="shared" si="8"/>
-        <v>137951.53</v>
+        <v>163898.53</v>
       </c>
       <c r="R25" s="44">
         <f t="shared" si="9"/>
         <v>0.53</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="61">
         <v>6</v>
       </c>
@@ -4811,11 +4818,11 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G26" s="69">
-        <v>97010.54</v>
+        <v>90592.54</v>
       </c>
       <c r="H26" s="118">
         <f>G26</f>
-        <v>97010.54</v>
+        <v>90592.54</v>
       </c>
       <c r="I26" s="70">
         <f t="shared" si="0"/>
@@ -4827,11 +4834,11 @@
       </c>
       <c r="K26" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L26" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M26" s="125">
         <f t="shared" si="4"/>
@@ -4847,18 +4854,18 @@
       </c>
       <c r="P26" s="72">
         <f t="shared" si="7"/>
-        <v>92161.54</v>
+        <v>107832.54</v>
       </c>
       <c r="Q26" s="73">
         <f t="shared" si="8"/>
-        <v>94926.54</v>
+        <v>111067.54</v>
       </c>
       <c r="R26" s="44">
         <f t="shared" si="9"/>
         <v>0.54</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="61">
         <v>7</v>
       </c>
@@ -4868,37 +4875,37 @@
       <c r="C27" s="61">
         <v>55</v>
       </c>
-      <c r="D27" s="176" t="s">
+      <c r="D27" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="179" t="s">
+      <c r="E27" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="F27" s="177">
+      <c r="F27" s="179">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G27" s="69">
-        <v>117734.55</v>
+        <v>102503.55</v>
       </c>
       <c r="H27" s="118">
-        <f>106171</f>
-        <v>106171</v>
+        <f>G27</f>
+        <v>102503.55</v>
       </c>
       <c r="I27" s="70">
         <f t="shared" si="0"/>
-        <v>11563.550000000003</v>
+        <v>0</v>
       </c>
       <c r="J27" s="70">
         <f t="shared" si="1"/>
-        <v>346.90650000000005</v>
+        <v>0</v>
       </c>
       <c r="K27" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L27" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M27" s="125">
         <f t="shared" si="4"/>
@@ -4914,86 +4921,85 @@
       </c>
       <c r="P27" s="72">
         <f t="shared" si="7"/>
-        <v>104072.55</v>
+        <v>107832.55</v>
       </c>
       <c r="Q27" s="73">
         <f t="shared" si="8"/>
-        <v>107194.55</v>
+        <v>111067.55</v>
       </c>
       <c r="R27" s="44">
         <f t="shared" si="9"/>
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="61">
         <v>7</v>
       </c>
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="180" t="s">
         <v>128</v>
       </c>
-      <c r="C28" s="61">
+      <c r="C28" s="180">
         <v>56</v>
       </c>
-      <c r="D28" s="60" t="s">
+      <c r="D28" s="180" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="74" t="s">
+      <c r="E28" s="189" t="s">
         <v>130</v>
       </c>
-      <c r="F28" s="68">
+      <c r="F28" s="181">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G28" s="69">
-        <f>3521+145670.56</f>
-        <v>149191.56</v>
-      </c>
-      <c r="H28" s="118">
-        <f>24240.56+124951.23</f>
-        <v>149191.79</v>
-      </c>
-      <c r="I28" s="70">
+      <c r="G28" s="182">
+        <v>135602.56</v>
+      </c>
+      <c r="H28" s="230">
+        <f>137965-H65</f>
+        <v>135601.76999999999</v>
+      </c>
+      <c r="I28" s="183">
         <f t="shared" si="0"/>
-        <v>-0.23000000001047738</v>
-      </c>
-      <c r="J28" s="70">
+        <v>0.79000000000814907</v>
+      </c>
+      <c r="J28" s="183">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="71">
+        <v>2.370000000024447E-2</v>
+      </c>
+      <c r="K28" s="184">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="71">
+        <v>980.171064</v>
+      </c>
+      <c r="L28" s="184">
         <f t="shared" si="3"/>
-        <v>72720</v>
-      </c>
-      <c r="M28" s="125">
+        <v>94512.405188000004</v>
+      </c>
+      <c r="M28" s="185">
         <f t="shared" si="4"/>
         <v>45683.387971999997</v>
       </c>
-      <c r="N28" s="125">
+      <c r="N28" s="185">
         <f t="shared" si="5"/>
         <v>15529.123296</v>
       </c>
-      <c r="O28" s="125">
+      <c r="O28" s="185">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P28" s="72">
+      <c r="P28" s="186">
         <f t="shared" si="7"/>
-        <v>133932.56</v>
-      </c>
-      <c r="Q28" s="73">
+        <v>156706.56</v>
+      </c>
+      <c r="Q28" s="187">
         <f t="shared" si="8"/>
-        <v>137950.56</v>
+        <v>161407.56</v>
       </c>
       <c r="R28" s="44">
         <f t="shared" si="9"/>
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="61">
         <v>8</v>
       </c>
@@ -5011,11 +5017,11 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G29" s="69">
-        <v>145692.57</v>
+        <v>131652.57</v>
       </c>
       <c r="H29" s="118">
         <f>G29</f>
-        <v>145692.57</v>
+        <v>131652.57</v>
       </c>
       <c r="I29" s="70">
         <f t="shared" si="0"/>
@@ -5027,11 +5033,11 @@
       </c>
       <c r="K29" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L29" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M29" s="125">
         <f t="shared" si="4"/>
@@ -5047,18 +5053,18 @@
       </c>
       <c r="P29" s="72">
         <f t="shared" si="7"/>
-        <v>133933.57</v>
+        <v>156705.57</v>
       </c>
       <c r="Q29" s="73">
         <f t="shared" si="8"/>
-        <v>137951.57</v>
+        <v>161406.57</v>
       </c>
       <c r="R29" s="44">
         <f t="shared" si="9"/>
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="61">
         <v>8</v>
       </c>
@@ -5078,11 +5084,11 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G30" s="69">
-        <v>83572.58</v>
+        <v>90592.58</v>
       </c>
       <c r="H30" s="118">
         <f>G30</f>
-        <v>83572.58</v>
+        <v>90592.58</v>
       </c>
       <c r="I30" s="70">
         <f t="shared" si="0"/>
@@ -5094,11 +5100,11 @@
       </c>
       <c r="K30" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L30" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M30" s="125">
         <f t="shared" si="4"/>
@@ -5114,18 +5120,18 @@
       </c>
       <c r="P30" s="72">
         <f t="shared" si="7"/>
-        <v>92161.58</v>
+        <v>107832.58</v>
       </c>
       <c r="Q30" s="73">
         <f t="shared" si="8"/>
-        <v>94926.58</v>
+        <v>111067.58</v>
       </c>
       <c r="R30" s="44">
         <f t="shared" si="9"/>
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="61">
         <v>9</v>
       </c>
@@ -5143,27 +5149,24 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G31" s="69">
-        <v>211586.59</v>
-      </c>
-      <c r="H31" s="118">
-        <f>G31</f>
-        <v>211586.59</v>
-      </c>
+        <v>90592.59</v>
+      </c>
+      <c r="H31" s="118"/>
       <c r="I31" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>90592.59</v>
       </c>
       <c r="J31" s="70">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2717.7776999999996</v>
       </c>
       <c r="K31" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L31" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M31" s="125">
         <f t="shared" si="4"/>
@@ -5179,18 +5182,18 @@
       </c>
       <c r="P31" s="72">
         <f t="shared" si="7"/>
-        <v>92161.59</v>
+        <v>201142.59</v>
       </c>
       <c r="Q31" s="73">
         <f t="shared" si="8"/>
-        <v>94926.59</v>
+        <v>207176.59</v>
       </c>
       <c r="R31" s="44">
         <f t="shared" si="9"/>
         <v>0.59</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="61">
         <v>9</v>
       </c>
@@ -5204,15 +5207,15 @@
         <v>139</v>
       </c>
       <c r="E32" s="60"/>
-      <c r="F32" s="68">
+      <c r="F32" s="179">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G32" s="69">
-        <v>145692.6</v>
+        <v>131652.6</v>
       </c>
       <c r="H32" s="118">
         <f>G32</f>
-        <v>145692.6</v>
+        <v>131652.6</v>
       </c>
       <c r="I32" s="70">
         <f t="shared" si="0"/>
@@ -5224,11 +5227,11 @@
       </c>
       <c r="K32" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L32" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M32" s="125">
         <f t="shared" si="4"/>
@@ -5244,83 +5247,83 @@
       </c>
       <c r="P32" s="72">
         <f t="shared" si="7"/>
-        <v>133933.6</v>
+        <v>156705.60000000001</v>
       </c>
       <c r="Q32" s="73">
         <f t="shared" si="8"/>
-        <v>137951.6</v>
+        <v>161406.6</v>
       </c>
       <c r="R32" s="44">
         <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="61">
+    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="180">
         <v>10</v>
       </c>
-      <c r="B33" s="61" t="s">
+      <c r="B33" s="180" t="s">
         <v>140</v>
       </c>
-      <c r="C33" s="61">
+      <c r="C33" s="180">
         <v>61</v>
       </c>
-      <c r="D33" s="176" t="s">
+      <c r="D33" s="180" t="s">
         <v>141</v>
       </c>
-      <c r="E33" s="176"/>
-      <c r="F33" s="177">
+      <c r="E33" s="180"/>
+      <c r="F33" s="181">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G33" s="181">
-        <v>145692.60999999999</v>
-      </c>
-      <c r="H33" s="118">
-        <f>183918-H87</f>
-        <v>145691.87</v>
-      </c>
-      <c r="I33" s="70">
+      <c r="G33" s="182">
+        <v>131653.60999999999</v>
+      </c>
+      <c r="H33" s="230">
+        <f>166195.74-H87</f>
+        <v>131653.60999999999</v>
+      </c>
+      <c r="I33" s="183">
         <f t="shared" si="0"/>
-        <v>0.73999999999068677</v>
-      </c>
-      <c r="J33" s="70">
+        <v>0</v>
+      </c>
+      <c r="J33" s="183">
         <f t="shared" si="1"/>
-        <v>2.2199999999720603E-2</v>
-      </c>
-      <c r="K33" s="71">
+        <v>0</v>
+      </c>
+      <c r="K33" s="184">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L33" s="71">
+        <v>980.171064</v>
+      </c>
+      <c r="L33" s="184">
         <f t="shared" si="3"/>
-        <v>72720</v>
-      </c>
-      <c r="M33" s="125">
+        <v>94512.405188000004</v>
+      </c>
+      <c r="M33" s="185">
         <f t="shared" si="4"/>
         <v>45683.387971999997</v>
       </c>
-      <c r="N33" s="125">
+      <c r="N33" s="185">
         <f t="shared" si="5"/>
         <v>15529.123296</v>
       </c>
-      <c r="O33" s="125">
+      <c r="O33" s="185">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P33" s="72">
+      <c r="P33" s="186">
         <f t="shared" si="7"/>
-        <v>133933.60999999999</v>
-      </c>
-      <c r="Q33" s="73">
+        <v>156705.60999999999</v>
+      </c>
+      <c r="Q33" s="187">
         <f t="shared" si="8"/>
-        <v>137951.60999999999</v>
+        <v>161406.60999999999</v>
       </c>
       <c r="R33" s="44">
         <f t="shared" si="9"/>
         <v>0.61</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="61">
         <v>10</v>
       </c>
@@ -5336,15 +5339,15 @@
       <c r="E34" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="F34" s="68">
+      <c r="F34" s="179">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G34" s="69">
-        <v>100253.62</v>
+        <v>90592.62</v>
       </c>
       <c r="H34" s="118">
         <f>G34</f>
-        <v>100253.62</v>
+        <v>90592.62</v>
       </c>
       <c r="I34" s="70">
         <f t="shared" si="0"/>
@@ -5356,11 +5359,11 @@
       </c>
       <c r="K34" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L34" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M34" s="125">
         <f t="shared" si="4"/>
@@ -5376,18 +5379,18 @@
       </c>
       <c r="P34" s="72">
         <f t="shared" si="7"/>
-        <v>92161.62</v>
+        <v>107832.62</v>
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="8"/>
-        <v>94926.62</v>
+        <v>111067.62</v>
       </c>
       <c r="R34" s="44">
         <f t="shared" si="9"/>
         <v>0.62</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="61">
         <v>11</v>
       </c>
@@ -5407,11 +5410,11 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G35" s="69">
-        <v>100253.63</v>
+        <v>90592.63</v>
       </c>
       <c r="H35" s="118">
         <f>G35</f>
-        <v>100253.63</v>
+        <v>90592.63</v>
       </c>
       <c r="I35" s="70">
         <f t="shared" si="0"/>
@@ -5423,11 +5426,11 @@
       </c>
       <c r="K35" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L35" s="71">
         <f t="shared" si="3"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M35" s="125">
         <f t="shared" si="4"/>
@@ -5443,18 +5446,18 @@
       </c>
       <c r="P35" s="72">
         <f t="shared" si="7"/>
-        <v>92161.63</v>
+        <v>107832.63</v>
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="8"/>
-        <v>94926.63</v>
+        <v>111067.63</v>
       </c>
       <c r="R35" s="44">
         <f t="shared" si="9"/>
         <v>0.63</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="61">
         <v>11</v>
       </c>
@@ -5474,11 +5477,11 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G36" s="69">
-        <v>169987.64</v>
+        <v>131652.64000000001</v>
       </c>
       <c r="H36" s="118">
         <f>G36</f>
-        <v>169987.64</v>
+        <v>131652.64000000001</v>
       </c>
       <c r="I36" s="70">
         <f t="shared" si="0"/>
@@ -5490,11 +5493,11 @@
       </c>
       <c r="K36" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L36" s="71">
         <f t="shared" si="3"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M36" s="125">
         <f t="shared" si="4"/>
@@ -5510,18 +5513,18 @@
       </c>
       <c r="P36" s="72">
         <f t="shared" si="7"/>
-        <v>133933.64000000001</v>
+        <v>156705.64000000001</v>
       </c>
       <c r="Q36" s="73">
         <f t="shared" si="8"/>
-        <v>137951.64000000001</v>
+        <v>161406.64000000001</v>
       </c>
       <c r="R36" s="44">
         <f t="shared" si="9"/>
         <v>0.64</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="61">
         <v>12</v>
       </c>
@@ -5541,11 +5544,11 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G37" s="69">
-        <v>145692.65</v>
+        <v>131652.65</v>
       </c>
       <c r="H37" s="118">
         <f>G37</f>
-        <v>145692.65</v>
+        <v>131652.65</v>
       </c>
       <c r="I37" s="70">
         <f t="shared" ref="I37:I56" si="10">G37-H37</f>
@@ -5557,11 +5560,11 @@
       </c>
       <c r="K37" s="71">
         <f t="shared" ref="K37:K56" si="12">M$2*F37</f>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L37" s="71">
         <f t="shared" ref="L37:L68" si="13">M$1*F37</f>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M37" s="125">
         <f t="shared" ref="M37:M56" si="14">F$1*F37</f>
@@ -5577,18 +5580,18 @@
       </c>
       <c r="P37" s="72">
         <f t="shared" ref="P37:P68" si="17">ROUND(SUM(I37:O37),0) + R37</f>
-        <v>133933.65</v>
+        <v>156705.65</v>
       </c>
       <c r="Q37" s="73">
         <f t="shared" ref="Q37:Q56" si="18">ROUND(P37*3%,0) + P37</f>
-        <v>137951.65</v>
+        <v>161406.65</v>
       </c>
       <c r="R37" s="44">
         <f t="shared" ref="R37:R68" si="19">ROUND(0.001+C37/100,2)</f>
         <v>0.65</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="61">
         <v>12</v>
       </c>
@@ -5608,24 +5611,26 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G38" s="69">
-        <v>211585.66</v>
-      </c>
-      <c r="H38" s="118"/>
+        <v>308526.65999999997</v>
+      </c>
+      <c r="H38" s="118">
+        <v>200000</v>
+      </c>
       <c r="I38" s="70">
         <f t="shared" si="10"/>
-        <v>211585.66</v>
+        <v>108526.65999999997</v>
       </c>
       <c r="J38" s="70">
         <f t="shared" si="11"/>
-        <v>6347.5698000000002</v>
+        <v>3255.7997999999993</v>
       </c>
       <c r="K38" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L38" s="71">
         <f t="shared" si="13"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M38" s="125">
         <f t="shared" si="14"/>
@@ -5641,18 +5646,18 @@
       </c>
       <c r="P38" s="72">
         <f t="shared" si="17"/>
-        <v>310095.65999999997</v>
+        <v>219614.66</v>
       </c>
       <c r="Q38" s="73">
         <f t="shared" si="18"/>
-        <v>319398.65999999997</v>
+        <v>226202.66</v>
       </c>
       <c r="R38" s="44">
         <f t="shared" si="19"/>
         <v>0.66</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="61">
         <v>1</v>
       </c>
@@ -5672,27 +5677,24 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G39" s="69">
-        <v>120956.67</v>
-      </c>
-      <c r="H39" s="118">
-        <f>17179.67+103777</f>
-        <v>120956.67</v>
-      </c>
+        <v>90592.67</v>
+      </c>
+      <c r="H39" s="118"/>
       <c r="I39" s="70">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>90592.67</v>
       </c>
       <c r="J39" s="70">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2717.7800999999999</v>
       </c>
       <c r="K39" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L39" s="71">
         <f t="shared" si="13"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M39" s="125">
         <f t="shared" si="14"/>
@@ -5708,31 +5710,31 @@
       </c>
       <c r="P39" s="72">
         <f t="shared" si="17"/>
-        <v>92161.67</v>
+        <v>201142.67</v>
       </c>
       <c r="Q39" s="73">
         <f t="shared" si="18"/>
-        <v>94926.67</v>
+        <v>207176.67</v>
       </c>
       <c r="R39" s="44">
         <f t="shared" si="19"/>
         <v>0.67</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="61">
         <v>1</v>
       </c>
       <c r="B40" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="C40" s="193">
+      <c r="C40" s="60">
         <v>68</v>
       </c>
-      <c r="D40" s="193" t="s">
+      <c r="D40" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="E40" s="194" t="str">
+      <c r="E40" s="74" t="str">
         <f>D76</f>
         <v>Jesica Romina Tobio</v>
       </c>
@@ -5740,24 +5742,27 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G40" s="69">
-        <v>145692.68</v>
-      </c>
-      <c r="H40" s="118"/>
+        <v>281716.68</v>
+      </c>
+      <c r="H40" s="118">
+        <f>191852.7+173373.7+5746-G76</f>
+        <v>281716.38</v>
+      </c>
       <c r="I40" s="70">
         <f t="shared" si="10"/>
-        <v>145692.68</v>
+        <v>0.29999999998835847</v>
       </c>
       <c r="J40" s="70">
         <f t="shared" si="11"/>
-        <v>4370.7803999999996</v>
+        <v>8.9999999996507544E-3</v>
       </c>
       <c r="K40" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L40" s="71">
         <f t="shared" si="13"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M40" s="125">
         <f t="shared" si="14"/>
@@ -5773,18 +5778,18 @@
       </c>
       <c r="P40" s="72">
         <f t="shared" si="17"/>
-        <v>283996.68</v>
+        <v>156705.68</v>
       </c>
       <c r="Q40" s="73">
         <f t="shared" si="18"/>
-        <v>292516.68</v>
+        <v>161406.68</v>
       </c>
       <c r="R40" s="44">
         <f t="shared" si="19"/>
         <v>0.68</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="60">
         <v>1</v>
       </c>
@@ -5804,10 +5809,11 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G41" s="69">
-        <v>145677.69</v>
+        <v>131652.69</v>
       </c>
       <c r="H41" s="118">
-        <v>145677.69</v>
+        <f>G41</f>
+        <v>131652.69</v>
       </c>
       <c r="I41" s="70">
         <f t="shared" si="10"/>
@@ -5819,11 +5825,11 @@
       </c>
       <c r="K41" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L41" s="71">
         <f t="shared" si="13"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M41" s="125">
         <f t="shared" si="14"/>
@@ -5839,18 +5845,18 @@
       </c>
       <c r="P41" s="72">
         <f t="shared" si="17"/>
-        <v>133933.69</v>
+        <v>156705.69</v>
       </c>
       <c r="Q41" s="73">
         <f t="shared" si="18"/>
-        <v>137951.69</v>
+        <v>161406.69</v>
       </c>
       <c r="R41" s="44">
         <f t="shared" si="19"/>
         <v>0.69</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="61">
         <v>2</v>
       </c>
@@ -5870,27 +5876,27 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G42" s="69">
-        <v>248195.7</v>
+        <v>131445.70000000001</v>
       </c>
       <c r="H42" s="118">
-        <f>16680+191852.7</f>
-        <v>208532.7</v>
+        <f>205601-191852.7</f>
+        <v>13748.299999999988</v>
       </c>
       <c r="I42" s="70">
         <f t="shared" si="10"/>
-        <v>39663</v>
+        <v>117697.40000000002</v>
       </c>
       <c r="J42" s="70">
         <f t="shared" si="11"/>
-        <v>1189.8899999999999</v>
+        <v>3530.9220000000005</v>
       </c>
       <c r="K42" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L42" s="71">
         <f t="shared" si="13"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M42" s="125">
         <f t="shared" si="14"/>
@@ -5906,18 +5912,18 @@
       </c>
       <c r="P42" s="72">
         <f t="shared" si="17"/>
-        <v>133014.70000000001</v>
+        <v>229060.7</v>
       </c>
       <c r="Q42" s="73">
         <f t="shared" si="18"/>
-        <v>137004.70000000001</v>
+        <v>235932.7</v>
       </c>
       <c r="R42" s="44">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="61">
         <v>2</v>
       </c>
@@ -5937,11 +5943,11 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G43" s="69">
-        <v>100254.71</v>
+        <v>90592.71</v>
       </c>
       <c r="H43" s="118">
         <f>G43</f>
-        <v>100254.71</v>
+        <v>90592.71</v>
       </c>
       <c r="I43" s="70">
         <f t="shared" si="10"/>
@@ -5953,11 +5959,11 @@
       </c>
       <c r="K43" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L43" s="71">
         <f t="shared" si="13"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M43" s="125">
         <f t="shared" si="14"/>
@@ -5973,18 +5979,18 @@
       </c>
       <c r="P43" s="72">
         <f t="shared" si="17"/>
-        <v>92161.71</v>
+        <v>107832.71</v>
       </c>
       <c r="Q43" s="73">
         <f t="shared" si="18"/>
-        <v>94926.71</v>
+        <v>111067.71</v>
       </c>
       <c r="R43" s="44">
         <f t="shared" si="19"/>
         <v>0.71</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="61">
         <v>2</v>
       </c>
@@ -5994,36 +6000,36 @@
       <c r="C44" s="61">
         <v>72</v>
       </c>
-      <c r="D44" s="176" t="s">
+      <c r="D44" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="E44" s="176" t="s">
-        <v>249</v>
-      </c>
-      <c r="F44" s="180">
+      <c r="E44" s="60" t="s">
+        <v>248</v>
+      </c>
+      <c r="F44" s="75">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G44" s="69">
-        <v>465918.71999999997</v>
+      <c r="G44" s="170">
+        <v>451878.72</v>
       </c>
       <c r="H44" s="118">
-        <v>155020</v>
+        <v>131652.72</v>
       </c>
       <c r="I44" s="70">
         <f t="shared" si="10"/>
-        <v>310898.71999999997</v>
+        <v>320226</v>
       </c>
       <c r="J44" s="70">
         <f t="shared" si="11"/>
-        <v>9326.9615999999987</v>
+        <v>9606.7799999999988</v>
       </c>
       <c r="K44" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L44" s="71">
         <f t="shared" si="13"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M44" s="125">
         <f t="shared" si="14"/>
@@ -6039,18 +6045,18 @@
       </c>
       <c r="P44" s="72">
         <f t="shared" si="17"/>
-        <v>454158.72</v>
+        <v>486538.72</v>
       </c>
       <c r="Q44" s="73">
         <f t="shared" si="18"/>
-        <v>467783.72</v>
+        <v>501134.72</v>
       </c>
       <c r="R44" s="44">
         <f t="shared" si="19"/>
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="61">
         <v>3</v>
       </c>
@@ -6069,25 +6075,27 @@
       <c r="F45" s="75">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G45" s="69">
-        <v>471172.73</v>
-      </c>
-      <c r="H45" s="118"/>
+      <c r="G45" s="170">
+        <v>616960.73</v>
+      </c>
+      <c r="H45" s="118">
+        <v>100000.73</v>
+      </c>
       <c r="I45" s="70">
         <f t="shared" si="10"/>
-        <v>471172.73</v>
+        <v>516960</v>
       </c>
       <c r="J45" s="70">
         <f t="shared" si="11"/>
-        <v>14135.1819</v>
+        <v>15508.8</v>
       </c>
       <c r="K45" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L45" s="71">
         <f t="shared" si="13"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M45" s="125">
         <f t="shared" si="14"/>
@@ -6103,18 +6111,18 @@
       </c>
       <c r="P45" s="72">
         <f t="shared" si="17"/>
-        <v>619240.73</v>
+        <v>689174.73</v>
       </c>
       <c r="Q45" s="73">
         <f t="shared" si="18"/>
-        <v>637817.73</v>
+        <v>709849.73</v>
       </c>
       <c r="R45" s="44">
         <f t="shared" si="19"/>
         <v>0.73</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="61">
         <v>3</v>
       </c>
@@ -6133,11 +6141,12 @@
       <c r="F46" s="75">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="G46" s="69">
-        <v>100253.74</v>
+      <c r="G46" s="170">
+        <v>90592.74</v>
       </c>
       <c r="H46" s="118">
-        <v>100253.74</v>
+        <f>G46</f>
+        <v>90592.74</v>
       </c>
       <c r="I46" s="70">
         <f t="shared" si="10"/>
@@ -6149,11 +6158,11 @@
       </c>
       <c r="K46" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L46" s="71">
         <f t="shared" si="13"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M46" s="125">
         <f t="shared" si="14"/>
@@ -6169,18 +6178,18 @@
       </c>
       <c r="P46" s="72">
         <f t="shared" si="17"/>
-        <v>92161.74</v>
+        <v>107832.74</v>
       </c>
       <c r="Q46" s="73">
         <f t="shared" si="18"/>
-        <v>94926.74</v>
+        <v>111067.74</v>
       </c>
       <c r="R46" s="44">
         <f t="shared" si="19"/>
         <v>0.74</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="61">
         <v>3</v>
       </c>
@@ -6199,25 +6208,28 @@
       <c r="F47" s="75">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="G47" s="69">
-        <v>100253.75</v>
-      </c>
-      <c r="H47" s="118"/>
+      <c r="G47" s="170">
+        <v>199670.75</v>
+      </c>
+      <c r="H47" s="118">
+        <f>G47</f>
+        <v>199670.75</v>
+      </c>
       <c r="I47" s="70">
         <f t="shared" si="10"/>
-        <v>100253.75</v>
+        <v>0</v>
       </c>
       <c r="J47" s="70">
         <f t="shared" si="11"/>
-        <v>3007.6124999999997</v>
+        <v>0</v>
       </c>
       <c r="K47" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L47" s="71">
         <f t="shared" si="13"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M47" s="125">
         <f t="shared" si="14"/>
@@ -6233,19 +6245,19 @@
       </c>
       <c r="P47" s="72">
         <f t="shared" si="17"/>
-        <v>195423.75</v>
+        <v>107832.75</v>
       </c>
       <c r="Q47" s="73">
         <f t="shared" si="18"/>
-        <v>201286.75</v>
+        <v>111067.75</v>
       </c>
       <c r="R47" s="44">
         <f t="shared" si="19"/>
         <v>0.75</v>
       </c>
-      <c r="T47" s="142"/>
-    </row>
-    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T47" s="140"/>
+    </row>
+    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="61">
         <v>4</v>
       </c>
@@ -6264,12 +6276,12 @@
       <c r="F48" s="75">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G48" s="69">
-        <v>145692.76</v>
+      <c r="G48" s="170">
+        <v>131652.76</v>
       </c>
       <c r="H48" s="118">
         <f>G48</f>
-        <v>145692.76</v>
+        <v>131652.76</v>
       </c>
       <c r="I48" s="70">
         <f t="shared" si="10"/>
@@ -6281,11 +6293,11 @@
       </c>
       <c r="K48" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L48" s="71">
         <f t="shared" si="13"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M48" s="125">
         <f t="shared" si="14"/>
@@ -6301,18 +6313,18 @@
       </c>
       <c r="P48" s="72">
         <f t="shared" si="17"/>
-        <v>133933.76000000001</v>
+        <v>156705.76</v>
       </c>
       <c r="Q48" s="73">
         <f t="shared" si="18"/>
-        <v>137951.76</v>
+        <v>161406.76</v>
       </c>
       <c r="R48" s="44">
         <f t="shared" si="19"/>
         <v>0.76</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="61">
         <v>4</v>
       </c>
@@ -6322,21 +6334,21 @@
       <c r="C49" s="61">
         <v>77</v>
       </c>
-      <c r="D49" s="176" t="s">
+      <c r="D49" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="E49" s="176" t="s">
+      <c r="E49" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="F49" s="180">
+      <c r="F49" s="75">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G49" s="69">
-        <v>145692.76999999999</v>
+      <c r="G49" s="170">
+        <v>131652.76999999999</v>
       </c>
       <c r="H49" s="118">
         <f>G49</f>
-        <v>145692.76999999999</v>
+        <v>131652.76999999999</v>
       </c>
       <c r="I49" s="70">
         <f t="shared" si="10"/>
@@ -6348,11 +6360,11 @@
       </c>
       <c r="K49" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L49" s="71">
         <f t="shared" si="13"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M49" s="125">
         <f t="shared" si="14"/>
@@ -6368,18 +6380,18 @@
       </c>
       <c r="P49" s="72">
         <f t="shared" si="17"/>
-        <v>133933.76999999999</v>
+        <v>156705.76999999999</v>
       </c>
       <c r="Q49" s="73">
         <f t="shared" si="18"/>
-        <v>137951.76999999999</v>
+        <v>161406.76999999999</v>
       </c>
       <c r="R49" s="44">
         <f t="shared" si="19"/>
         <v>0.77</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="61">
         <v>4</v>
       </c>
@@ -6398,27 +6410,27 @@
       <c r="F50" s="75">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="G50" s="69">
-        <v>427555.78</v>
+      <c r="G50" s="170">
+        <v>193854.78</v>
       </c>
       <c r="H50" s="118">
-        <v>327301.78000000003</v>
+        <v>113081</v>
       </c>
       <c r="I50" s="70">
         <f t="shared" si="10"/>
-        <v>100254</v>
+        <v>80773.78</v>
       </c>
       <c r="J50" s="70">
         <f t="shared" si="11"/>
-        <v>3007.62</v>
+        <v>2423.2134000000001</v>
       </c>
       <c r="K50" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L50" s="71">
         <f t="shared" si="13"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M50" s="125">
         <f t="shared" si="14"/>
@@ -6434,18 +6446,18 @@
       </c>
       <c r="P50" s="72">
         <f t="shared" si="17"/>
-        <v>195423.78</v>
+        <v>191029.78</v>
       </c>
       <c r="Q50" s="73">
         <f t="shared" si="18"/>
-        <v>201286.78</v>
+        <v>196760.78</v>
       </c>
       <c r="R50" s="44">
         <f t="shared" si="19"/>
         <v>0.78</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="61">
         <v>5</v>
       </c>
@@ -6463,14 +6475,15 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G51" s="69">
-        <v>100253.79</v>
+        <v>87584.79</v>
       </c>
       <c r="H51" s="118">
-        <v>103261.79</v>
+        <f>G51</f>
+        <v>87584.79</v>
       </c>
       <c r="I51" s="70">
         <f t="shared" si="10"/>
-        <v>-3008</v>
+        <v>0</v>
       </c>
       <c r="J51" s="70">
         <f t="shared" si="11"/>
@@ -6478,11 +6491,11 @@
       </c>
       <c r="K51" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L51" s="71">
         <f t="shared" si="13"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M51" s="125">
         <f t="shared" si="14"/>
@@ -6498,18 +6511,18 @@
       </c>
       <c r="P51" s="72">
         <f t="shared" si="17"/>
-        <v>89153.79</v>
+        <v>107832.79</v>
       </c>
       <c r="Q51" s="73">
         <f t="shared" si="18"/>
-        <v>91828.79</v>
+        <v>111067.79</v>
       </c>
       <c r="R51" s="44">
         <f t="shared" si="19"/>
         <v>0.79</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="61">
         <v>5</v>
       </c>
@@ -6529,14 +6542,14 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G52" s="69">
-        <v>277978.8</v>
+        <v>123313.8</v>
       </c>
       <c r="H52" s="118">
-        <v>286317.8</v>
+        <v>127012.8</v>
       </c>
       <c r="I52" s="70">
         <f t="shared" si="10"/>
-        <v>-8339</v>
+        <v>-3699</v>
       </c>
       <c r="J52" s="70">
         <f t="shared" si="11"/>
@@ -6544,11 +6557,11 @@
       </c>
       <c r="K52" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L52" s="71">
         <f t="shared" si="13"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M52" s="125">
         <f t="shared" si="14"/>
@@ -6564,18 +6577,18 @@
       </c>
       <c r="P52" s="72">
         <f t="shared" si="17"/>
-        <v>125594.8</v>
+        <v>153006.79999999999</v>
       </c>
       <c r="Q52" s="73">
         <f t="shared" si="18"/>
-        <v>129362.8</v>
+        <v>157596.79999999999</v>
       </c>
       <c r="R52" s="44">
         <f t="shared" si="19"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="61">
         <v>5</v>
       </c>
@@ -6595,27 +6608,24 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G53" s="69">
-        <v>145692.81</v>
-      </c>
-      <c r="H53" s="118">
-        <f>G53</f>
-        <v>145692.81</v>
-      </c>
+        <v>131652.81</v>
+      </c>
+      <c r="H53" s="118"/>
       <c r="I53" s="70">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>131652.81</v>
       </c>
       <c r="J53" s="70">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3949.5843</v>
       </c>
       <c r="K53" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L53" s="71">
         <f t="shared" si="13"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M53" s="125">
         <f t="shared" si="14"/>
@@ -6631,21 +6641,21 @@
       </c>
       <c r="P53" s="72">
         <f t="shared" si="17"/>
-        <v>133933.81</v>
+        <v>292307.81</v>
       </c>
       <c r="Q53" s="73">
         <f t="shared" si="18"/>
-        <v>137951.81</v>
+        <v>301076.81</v>
       </c>
       <c r="R53" s="44">
         <f t="shared" si="19"/>
         <v>0.81</v>
       </c>
       <c r="T53" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="61">
         <v>6</v>
       </c>
@@ -6663,11 +6673,11 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G54" s="69">
-        <v>100253.82</v>
+        <v>90592.82</v>
       </c>
       <c r="H54" s="118">
         <f>G54</f>
-        <v>100253.82</v>
+        <v>90592.82</v>
       </c>
       <c r="I54" s="70">
         <f t="shared" si="10"/>
@@ -6679,11 +6689,11 @@
       </c>
       <c r="K54" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L54" s="71">
         <f t="shared" si="13"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M54" s="125">
         <f t="shared" si="14"/>
@@ -6699,18 +6709,18 @@
       </c>
       <c r="P54" s="72">
         <f t="shared" si="17"/>
-        <v>92161.82</v>
+        <v>107832.82</v>
       </c>
       <c r="Q54" s="73">
         <f t="shared" si="18"/>
-        <v>94926.82</v>
+        <v>111067.82</v>
       </c>
       <c r="R54" s="44">
         <f t="shared" si="19"/>
         <v>0.82</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="61">
         <v>6</v>
       </c>
@@ -6730,24 +6740,24 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G55" s="69">
-        <v>324223.83</v>
+        <v>424543.83</v>
       </c>
       <c r="H55" s="118"/>
       <c r="I55" s="70">
         <f t="shared" si="10"/>
-        <v>324223.83</v>
+        <v>424543.83</v>
       </c>
       <c r="J55" s="70">
         <f t="shared" si="11"/>
-        <v>9726.7149000000009</v>
+        <v>12736.314899999999</v>
       </c>
       <c r="K55" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.4741479999999</v>
       </c>
       <c r="L55" s="71">
         <f t="shared" si="13"/>
-        <v>50040</v>
+        <v>65035.763965999999</v>
       </c>
       <c r="M55" s="125">
         <f t="shared" si="14"/>
@@ -6763,18 +6773,18 @@
       </c>
       <c r="P55" s="72">
         <f t="shared" si="17"/>
-        <v>426112.83</v>
+        <v>545112.82999999996</v>
       </c>
       <c r="Q55" s="73">
         <f t="shared" si="18"/>
-        <v>438895.83</v>
+        <v>561465.82999999996</v>
       </c>
       <c r="R55" s="44">
         <f t="shared" si="19"/>
         <v>0.83</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="61">
         <v>6</v>
       </c>
@@ -6792,11 +6802,11 @@
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G56" s="69">
-        <v>145692.84</v>
+        <v>131652.84</v>
       </c>
       <c r="H56" s="118">
         <f>G56</f>
-        <v>145692.84</v>
+        <v>131652.84</v>
       </c>
       <c r="I56" s="70">
         <f t="shared" si="10"/>
@@ -6808,11 +6818,11 @@
       </c>
       <c r="K56" s="71">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>980.171064</v>
       </c>
       <c r="L56" s="71">
         <f t="shared" si="13"/>
-        <v>72720</v>
+        <v>94512.405188000004</v>
       </c>
       <c r="M56" s="125">
         <f t="shared" si="14"/>
@@ -6828,18 +6838,18 @@
       </c>
       <c r="P56" s="72">
         <f t="shared" si="17"/>
-        <v>133933.84</v>
+        <v>156705.84</v>
       </c>
       <c r="Q56" s="73">
         <f t="shared" si="18"/>
-        <v>137951.84</v>
+        <v>161406.84</v>
       </c>
       <c r="R56" s="44">
         <f t="shared" si="19"/>
         <v>0.84</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="61">
         <v>7</v>
       </c>
@@ -6875,7 +6885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="61">
         <v>7</v>
       </c>
@@ -6911,7 +6921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="61">
         <v>7</v>
       </c>
@@ -6931,27 +6941,24 @@
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="G59" s="69">
-        <v>22286.17</v>
-      </c>
-      <c r="H59" s="118">
-        <f>G59</f>
-        <v>22286.17</v>
-      </c>
+        <v>20856.169999999998</v>
+      </c>
+      <c r="H59" s="118"/>
       <c r="I59" s="70">
         <f t="shared" ref="I59:I90" si="20">G59-H59</f>
-        <v>0</v>
+        <v>20856.169999999998</v>
       </c>
       <c r="J59" s="70">
         <f t="shared" ref="J59:J90" si="21">IF(I59&gt;0,I59*3%,0)</f>
-        <v>0</v>
+        <v>625.68509999999992</v>
       </c>
       <c r="K59" s="71">
         <f t="shared" ref="K59:K90" si="22">M$2*F59</f>
-        <v>0</v>
+        <v>155.27462400000002</v>
       </c>
       <c r="L59" s="71">
         <f t="shared" si="13"/>
-        <v>11520</v>
+        <v>14972.262208000002</v>
       </c>
       <c r="M59" s="125">
         <f t="shared" ref="M59:M90" si="23">F$1*F59</f>
@@ -6967,18 +6974,18 @@
       </c>
       <c r="P59" s="72">
         <f t="shared" si="17"/>
-        <v>21217.17</v>
+        <v>46306.17</v>
       </c>
       <c r="Q59" s="73">
         <f t="shared" ref="Q59:Q90" si="25">ROUND(P59*3%,0) + P59</f>
-        <v>21854.17</v>
+        <v>47695.17</v>
       </c>
       <c r="R59" s="44">
         <f t="shared" si="19"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="61">
         <v>8</v>
       </c>
@@ -6996,24 +7003,24 @@
         <v>3.3E-3</v>
       </c>
       <c r="G60" s="69">
-        <v>201811.18</v>
+        <v>229373.18</v>
       </c>
       <c r="H60" s="118"/>
       <c r="I60" s="70">
         <f t="shared" si="20"/>
-        <v>201811.18</v>
+        <v>229373.18</v>
       </c>
       <c r="J60" s="70">
         <f t="shared" si="21"/>
-        <v>6054.3353999999999</v>
+        <v>6881.1953999999996</v>
       </c>
       <c r="K60" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>160.12695600000001</v>
       </c>
       <c r="L60" s="71">
         <f t="shared" si="13"/>
-        <v>11880</v>
+        <v>15440.145402000002</v>
       </c>
       <c r="M60" s="125">
         <f t="shared" si="23"/>
@@ -7029,18 +7036,18 @@
       </c>
       <c r="P60" s="72">
         <f t="shared" si="17"/>
-        <v>229746.18</v>
+        <v>261855.18</v>
       </c>
       <c r="Q60" s="73">
         <f t="shared" si="25"/>
-        <v>236638.18</v>
+        <v>269711.18</v>
       </c>
       <c r="R60" s="44">
         <f t="shared" si="19"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="61">
         <v>8</v>
       </c>
@@ -7058,24 +7065,24 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="G61" s="69">
-        <v>7081.19</v>
+        <v>9901.19</v>
       </c>
       <c r="H61" s="118"/>
       <c r="I61" s="70">
         <f t="shared" si="20"/>
-        <v>7081.19</v>
+        <v>9901.19</v>
       </c>
       <c r="J61" s="70">
         <f t="shared" si="21"/>
-        <v>212.43569999999997</v>
+        <v>297.03570000000002</v>
       </c>
       <c r="K61" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>19.409328000000002</v>
       </c>
       <c r="L61" s="71">
         <f t="shared" si="13"/>
-        <v>1440</v>
+        <v>1871.5327760000002</v>
       </c>
       <c r="M61" s="125">
         <f t="shared" si="23"/>
@@ -7091,18 +7098,18 @@
       </c>
       <c r="P61" s="72">
         <f t="shared" si="17"/>
-        <v>9946.19</v>
+        <v>13301.19</v>
       </c>
       <c r="Q61" s="73">
         <f t="shared" si="25"/>
-        <v>10244.19</v>
+        <v>13700.19</v>
       </c>
       <c r="R61" s="44">
         <f t="shared" si="19"/>
         <v>0.19</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="61">
         <v>8</v>
       </c>
@@ -7113,31 +7120,31 @@
         <v>20</v>
       </c>
       <c r="D62" s="60" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E62" s="74"/>
       <c r="F62" s="75">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G62" s="69">
-        <v>1442.2</v>
+        <v>2789.2</v>
       </c>
       <c r="H62" s="118"/>
       <c r="I62" s="70">
         <f t="shared" si="20"/>
-        <v>1442.2</v>
+        <v>2789.2</v>
       </c>
       <c r="J62" s="70">
         <f t="shared" si="21"/>
-        <v>43.265999999999998</v>
+        <v>83.675999999999988</v>
       </c>
       <c r="K62" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L62" s="71">
         <f t="shared" si="13"/>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M62" s="125">
         <f t="shared" si="23"/>
@@ -7153,18 +7160,18 @@
       </c>
       <c r="P62" s="72">
         <f t="shared" si="17"/>
-        <v>2812.2</v>
+        <v>4424.2</v>
       </c>
       <c r="Q62" s="73">
         <f t="shared" si="25"/>
-        <v>2896.2</v>
+        <v>4557.2</v>
       </c>
       <c r="R62" s="44">
         <f t="shared" si="19"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="61">
         <v>9</v>
       </c>
@@ -7184,12 +7191,12 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G63" s="69">
-        <v>-45074.79</v>
+        <v>-43770.79</v>
       </c>
       <c r="H63" s="118"/>
       <c r="I63" s="70">
         <f t="shared" si="20"/>
-        <v>-45074.79</v>
+        <v>-43770.79</v>
       </c>
       <c r="J63" s="70">
         <f t="shared" si="21"/>
@@ -7197,11 +7204,11 @@
       </c>
       <c r="K63" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L63" s="71">
         <f t="shared" si="13"/>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M63" s="125">
         <f t="shared" si="23"/>
@@ -7217,18 +7224,18 @@
       </c>
       <c r="P63" s="72">
         <f t="shared" si="17"/>
-        <v>-43748.79</v>
+        <v>-42218.79</v>
       </c>
       <c r="Q63" s="73">
         <f t="shared" si="25"/>
-        <v>-45060.79</v>
+        <v>-43485.79</v>
       </c>
       <c r="R63" s="44">
         <f t="shared" si="19"/>
         <v>0.21</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="61">
         <v>9</v>
       </c>
@@ -7238,19 +7245,19 @@
       <c r="C64" s="61">
         <v>22</v>
       </c>
-      <c r="D64" s="176" t="s">
+      <c r="D64" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="E64" s="179"/>
-      <c r="F64" s="180">
+      <c r="E64" s="74"/>
+      <c r="F64" s="75">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G64" s="69">
-        <v>1442.22</v>
+        <v>1303.22</v>
       </c>
       <c r="H64" s="118">
         <f>G64</f>
-        <v>1442.22</v>
+        <v>1303.22</v>
       </c>
       <c r="I64" s="70">
         <f t="shared" si="20"/>
@@ -7262,11 +7269,11 @@
       </c>
       <c r="K64" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L64" s="71">
         <f t="shared" si="13"/>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M64" s="125">
         <f t="shared" si="23"/>
@@ -7282,85 +7289,85 @@
       </c>
       <c r="P64" s="72">
         <f t="shared" si="17"/>
-        <v>1326.22</v>
+        <v>1552.22</v>
       </c>
       <c r="Q64" s="73">
         <f t="shared" si="25"/>
-        <v>1366.22</v>
+        <v>1599.22</v>
       </c>
       <c r="R64" s="44">
         <f t="shared" si="19"/>
         <v>0.22</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="61">
         <v>9</v>
       </c>
-      <c r="B65" s="76" t="s">
+      <c r="B65" s="190" t="s">
         <v>212</v>
       </c>
-      <c r="C65" s="61">
+      <c r="C65" s="180">
         <v>23</v>
       </c>
-      <c r="D65" s="60" t="s">
+      <c r="D65" s="180" t="s">
         <v>129</v>
       </c>
-      <c r="E65" s="74" t="s">
+      <c r="E65" s="189" t="s">
         <v>130</v>
       </c>
-      <c r="F65" s="75">
+      <c r="F65" s="191">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="G65" s="69">
-        <v>1202.23</v>
-      </c>
-      <c r="H65" s="118">
-        <f>240.23</f>
-        <v>240.23</v>
-      </c>
-      <c r="I65" s="70">
+      <c r="G65" s="182">
+        <v>2363.23</v>
+      </c>
+      <c r="H65" s="230">
+        <f>G65</f>
+        <v>2363.23</v>
+      </c>
+      <c r="I65" s="183">
         <f t="shared" si="20"/>
-        <v>962</v>
-      </c>
-      <c r="J65" s="70">
+        <v>0</v>
+      </c>
+      <c r="J65" s="183">
         <f t="shared" si="21"/>
-        <v>28.86</v>
-      </c>
-      <c r="K65" s="71">
+        <v>0</v>
+      </c>
+      <c r="K65" s="184">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L65" s="71">
+        <v>9.7046640000000011</v>
+      </c>
+      <c r="L65" s="184">
         <f t="shared" si="13"/>
-        <v>720</v>
-      </c>
-      <c r="M65" s="125">
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M65" s="185">
         <f t="shared" si="23"/>
         <v>452.31077199999999</v>
       </c>
-      <c r="N65" s="125">
+      <c r="N65" s="185">
         <f t="shared" si="24"/>
         <v>153.75369599999999</v>
       </c>
-      <c r="O65" s="125">
+      <c r="O65" s="185">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="P65" s="72">
+      <c r="P65" s="186">
         <f t="shared" si="17"/>
-        <v>2317.23</v>
-      </c>
-      <c r="Q65" s="73">
+        <v>1552.23</v>
+      </c>
+      <c r="Q65" s="187">
         <f t="shared" si="25"/>
-        <v>2387.23</v>
+        <v>1599.23</v>
       </c>
       <c r="R65" s="44">
         <f t="shared" si="19"/>
         <v>0.23</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="61">
         <v>10</v>
       </c>
@@ -7378,14 +7385,15 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G66" s="69">
-        <v>1442.24</v>
+        <v>1260.24</v>
       </c>
       <c r="H66" s="118">
-        <v>1485.24</v>
+        <f>G66</f>
+        <v>1260.24</v>
       </c>
       <c r="I66" s="70">
         <f t="shared" si="20"/>
-        <v>-43</v>
+        <v>0</v>
       </c>
       <c r="J66" s="70">
         <f t="shared" si="21"/>
@@ -7393,11 +7401,11 @@
       </c>
       <c r="K66" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L66" s="71">
         <f t="shared" si="13"/>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M66" s="125">
         <f t="shared" si="23"/>
@@ -7413,18 +7421,18 @@
       </c>
       <c r="P66" s="72">
         <f t="shared" si="17"/>
-        <v>1283.24</v>
+        <v>1552.24</v>
       </c>
       <c r="Q66" s="73">
         <f t="shared" si="25"/>
-        <v>1321.24</v>
+        <v>1599.24</v>
       </c>
       <c r="R66" s="44">
         <f t="shared" si="19"/>
         <v>0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="61">
         <v>10</v>
       </c>
@@ -7444,11 +7452,11 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G67" s="69">
-        <v>1442.25</v>
+        <v>1303.25</v>
       </c>
       <c r="H67" s="118">
         <f>G67</f>
-        <v>1442.25</v>
+        <v>1303.25</v>
       </c>
       <c r="I67" s="70">
         <f t="shared" si="20"/>
@@ -7460,11 +7468,11 @@
       </c>
       <c r="K67" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L67" s="71">
         <f t="shared" si="13"/>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M67" s="125">
         <f t="shared" si="23"/>
@@ -7480,18 +7488,18 @@
       </c>
       <c r="P67" s="72">
         <f t="shared" si="17"/>
-        <v>1326.25</v>
+        <v>1552.25</v>
       </c>
       <c r="Q67" s="73">
         <f t="shared" si="25"/>
-        <v>1366.25</v>
+        <v>1599.25</v>
       </c>
       <c r="R67" s="44">
         <f t="shared" si="19"/>
         <v>0.25</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="61">
         <v>10</v>
       </c>
@@ -7505,17 +7513,17 @@
         <v>134</v>
       </c>
       <c r="E68" s="60" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="F68" s="75">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G68" s="69">
-        <v>1064.26</v>
+        <v>1303.26</v>
       </c>
       <c r="H68" s="118">
-        <f>1064.26</f>
-        <v>1064.26</v>
+        <f>G68</f>
+        <v>1303.26</v>
       </c>
       <c r="I68" s="70">
         <f t="shared" si="20"/>
@@ -7527,11 +7535,11 @@
       </c>
       <c r="K68" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L68" s="71">
         <f t="shared" si="13"/>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M68" s="125">
         <f t="shared" si="23"/>
@@ -7547,18 +7555,18 @@
       </c>
       <c r="P68" s="72">
         <f t="shared" si="17"/>
-        <v>1326.26</v>
+        <v>1552.26</v>
       </c>
       <c r="Q68" s="73">
         <f t="shared" si="25"/>
-        <v>1366.26</v>
+        <v>1599.26</v>
       </c>
       <c r="R68" s="44">
         <f t="shared" si="19"/>
         <v>0.26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="61">
         <v>11</v>
       </c>
@@ -7576,24 +7584,24 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G69" s="69">
-        <v>13721.27</v>
+        <v>15436.27</v>
       </c>
       <c r="H69" s="118"/>
       <c r="I69" s="70">
         <f t="shared" si="20"/>
-        <v>13721.27</v>
+        <v>15436.27</v>
       </c>
       <c r="J69" s="70">
         <f t="shared" si="21"/>
-        <v>411.63810000000001</v>
+        <v>463.0881</v>
       </c>
       <c r="K69" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L69" s="71">
         <f t="shared" ref="L69:L90" si="26">M$1*F69</f>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M69" s="125">
         <f t="shared" si="23"/>
@@ -7609,18 +7617,18 @@
       </c>
       <c r="P69" s="72">
         <f t="shared" ref="P69:P90" si="28">ROUND(SUM(I69:O69),0) + R69</f>
-        <v>15459.27</v>
+        <v>17451.27</v>
       </c>
       <c r="Q69" s="73">
         <f t="shared" si="25"/>
-        <v>15923.27</v>
+        <v>17975.27</v>
       </c>
       <c r="R69" s="44">
         <f t="shared" ref="R69:R90" si="29">ROUND(0.001+C69/100,2)</f>
         <v>0.27</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="61">
         <v>11</v>
       </c>
@@ -7638,24 +7646,24 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G70" s="69">
-        <v>13721.28</v>
+        <v>15436.28</v>
       </c>
       <c r="H70" s="118"/>
       <c r="I70" s="70">
         <f t="shared" si="20"/>
-        <v>13721.28</v>
+        <v>15436.28</v>
       </c>
       <c r="J70" s="70">
         <f t="shared" si="21"/>
-        <v>411.63839999999999</v>
+        <v>463.08839999999998</v>
       </c>
       <c r="K70" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L70" s="71">
         <f t="shared" si="26"/>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M70" s="125">
         <f t="shared" si="23"/>
@@ -7671,18 +7679,18 @@
       </c>
       <c r="P70" s="72">
         <f t="shared" si="28"/>
-        <v>15459.28</v>
+        <v>17451.28</v>
       </c>
       <c r="Q70" s="73">
         <f t="shared" si="25"/>
-        <v>15923.28</v>
+        <v>17975.28</v>
       </c>
       <c r="R70" s="44">
         <f t="shared" si="29"/>
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="61">
         <v>11</v>
       </c>
@@ -7702,24 +7710,27 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G71" s="69">
-        <v>2959.29</v>
-      </c>
-      <c r="H71" s="118"/>
+        <v>4352.29</v>
+      </c>
+      <c r="H71" s="118">
+        <f>G71</f>
+        <v>4352.29</v>
+      </c>
       <c r="I71" s="70">
         <f t="shared" si="20"/>
-        <v>2959.29</v>
+        <v>0</v>
       </c>
       <c r="J71" s="70">
         <f t="shared" si="21"/>
-        <v>88.778700000000001</v>
+        <v>0</v>
       </c>
       <c r="K71" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L71" s="71">
         <f t="shared" si="26"/>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M71" s="125">
         <f t="shared" si="23"/>
@@ -7735,18 +7746,18 @@
       </c>
       <c r="P71" s="72">
         <f t="shared" si="28"/>
-        <v>4374.29</v>
+        <v>1552.29</v>
       </c>
       <c r="Q71" s="73">
         <f t="shared" si="25"/>
-        <v>4505.29</v>
+        <v>1599.29</v>
       </c>
       <c r="R71" s="44">
         <f t="shared" si="29"/>
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="61"/>
       <c r="B72" s="77" t="s">
         <v>223</v>
@@ -7764,24 +7775,27 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G72" s="69">
-        <v>1442.3</v>
-      </c>
-      <c r="H72" s="118"/>
+        <v>2789.3</v>
+      </c>
+      <c r="H72" s="118">
+        <f>G72</f>
+        <v>2789.3</v>
+      </c>
       <c r="I72" s="70">
         <f t="shared" si="20"/>
-        <v>1442.3</v>
+        <v>0</v>
       </c>
       <c r="J72" s="70">
         <f t="shared" si="21"/>
-        <v>43.268999999999998</v>
+        <v>0</v>
       </c>
       <c r="K72" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L72" s="71">
         <f t="shared" si="26"/>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M72" s="125">
         <f t="shared" si="23"/>
@@ -7797,18 +7811,18 @@
       </c>
       <c r="P72" s="72">
         <f t="shared" si="28"/>
-        <v>2812.3</v>
+        <v>1552.3</v>
       </c>
       <c r="Q72" s="73">
         <f t="shared" si="25"/>
-        <v>2896.3</v>
+        <v>1599.3</v>
       </c>
       <c r="R72" s="44">
         <f t="shared" si="29"/>
         <v>0.3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="61"/>
       <c r="B73" s="77" t="s">
         <v>224</v>
@@ -7824,24 +7838,24 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="G73" s="69">
-        <v>7279.31</v>
+        <v>8801.31</v>
       </c>
       <c r="H73" s="118"/>
       <c r="I73" s="70">
         <f t="shared" si="20"/>
-        <v>7279.31</v>
+        <v>8801.31</v>
       </c>
       <c r="J73" s="70">
         <f t="shared" si="21"/>
-        <v>218.3793</v>
+        <v>264.03929999999997</v>
       </c>
       <c r="K73" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>9.7046640000000011</v>
       </c>
       <c r="L73" s="71">
         <f t="shared" si="26"/>
-        <v>720</v>
+        <v>935.76638800000012</v>
       </c>
       <c r="M73" s="125">
         <f t="shared" si="23"/>
@@ -7857,18 +7871,18 @@
       </c>
       <c r="P73" s="72">
         <f t="shared" si="28"/>
-        <v>8824.31</v>
+        <v>10617.31</v>
       </c>
       <c r="Q73" s="73">
         <f t="shared" si="25"/>
-        <v>9089.31</v>
+        <v>10936.31</v>
       </c>
       <c r="R73" s="44">
         <f t="shared" si="29"/>
         <v>0.31</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="61"/>
       <c r="B74" s="77" t="s">
         <v>225</v>
@@ -7884,24 +7898,24 @@
         <v>1.5800000000000002E-2</v>
       </c>
       <c r="G74" s="69">
-        <v>2619346.3199999998</v>
+        <v>2800902.32</v>
       </c>
       <c r="H74" s="118"/>
       <c r="I74" s="70">
         <f t="shared" si="20"/>
-        <v>2619346.3199999998</v>
+        <v>2800902.32</v>
       </c>
       <c r="J74" s="70">
         <f t="shared" si="21"/>
-        <v>78580.389599999995</v>
+        <v>84027.069599999988</v>
       </c>
       <c r="K74" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>766.66845600000011</v>
       </c>
       <c r="L74" s="71">
         <f t="shared" si="26"/>
-        <v>56880.000000000007</v>
+        <v>73925.544652000011</v>
       </c>
       <c r="M74" s="125">
         <f t="shared" si="23"/>
@@ -7912,23 +7926,22 @@
         <v>12146.541984000001</v>
       </c>
       <c r="O74" s="125">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <v>93376</v>
       </c>
       <c r="P74" s="72">
         <f t="shared" si="28"/>
-        <v>2802686.32</v>
+        <v>3100877.32</v>
       </c>
       <c r="Q74" s="73">
         <f t="shared" si="25"/>
-        <v>2886767.32</v>
+        <v>3193903.32</v>
       </c>
       <c r="R74" s="44">
         <f t="shared" si="29"/>
         <v>0.32</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="61"/>
       <c r="B75" s="77" t="s">
         <v>227</v>
@@ -7944,24 +7957,24 @@
         <v>6.1000000000000004E-3</v>
       </c>
       <c r="G75" s="69">
-        <v>340121.01</v>
+        <v>390081.01</v>
       </c>
       <c r="H75" s="118"/>
       <c r="I75" s="70">
         <f t="shared" si="20"/>
-        <v>340121.01</v>
+        <v>390081.01</v>
       </c>
       <c r="J75" s="70">
         <f t="shared" si="21"/>
-        <v>10203.630300000001</v>
+        <v>11702.4303</v>
       </c>
       <c r="K75" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>295.99225200000001</v>
       </c>
       <c r="L75" s="71">
         <f t="shared" si="26"/>
-        <v>21960</v>
+        <v>28540.874834000006</v>
       </c>
       <c r="M75" s="125">
         <f t="shared" si="23"/>
@@ -7977,51 +7990,54 @@
       </c>
       <c r="P75" s="72">
         <f t="shared" si="28"/>
-        <v>390770.01</v>
+        <v>449105.01</v>
       </c>
       <c r="Q75" s="73">
         <f t="shared" si="25"/>
-        <v>402493.01</v>
+        <v>462578.01</v>
       </c>
       <c r="R75" s="44">
         <f t="shared" si="29"/>
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="61"/>
-      <c r="B76" s="195" t="s">
+      <c r="B76" s="229" t="s">
         <v>228</v>
       </c>
-      <c r="C76" s="193">
+      <c r="C76" s="60">
         <v>2</v>
       </c>
-      <c r="D76" s="196" t="s">
+      <c r="D76" s="78" t="s">
         <v>229</v>
       </c>
-      <c r="E76" s="196"/>
+      <c r="E76" s="78"/>
       <c r="F76" s="79">
         <v>6.4000000000000003E-3</v>
       </c>
       <c r="G76" s="69">
-        <v>46160.02</v>
-      </c>
-      <c r="H76" s="118"/>
+        <v>89256.02</v>
+      </c>
+      <c r="H76" s="118">
+        <f>G76</f>
+        <v>89256.02</v>
+      </c>
       <c r="I76" s="70">
         <f t="shared" si="20"/>
-        <v>46160.02</v>
+        <v>0</v>
       </c>
       <c r="J76" s="70">
         <f t="shared" si="21"/>
-        <v>1384.8005999999998</v>
+        <v>0</v>
       </c>
       <c r="K76" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>310.54924800000003</v>
       </c>
       <c r="L76" s="71">
         <f t="shared" si="26"/>
-        <v>23040</v>
+        <v>29944.524416000004</v>
       </c>
       <c r="M76" s="125">
         <f t="shared" si="23"/>
@@ -8037,18 +8053,18 @@
       </c>
       <c r="P76" s="72">
         <f t="shared" si="28"/>
-        <v>89979.02</v>
+        <v>49649.02</v>
       </c>
       <c r="Q76" s="73">
         <f t="shared" si="25"/>
-        <v>92678.02</v>
+        <v>51138.02</v>
       </c>
       <c r="R76" s="44">
         <f t="shared" si="29"/>
         <v>0.02</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="61"/>
       <c r="B77" s="77" t="s">
         <v>230</v>
@@ -8064,10 +8080,11 @@
         <v>5.7000000000000002E-3</v>
       </c>
       <c r="G77" s="69">
-        <v>41111.03</v>
+        <v>37149.03</v>
       </c>
       <c r="H77" s="118">
-        <v>41111.03</v>
+        <f>G77</f>
+        <v>37149.03</v>
       </c>
       <c r="I77" s="70">
         <f t="shared" si="20"/>
@@ -8079,11 +8096,11 @@
       </c>
       <c r="K77" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>276.58292399999999</v>
       </c>
       <c r="L77" s="71">
         <f t="shared" si="26"/>
-        <v>20520</v>
+        <v>26669.342058000002</v>
       </c>
       <c r="M77" s="125">
         <f t="shared" si="23"/>
@@ -8099,18 +8116,18 @@
       </c>
       <c r="P77" s="72">
         <f t="shared" si="28"/>
-        <v>37793.03</v>
+        <v>44219.03</v>
       </c>
       <c r="Q77" s="73">
         <f t="shared" si="25"/>
-        <v>38927.03</v>
+        <v>45546.03</v>
       </c>
       <c r="R77" s="44">
         <f t="shared" si="29"/>
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="61"/>
       <c r="B78" s="77" t="s">
         <v>232</v>
@@ -8126,24 +8143,24 @@
         <v>5.3E-3</v>
       </c>
       <c r="G78" s="69">
-        <v>38226.04</v>
+        <v>73915.039999999994</v>
       </c>
       <c r="H78" s="118"/>
       <c r="I78" s="70">
         <f t="shared" si="20"/>
-        <v>38226.04</v>
+        <v>73915.039999999994</v>
       </c>
       <c r="J78" s="70">
         <f t="shared" si="21"/>
-        <v>1146.7811999999999</v>
+        <v>2217.4511999999995</v>
       </c>
       <c r="K78" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L78" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M78" s="125">
         <f t="shared" si="23"/>
@@ -8159,18 +8176,18 @@
       </c>
       <c r="P78" s="72">
         <f t="shared" si="28"/>
-        <v>74514.039999999994</v>
+        <v>117248.04</v>
       </c>
       <c r="Q78" s="73">
         <f t="shared" si="25"/>
-        <v>76749.039999999994</v>
+        <v>120765.04</v>
       </c>
       <c r="R78" s="44">
         <f t="shared" si="29"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="61"/>
       <c r="B79" s="77" t="s">
         <v>233</v>
@@ -8188,11 +8205,11 @@
         <v>5.3E-3</v>
       </c>
       <c r="G79" s="69">
-        <v>38226.050000000003</v>
+        <v>34542.050000000003</v>
       </c>
       <c r="H79" s="118">
-        <f>6360+31866.05</f>
-        <v>38226.050000000003</v>
+        <f>G79</f>
+        <v>34542.050000000003</v>
       </c>
       <c r="I79" s="70">
         <f t="shared" si="20"/>
@@ -8204,11 +8221,11 @@
       </c>
       <c r="K79" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L79" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M79" s="125">
         <f t="shared" si="23"/>
@@ -8224,18 +8241,18 @@
       </c>
       <c r="P79" s="72">
         <f t="shared" si="28"/>
-        <v>35141.050000000003</v>
+        <v>41116.050000000003</v>
       </c>
       <c r="Q79" s="73">
         <f t="shared" si="25"/>
-        <v>36195.050000000003</v>
+        <v>42349.05</v>
       </c>
       <c r="R79" s="44">
         <f t="shared" si="29"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="61"/>
       <c r="B80" s="77" t="s">
         <v>234</v>
@@ -8253,15 +8270,15 @@
         <v>5.3E-3</v>
       </c>
       <c r="G80" s="69">
-        <v>38226.06</v>
+        <v>27846.063999999998</v>
       </c>
       <c r="H80" s="118">
-        <f>6360.06+39373.06</f>
-        <v>45733.119999999995</v>
+        <f>G80</f>
+        <v>27846.063999999998</v>
       </c>
       <c r="I80" s="84">
         <f t="shared" si="20"/>
-        <v>-7507.0599999999977</v>
+        <v>0</v>
       </c>
       <c r="J80" s="70">
         <f t="shared" si="21"/>
@@ -8269,11 +8286,11 @@
       </c>
       <c r="K80" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L80" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M80" s="125">
         <f t="shared" si="23"/>
@@ -8289,21 +8306,21 @@
       </c>
       <c r="P80" s="72">
         <f t="shared" si="28"/>
-        <v>27634.06</v>
+        <v>41116.06</v>
       </c>
       <c r="Q80" s="73">
         <f t="shared" si="25"/>
-        <v>28463.06</v>
+        <v>42349.06</v>
       </c>
       <c r="R80" s="44">
         <f t="shared" si="29"/>
         <v>0.06</v>
       </c>
-      <c r="S80" s="168" t="s">
+      <c r="S80" s="164" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="61">
         <v>12</v>
       </c>
@@ -8323,11 +8340,11 @@
         <v>5.3E-3</v>
       </c>
       <c r="G81" s="69">
-        <v>38226.07</v>
+        <v>34542.07</v>
       </c>
       <c r="H81" s="118">
         <f>G81</f>
-        <v>38226.07</v>
+        <v>34542.07</v>
       </c>
       <c r="I81" s="70">
         <f t="shared" si="20"/>
@@ -8339,11 +8356,11 @@
       </c>
       <c r="K81" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L81" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M81" s="125">
         <f t="shared" si="23"/>
@@ -8359,18 +8376,18 @@
       </c>
       <c r="P81" s="72">
         <f t="shared" si="28"/>
-        <v>35141.07</v>
+        <v>41116.07</v>
       </c>
       <c r="Q81" s="73">
         <f t="shared" si="25"/>
-        <v>36195.07</v>
+        <v>42349.07</v>
       </c>
       <c r="R81" s="44">
         <f t="shared" si="29"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="61">
         <v>12</v>
       </c>
@@ -8383,29 +8400,29 @@
       <c r="D82" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="E82" s="170"/>
+      <c r="E82" s="166"/>
       <c r="F82" s="79">
         <v>5.3E-3</v>
       </c>
       <c r="G82" s="69">
-        <v>192869.08</v>
+        <v>233198.07999999999</v>
       </c>
       <c r="H82" s="118"/>
       <c r="I82" s="70">
         <f t="shared" si="20"/>
-        <v>192869.08</v>
+        <v>233198.07999999999</v>
       </c>
       <c r="J82" s="70">
         <f t="shared" si="21"/>
-        <v>5786.0723999999991</v>
+        <v>6995.942399999999</v>
       </c>
       <c r="K82" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L82" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M82" s="125">
         <f t="shared" si="23"/>
@@ -8421,18 +8438,18 @@
       </c>
       <c r="P82" s="72">
         <f t="shared" si="28"/>
-        <v>233796.08</v>
+        <v>281310.08000000002</v>
       </c>
       <c r="Q82" s="73">
         <f t="shared" si="25"/>
-        <v>240810.08</v>
+        <v>289749.08</v>
       </c>
       <c r="R82" s="44">
         <f t="shared" si="29"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="61">
         <v>12</v>
       </c>
@@ -8453,24 +8470,24 @@
         <v>5.3E-3</v>
       </c>
       <c r="G83" s="69">
-        <v>123624.09</v>
+        <v>161875.09</v>
       </c>
       <c r="H83" s="118"/>
       <c r="I83" s="70">
         <f t="shared" si="20"/>
-        <v>123624.09</v>
+        <v>161875.09</v>
       </c>
       <c r="J83" s="70">
         <f t="shared" si="21"/>
-        <v>3708.7226999999998</v>
+        <v>4856.2527</v>
       </c>
       <c r="K83" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L83" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M83" s="125">
         <f t="shared" si="23"/>
@@ -8486,18 +8503,18 @@
       </c>
       <c r="P83" s="72">
         <f t="shared" si="28"/>
-        <v>162474.09</v>
+        <v>207847.09</v>
       </c>
       <c r="Q83" s="73">
         <f t="shared" si="25"/>
-        <v>167348.09</v>
+        <v>214082.09</v>
       </c>
       <c r="R83" s="44">
         <f t="shared" si="29"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="61"/>
       <c r="B84" s="76" t="s">
         <v>240</v>
@@ -8513,24 +8530,24 @@
         <v>5.3E-3</v>
       </c>
       <c r="G84" s="69">
-        <v>292057.09999999998</v>
+        <v>335361.09999999998</v>
       </c>
       <c r="H84" s="118"/>
       <c r="I84" s="70">
         <f t="shared" si="20"/>
-        <v>292057.09999999998</v>
+        <v>335361.09999999998</v>
       </c>
       <c r="J84" s="70">
         <f t="shared" si="21"/>
-        <v>8761.7129999999997</v>
+        <v>10060.832999999999</v>
       </c>
       <c r="K84" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L84" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M84" s="125">
         <f t="shared" si="23"/>
@@ -8546,55 +8563,53 @@
       </c>
       <c r="P84" s="72">
         <f t="shared" si="28"/>
-        <v>335960.1</v>
+        <v>386538.1</v>
       </c>
       <c r="Q84" s="73">
         <f t="shared" si="25"/>
-        <v>346039.1</v>
+        <v>398134.1</v>
       </c>
       <c r="R84" s="44">
         <f t="shared" si="29"/>
         <v>0.1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="61"/>
       <c r="B85" s="76" t="s">
         <v>241</v>
       </c>
-      <c r="C85" s="76">
+      <c r="C85" s="192">
         <v>11</v>
       </c>
-      <c r="D85" s="176" t="s">
+      <c r="D85" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="E85" s="176" t="s">
-        <v>264</v>
-      </c>
-      <c r="F85" s="177">
+      <c r="E85" s="60" t="s">
+        <v>252</v>
+      </c>
+      <c r="F85" s="179">
         <v>5.3E-3</v>
       </c>
       <c r="G85" s="69">
-        <v>117437.11</v>
-      </c>
-      <c r="H85" s="118">
-        <v>28633</v>
-      </c>
+        <v>126011.11</v>
+      </c>
+      <c r="H85" s="118"/>
       <c r="I85" s="70">
         <f t="shared" si="20"/>
-        <v>88804.11</v>
+        <v>126011.11</v>
       </c>
       <c r="J85" s="70">
         <f t="shared" si="21"/>
-        <v>2664.1232999999997</v>
+        <v>3780.3332999999998</v>
       </c>
       <c r="K85" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L85" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M85" s="125">
         <f t="shared" si="23"/>
@@ -8610,18 +8625,18 @@
       </c>
       <c r="P85" s="72">
         <f t="shared" si="28"/>
-        <v>126609.11</v>
+        <v>170907.11</v>
       </c>
       <c r="Q85" s="73">
         <f t="shared" si="25"/>
-        <v>130407.11</v>
+        <v>176034.11</v>
       </c>
       <c r="R85" s="44">
         <f t="shared" si="29"/>
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="61"/>
       <c r="B86" s="76" t="s">
         <v>242</v>
@@ -8629,7 +8644,7 @@
       <c r="C86" s="76">
         <v>12</v>
       </c>
-      <c r="D86" s="171" t="s">
+      <c r="D86" s="167" t="s">
         <v>119</v>
       </c>
       <c r="E86" s="60" t="s">
@@ -8639,11 +8654,11 @@
         <v>5.3E-3</v>
       </c>
       <c r="G86" s="69">
-        <v>38226.120000000003</v>
+        <v>34542.120000000003</v>
       </c>
       <c r="H86" s="118">
-        <f>31866+6360.12</f>
-        <v>38226.120000000003</v>
+        <f>G86</f>
+        <v>34542.120000000003</v>
       </c>
       <c r="I86" s="70">
         <f t="shared" si="20"/>
@@ -8655,11 +8670,11 @@
       </c>
       <c r="K86" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L86" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M86" s="125">
         <f t="shared" si="23"/>
@@ -8675,81 +8690,81 @@
       </c>
       <c r="P86" s="72">
         <f t="shared" si="28"/>
-        <v>35141.120000000003</v>
+        <v>41116.120000000003</v>
       </c>
       <c r="Q86" s="73">
         <f t="shared" si="25"/>
-        <v>36195.120000000003</v>
+        <v>42349.120000000003</v>
       </c>
       <c r="R86" s="44">
         <f t="shared" si="29"/>
         <v>0.12</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="61"/>
-      <c r="B87" s="61" t="s">
+      <c r="B87" s="180" t="s">
         <v>243</v>
       </c>
-      <c r="C87" s="61">
+      <c r="C87" s="180">
         <v>13</v>
       </c>
-      <c r="D87" s="178" t="s">
+      <c r="D87" s="188" t="s">
         <v>141</v>
       </c>
-      <c r="E87" s="179"/>
-      <c r="F87" s="177">
+      <c r="E87" s="189"/>
+      <c r="F87" s="181">
         <v>5.3E-3</v>
       </c>
-      <c r="G87" s="69">
-        <v>38226.129999999997</v>
-      </c>
-      <c r="H87" s="118">
+      <c r="G87" s="182">
+        <v>34542.129999999997</v>
+      </c>
+      <c r="H87" s="230">
         <f>G87</f>
-        <v>38226.129999999997</v>
-      </c>
-      <c r="I87" s="70">
+        <v>34542.129999999997</v>
+      </c>
+      <c r="I87" s="183">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J87" s="70">
+      <c r="J87" s="183">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="K87" s="71">
+      <c r="K87" s="184">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L87" s="71">
+        <v>257.17359599999997</v>
+      </c>
+      <c r="L87" s="184">
         <f t="shared" si="26"/>
-        <v>19080</v>
-      </c>
-      <c r="M87" s="125">
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M87" s="185">
         <f t="shared" si="23"/>
         <v>11986.235457999999</v>
       </c>
-      <c r="N87" s="125">
+      <c r="N87" s="185">
         <f t="shared" si="24"/>
         <v>4074.4729440000001</v>
       </c>
-      <c r="O87" s="125">
+      <c r="O87" s="185">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="P87" s="72">
+      <c r="P87" s="186">
         <f t="shared" si="28"/>
-        <v>35141.129999999997</v>
-      </c>
-      <c r="Q87" s="73">
+        <v>41116.129999999997</v>
+      </c>
+      <c r="Q87" s="187">
         <f t="shared" si="25"/>
-        <v>36195.129999999997</v>
+        <v>42349.13</v>
       </c>
       <c r="R87" s="44">
         <f t="shared" si="29"/>
         <v>0.13</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="61"/>
       <c r="B88" s="61" t="s">
         <v>244</v>
@@ -8757,7 +8772,7 @@
       <c r="C88" s="61">
         <v>14</v>
       </c>
-      <c r="D88" s="171" t="s">
+      <c r="D88" s="167" t="s">
         <v>129</v>
       </c>
       <c r="E88" s="74" t="s">
@@ -8767,15 +8782,15 @@
         <v>5.3E-3</v>
       </c>
       <c r="G88" s="69">
-        <v>29456.14</v>
+        <v>27298.14</v>
       </c>
       <c r="H88" s="118">
-        <f>6360.14+30340.14</f>
-        <v>36700.28</v>
+        <f>G88</f>
+        <v>27298.14</v>
       </c>
       <c r="I88" s="70">
         <f t="shared" si="20"/>
-        <v>-7244.1399999999994</v>
+        <v>0</v>
       </c>
       <c r="J88" s="70">
         <f t="shared" si="21"/>
@@ -8783,11 +8798,11 @@
       </c>
       <c r="K88" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L88" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M88" s="125">
         <f t="shared" si="23"/>
@@ -8803,18 +8818,18 @@
       </c>
       <c r="P88" s="72">
         <f t="shared" si="28"/>
-        <v>27897.14</v>
+        <v>41116.14</v>
       </c>
       <c r="Q88" s="73">
         <f t="shared" si="25"/>
-        <v>28734.14</v>
+        <v>42349.14</v>
       </c>
       <c r="R88" s="44">
         <f t="shared" si="29"/>
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="61"/>
       <c r="B89" s="61" t="s">
         <v>246</v>
@@ -8822,7 +8837,7 @@
       <c r="C89" s="61">
         <v>15</v>
       </c>
-      <c r="D89" s="171" t="s">
+      <c r="D89" s="167" t="s">
         <v>111</v>
       </c>
       <c r="E89" s="74" t="str">
@@ -8833,11 +8848,11 @@
         <v>5.3E-3</v>
       </c>
       <c r="G89" s="69">
-        <v>38226.15</v>
+        <v>34542.15</v>
       </c>
       <c r="H89" s="118">
         <f>G89</f>
-        <v>38226.15</v>
+        <v>34542.15</v>
       </c>
       <c r="I89" s="70">
         <f t="shared" si="20"/>
@@ -8849,11 +8864,11 @@
       </c>
       <c r="K89" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>257.17359599999997</v>
       </c>
       <c r="L89" s="71">
         <f t="shared" si="26"/>
-        <v>19080</v>
+        <v>24797.809282000002</v>
       </c>
       <c r="M89" s="125">
         <f t="shared" si="23"/>
@@ -8869,18 +8884,18 @@
       </c>
       <c r="P89" s="72">
         <f t="shared" si="28"/>
-        <v>35141.15</v>
+        <v>41116.15</v>
       </c>
       <c r="Q89" s="73">
         <f t="shared" si="25"/>
-        <v>36195.15</v>
+        <v>42349.15</v>
       </c>
       <c r="R89" s="44">
         <f t="shared" si="29"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="60"/>
       <c r="B90" s="60" t="s">
         <v>247</v>
@@ -8895,25 +8910,27 @@
       <c r="F90" s="68">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="G90" s="148">
-        <v>44717.16</v>
-      </c>
-      <c r="H90" s="118"/>
-      <c r="I90" s="149">
+      <c r="G90" s="145">
+        <v>86467.16</v>
+      </c>
+      <c r="H90" s="118">
+        <v>80467.16</v>
+      </c>
+      <c r="I90" s="146">
         <f t="shared" si="20"/>
-        <v>44717.16</v>
+        <v>6000</v>
       </c>
       <c r="J90" s="70">
         <f t="shared" si="21"/>
-        <v>1341.5148000000002</v>
+        <v>180</v>
       </c>
       <c r="K90" s="71">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>300.844584</v>
       </c>
       <c r="L90" s="71">
         <f t="shared" si="26"/>
-        <v>22320</v>
+        <v>29008.758028</v>
       </c>
       <c r="M90" s="125">
         <f t="shared" si="23"/>
@@ -8929,223 +8946,223 @@
       </c>
       <c r="P90" s="72">
         <f t="shared" si="28"/>
-        <v>87167.16</v>
+        <v>54278.16</v>
       </c>
       <c r="Q90" s="73">
         <f t="shared" si="25"/>
-        <v>89782.16</v>
+        <v>55906.16</v>
       </c>
       <c r="R90" s="44">
         <f t="shared" si="29"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="61"/>
-      <c r="B91" s="138"/>
-      <c r="C91" s="138"/>
-      <c r="D91" s="138"/>
-      <c r="E91" s="138"/>
-      <c r="F91" s="150"/>
-      <c r="G91" s="151"/>
-      <c r="H91" s="152"/>
-      <c r="I91" s="153"/>
-      <c r="J91" s="154"/>
-      <c r="K91" s="155"/>
-      <c r="L91" s="156"/>
-      <c r="M91" s="156"/>
-      <c r="N91" s="156"/>
-      <c r="O91" s="156"/>
-      <c r="P91" s="157"/>
-      <c r="Q91" s="157"/>
+      <c r="B91" s="136"/>
+      <c r="C91" s="136"/>
+      <c r="D91" s="136"/>
+      <c r="E91" s="136"/>
+      <c r="F91" s="147"/>
+      <c r="G91" s="148"/>
+      <c r="H91" s="231"/>
+      <c r="I91" s="149"/>
+      <c r="J91" s="150"/>
+      <c r="K91" s="151"/>
+      <c r="L91" s="152"/>
+      <c r="M91" s="152"/>
+      <c r="N91" s="152"/>
+      <c r="O91" s="152"/>
+      <c r="P91" s="153"/>
+      <c r="Q91" s="153"/>
       <c r="R91" s="44"/>
     </row>
-    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="80"/>
-      <c r="B92" s="158"/>
-      <c r="C92" s="159"/>
-      <c r="D92" s="160"/>
-      <c r="E92" s="160"/>
-      <c r="F92" s="161">
+      <c r="B92" s="154"/>
+      <c r="C92" s="155"/>
+      <c r="D92" s="156"/>
+      <c r="E92" s="156"/>
+      <c r="F92" s="157">
         <f t="shared" ref="F92:L92" si="30">SUM(F5:F91)</f>
         <v>0.99999999999999956</v>
       </c>
-      <c r="G92" s="162">
+      <c r="G92" s="158">
         <f t="shared" si="30"/>
-        <v>13317175.699999997</v>
-      </c>
-      <c r="H92" s="163">
+        <v>13168221.703999996</v>
+      </c>
+      <c r="H92" s="159">
         <f t="shared" si="30"/>
-        <v>6886831.2500000009</v>
-      </c>
-      <c r="I92" s="164">
+        <v>6136186.074</v>
+      </c>
+      <c r="I92" s="160">
         <f t="shared" si="30"/>
-        <v>6430344.4500000002</v>
-      </c>
-      <c r="J92" s="165">
+        <v>7032035.629999999</v>
+      </c>
+      <c r="J92" s="161">
         <f t="shared" si="30"/>
-        <v>197632.69379999998</v>
-      </c>
-      <c r="K92" s="165">
+        <v>212501.20919999998</v>
+      </c>
+      <c r="K92" s="161">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="L92" s="166">
+        <v>48523.319999999992</v>
+      </c>
+      <c r="L92" s="162">
         <f t="shared" si="30"/>
-        <v>3600000</v>
-      </c>
-      <c r="M92" s="166">
+        <v>4678831.9400000013</v>
+      </c>
+      <c r="M92" s="162">
         <f>SUM(M5:M90)</f>
         <v>2261553.8600000041</v>
       </c>
-      <c r="N92" s="166">
+      <c r="N92" s="162">
         <f>SUM(N5:N90)</f>
         <v>768768.48000000021</v>
       </c>
-      <c r="O92" s="166">
+      <c r="O92" s="162">
         <f>SUM(O5:O90)</f>
-        <v>0</v>
-      </c>
-      <c r="P92" s="167">
+        <v>93376</v>
+      </c>
+      <c r="P92" s="163">
         <f>SUM(P5:P91)</f>
-        <v>13258339.699999997</v>
-      </c>
-      <c r="Q92" s="167">
+        <v>15095635.699999999</v>
+      </c>
+      <c r="Q92" s="163">
         <f>SUM(Q5:Q91)</f>
-        <v>13656092.699999997</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+        <v>15548498.699999997</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D93" s="50"/>
       <c r="E93" s="50"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="D94" s="228" t="s">
-        <v>266</v>
-      </c>
-      <c r="E94" s="228"/>
-      <c r="F94" s="228"/>
-      <c r="G94" s="228"/>
-      <c r="H94" s="228"/>
-      <c r="I94" s="228"/>
-      <c r="J94" s="228"/>
-      <c r="K94" s="228"/>
-      <c r="L94" s="228"/>
-      <c r="M94" s="228"/>
-      <c r="N94" s="228"/>
-      <c r="O94" s="228"/>
-      <c r="P94" s="228"/>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="D95" s="228"/>
-      <c r="E95" s="228"/>
-      <c r="F95" s="228"/>
-      <c r="G95" s="228"/>
-      <c r="H95" s="228"/>
-      <c r="I95" s="228"/>
-      <c r="J95" s="228"/>
-      <c r="K95" s="228"/>
-      <c r="L95" s="228"/>
-      <c r="M95" s="228"/>
-      <c r="N95" s="228"/>
-      <c r="O95" s="228"/>
-      <c r="P95" s="228"/>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D94" s="243" t="s">
+        <v>254</v>
+      </c>
+      <c r="E94" s="243"/>
+      <c r="F94" s="243"/>
+      <c r="G94" s="243"/>
+      <c r="H94" s="243"/>
+      <c r="I94" s="243"/>
+      <c r="J94" s="243"/>
+      <c r="K94" s="243"/>
+      <c r="L94" s="243"/>
+      <c r="M94" s="243"/>
+      <c r="N94" s="243"/>
+      <c r="O94" s="243"/>
+      <c r="P94" s="243"/>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D95" s="243"/>
+      <c r="E95" s="243"/>
+      <c r="F95" s="243"/>
+      <c r="G95" s="243"/>
+      <c r="H95" s="243"/>
+      <c r="I95" s="243"/>
+      <c r="J95" s="243"/>
+      <c r="K95" s="243"/>
+      <c r="L95" s="243"/>
+      <c r="M95" s="243"/>
+      <c r="N95" s="243"/>
+      <c r="O95" s="243"/>
+      <c r="P95" s="243"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H96" s="119"/>
     </row>
-    <row r="97" spans="4:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D97" s="207" t="str">
+    <row r="97" spans="4:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D97" s="203" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</v>
       </c>
-      <c r="E97" s="202"/>
-      <c r="F97" s="202"/>
-      <c r="G97" s="202"/>
-      <c r="H97" s="202"/>
-      <c r="I97" s="202"/>
-      <c r="J97" s="202"/>
-      <c r="K97" s="202"/>
-      <c r="L97" s="202"/>
-      <c r="M97" s="202"/>
-      <c r="N97" s="202"/>
-      <c r="O97" s="202"/>
-      <c r="P97" s="202"/>
-    </row>
-    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D98" s="202"/>
-      <c r="E98" s="202"/>
-      <c r="F98" s="202"/>
-      <c r="G98" s="202"/>
-      <c r="H98" s="202"/>
-      <c r="I98" s="202"/>
-      <c r="J98" s="202"/>
-      <c r="K98" s="202"/>
-      <c r="L98" s="202"/>
-      <c r="M98" s="202"/>
-      <c r="N98" s="202"/>
-      <c r="O98" s="202"/>
-      <c r="P98" s="202"/>
-    </row>
-    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D99" s="202"/>
-      <c r="E99" s="202"/>
-      <c r="F99" s="202"/>
-      <c r="G99" s="202"/>
-      <c r="H99" s="202"/>
-      <c r="I99" s="202"/>
-      <c r="J99" s="202"/>
-      <c r="K99" s="202"/>
-      <c r="L99" s="202"/>
-      <c r="M99" s="202"/>
-      <c r="N99" s="202"/>
-      <c r="O99" s="202"/>
-      <c r="P99" s="202"/>
-    </row>
-    <row r="100" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D100" s="202"/>
-      <c r="E100" s="202"/>
-      <c r="F100" s="202"/>
-      <c r="G100" s="202"/>
-      <c r="H100" s="202"/>
-      <c r="I100" s="202"/>
-      <c r="J100" s="202"/>
-      <c r="K100" s="202"/>
-      <c r="L100" s="202"/>
-      <c r="M100" s="202"/>
-      <c r="N100" s="202"/>
-      <c r="O100" s="202"/>
-      <c r="P100" s="202"/>
-    </row>
-    <row r="101" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D101" s="202"/>
-      <c r="E101" s="202"/>
-      <c r="F101" s="202"/>
-      <c r="G101" s="202"/>
-      <c r="H101" s="202"/>
-      <c r="I101" s="202"/>
-      <c r="J101" s="202"/>
-      <c r="K101" s="202"/>
-      <c r="L101" s="202"/>
-      <c r="M101" s="202"/>
-      <c r="N101" s="202"/>
-      <c r="O101" s="202"/>
-      <c r="P101" s="202"/>
-    </row>
-    <row r="102" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D102" s="202"/>
-      <c r="E102" s="202"/>
-      <c r="F102" s="202"/>
-      <c r="G102" s="202"/>
-      <c r="H102" s="202"/>
-      <c r="I102" s="202"/>
-      <c r="J102" s="202"/>
-      <c r="K102" s="202"/>
-      <c r="L102" s="202"/>
-      <c r="M102" s="202"/>
-      <c r="N102" s="202"/>
-      <c r="O102" s="202"/>
-      <c r="P102" s="202"/>
+      <c r="E97" s="198"/>
+      <c r="F97" s="198"/>
+      <c r="G97" s="198"/>
+      <c r="H97" s="198"/>
+      <c r="I97" s="198"/>
+      <c r="J97" s="198"/>
+      <c r="K97" s="198"/>
+      <c r="L97" s="198"/>
+      <c r="M97" s="198"/>
+      <c r="N97" s="198"/>
+      <c r="O97" s="198"/>
+      <c r="P97" s="198"/>
+    </row>
+    <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D98" s="198"/>
+      <c r="E98" s="198"/>
+      <c r="F98" s="198"/>
+      <c r="G98" s="198"/>
+      <c r="H98" s="198"/>
+      <c r="I98" s="198"/>
+      <c r="J98" s="198"/>
+      <c r="K98" s="198"/>
+      <c r="L98" s="198"/>
+      <c r="M98" s="198"/>
+      <c r="N98" s="198"/>
+      <c r="O98" s="198"/>
+      <c r="P98" s="198"/>
+    </row>
+    <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="198"/>
+      <c r="E99" s="198"/>
+      <c r="F99" s="198"/>
+      <c r="G99" s="198"/>
+      <c r="H99" s="198"/>
+      <c r="I99" s="198"/>
+      <c r="J99" s="198"/>
+      <c r="K99" s="198"/>
+      <c r="L99" s="198"/>
+      <c r="M99" s="198"/>
+      <c r="N99" s="198"/>
+      <c r="O99" s="198"/>
+      <c r="P99" s="198"/>
+    </row>
+    <row r="100" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D100" s="198"/>
+      <c r="E100" s="198"/>
+      <c r="F100" s="198"/>
+      <c r="G100" s="198"/>
+      <c r="H100" s="198"/>
+      <c r="I100" s="198"/>
+      <c r="J100" s="198"/>
+      <c r="K100" s="198"/>
+      <c r="L100" s="198"/>
+      <c r="M100" s="198"/>
+      <c r="N100" s="198"/>
+      <c r="O100" s="198"/>
+      <c r="P100" s="198"/>
+    </row>
+    <row r="101" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D101" s="198"/>
+      <c r="E101" s="198"/>
+      <c r="F101" s="198"/>
+      <c r="G101" s="198"/>
+      <c r="H101" s="198"/>
+      <c r="I101" s="198"/>
+      <c r="J101" s="198"/>
+      <c r="K101" s="198"/>
+      <c r="L101" s="198"/>
+      <c r="M101" s="198"/>
+      <c r="N101" s="198"/>
+      <c r="O101" s="198"/>
+      <c r="P101" s="198"/>
+    </row>
+    <row r="102" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="198"/>
+      <c r="E102" s="198"/>
+      <c r="F102" s="198"/>
+      <c r="G102" s="198"/>
+      <c r="H102" s="198"/>
+      <c r="I102" s="198"/>
+      <c r="J102" s="198"/>
+      <c r="K102" s="198"/>
+      <c r="L102" s="198"/>
+      <c r="M102" s="198"/>
+      <c r="N102" s="198"/>
+      <c r="O102" s="198"/>
+      <c r="P102" s="198"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -9182,78 +9199,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8AEA40-856C-4C69-BDF8-B1FFAA30BA95}">
   <dimension ref="D3:I21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D3" s="119"/>
     </row>
-    <row r="4" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D4" s="119"/>
     </row>
-    <row r="5" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D5" s="119"/>
     </row>
-    <row r="6" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D6" s="119"/>
     </row>
-    <row r="7" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D7" s="119"/>
     </row>
-    <row r="8" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D8" s="187" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="9" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D8" s="171" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D9" s="119"/>
     </row>
-    <row r="10" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D10" s="119"/>
     </row>
-    <row r="11" spans="4:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="190" t="s">
-        <v>268</v>
-      </c>
-      <c r="E11" s="190"/>
-      <c r="F11" s="190"/>
-      <c r="G11" s="231" t="s">
-        <v>269</v>
-      </c>
-      <c r="H11" s="231"/>
-      <c r="I11" s="231"/>
-    </row>
-    <row r="12" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D12" s="119"/>
     </row>
-    <row r="13" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D13" s="119"/>
     </row>
-    <row r="14" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D14" s="119"/>
     </row>
-    <row r="15" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D15" s="197" t="s">
-        <v>270</v>
-      </c>
-      <c r="E15" s="197"/>
-      <c r="F15" s="197"/>
-      <c r="G15" s="197"/>
-      <c r="H15" s="197"/>
-      <c r="I15" s="197"/>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D15" s="172" t="s">
+        <v>256</v>
+      </c>
+      <c r="E15" s="172"/>
+      <c r="F15" s="172"/>
+      <c r="G15" s="172"/>
+      <c r="H15" s="172"/>
+      <c r="I15" s="172"/>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="119"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D21" s="119"/>
       <c r="E21" s="119"/>
       <c r="F21" s="119"/>
       <c r="G21" s="119"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="G11:I11"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>